--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -16783,8 +16783,11 @@
       <c r="A466" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B466" s="14" t="s">
-        <v>455</v>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>1 MWe Solid Oxide electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years. Produced amount of H2 over 20 years: 3779894.18 kg. Amounts of lanthanum oxide and strontium carbonate are unsure. 
+SOEC matched ceramic reference v1. YSZ: 8 mol% Y2O3 among binary oxides; YDC: Ce0.8Y0.2O1.9 (20% Y on cation sites). Gerloff 2021 capacity scaling of the attributed Haefele 2016 component masses, not concentrate mass treated as pure oxide. Mixed Sm/Eu/Gd proxy replaced by stoichiometric Y2O3. See data/metals/soec_ceramic_reference.json for source-access limits, explicit composition/scaling assumptions and remaining whole-stack gaps.</t>
+        </is>
       </c>
       <c r="K466" s="12"/>
       <c r="L466" s="12"/>
@@ -17051,11 +17054,13 @@
       <c r="R476"/>
     </row>
     <row r="477" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A477" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B477" s="12">
-        <v>170.7</v>
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>market for zirconium oxide</t>
+        </is>
+      </c>
+      <c r="B477">
+        <v>160.0199108606363</v>
       </c>
       <c r="C477" s="11" t="s">
         <v>17</v>
@@ -17066,11 +17071,15 @@
       <c r="F477" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G477" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="H477" s="11" t="s">
-        <v>158</v>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>zirconium oxide</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>YSZ ceramic component. SOEC matched ceramic reference v1. YSZ: 8 mol% Y2O3 among binary oxides; YDC: Ce0.8Y0.2O1.9 (20% Y on cation sites). Gerloff 2021 capacity scaling of the attributed Haefele 2016 component masses, not concentrate mass treated as pure oxide. Mixed Sm/Eu/Gd proxy replaced by stoichiometric Y2O3. See data/metals/soec_ceramic_reference.json for source-access limits, explicit composition/scaling assumptions and remaining whole-stack gaps.</t>
+        </is>
       </c>
       <c r="J477"/>
       <c r="K477" s="19"/>
@@ -17083,11 +17092,13 @@
       <c r="R477"/>
     </row>
     <row r="478" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A478" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B478" s="12">
-        <v>14.8</v>
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>market for yttrium oxide</t>
+        </is>
+      </c>
+      <c r="B478">
+        <v>25.49931784143426</v>
       </c>
       <c r="C478" s="11" t="s">
         <v>17</v>
@@ -17098,11 +17109,15 @@
       <c r="F478" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G478" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="H478" s="11" t="s">
-        <v>158</v>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>yttrium oxide</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>YSZ ceramic component. SOEC matched ceramic reference v1. YSZ: 8 mol% Y2O3 among binary oxides; YDC: Ce0.8Y0.2O1.9 (20% Y on cation sites). Gerloff 2021 capacity scaling of the attributed Haefele 2016 component masses, not concentrate mass treated as pure oxide. Mixed Sm/Eu/Gd proxy replaced by stoichiometric Y2O3. See data/metals/soec_ceramic_reference.json for source-access limits, explicit composition/scaling assumptions and remaining whole-stack gaps.</t>
+        </is>
       </c>
       <c r="J478"/>
       <c r="K478" s="19"/>
@@ -17115,11 +17130,13 @@
       <c r="R478"/>
     </row>
     <row r="479" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A479" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B479" s="12">
-        <v>91.5</v>
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>market for cerium oxide</t>
+        </is>
+      </c>
+      <c r="B479">
+        <v>98.25386326929126</v>
       </c>
       <c r="C479" s="11" t="s">
         <v>17</v>
@@ -17130,11 +17147,15 @@
       <c r="F479" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G479" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="H479" s="11" t="s">
-        <v>157</v>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>cerium oxide</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>YDC ceramic component. SOEC matched ceramic reference v1. YSZ: 8 mol% Y2O3 among binary oxides; YDC: Ce0.8Y0.2O1.9 (20% Y on cation sites). Gerloff 2021 capacity scaling of the attributed Haefele 2016 component masses, not concentrate mass treated as pure oxide. Mixed Sm/Eu/Gd proxy replaced by stoichiometric Y2O3. See data/metals/soec_ceramic_reference.json for source-access limits, explicit composition/scaling assumptions and remaining whole-stack gaps.</t>
+        </is>
       </c>
       <c r="J479"/>
       <c r="K479" s="19"/>
@@ -17147,11 +17168,13 @@
       <c r="R479"/>
     </row>
     <row r="480" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A480" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B480" s="12">
-        <v>22.9</v>
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>market for yttrium oxide</t>
+        </is>
+      </c>
+      <c r="B480">
+        <v>16.113284777632224</v>
       </c>
       <c r="C480" s="11" t="s">
         <v>17</v>
@@ -17162,11 +17185,15 @@
       <c r="F480" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G480" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="H480" s="11" t="s">
-        <v>157</v>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>yttrium oxide</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>YDC ceramic component. SOEC matched ceramic reference v1. YSZ: 8 mol% Y2O3 among binary oxides; YDC: Ce0.8Y0.2O1.9 (20% Y on cation sites). Gerloff 2021 capacity scaling of the attributed Haefele 2016 component masses, not concentrate mass treated as pure oxide. Mixed Sm/Eu/Gd proxy replaced by stoichiometric Y2O3. See data/metals/soec_ceramic_reference.json for source-access limits, explicit composition/scaling assumptions and remaining whole-stack gaps.</t>
+        </is>
       </c>
       <c r="J480"/>
       <c r="K480" s="19"/>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U633"/>
+  <dimension ref="A1:U657"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -8200,8 +8200,12 @@
       <c r="A165" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B165" s="14" t="s">
-        <v>56</v>
+      <c r="B165" s="14" t="inlineStr">
+        <is>
+          <t>APPROVED FINISHED PFSA MEMBRANE REFERENCE, issue90, 2026-10-18. Weber et al.2018 DOI10.1021/acs.est.8b02073 SISec1.2.1/TableS2 describesTFE+SO3-&gt;FDA,HFPoxidationwithNaOCl-&gt;HFPO,FDA+2HFPOadduct,Na2CO3pyrolysistoPSEPVE,polymerization90%yieldand39.31MJ/kgformingheat. Harzer2021PhD https://mediatum.ub.tum.de/doc/1634530/1634530.pdf synthesisfigurecorroboratesPSEPVE/alkalihydrolysis/acidconversion. ElectrolyzermembraneEW1100reference:Mechanical Characterization of Electrolyzer Membranes and Components Under Compression,2024 DOI10.1149/1945-7111/ad7a26. Theseareseparatechemistry/referenceproperties,not a measuredcompleteNafionfactory. Replace16kgTFEmonomerby16kgfinishedunreinforceddryacid-formPFSAperexisting1MWePEMstack. PreserveapprovedPt/Ir/coatingreferencesandlifetimepurchases. UseexplicitbalancednetengineeringchemistrywithEW1100g/molSO3H;n=6.557783744855004TFEbackboneunitsperC7F13O5SHacid-sidechainunit. FDA=C2F4O3SfromTFE+SO3;HFPO=C3F6OfromHFP+NaOCl,HFPfromTFEat1:1mass(rearrangementreference). FDA+2HFPO+Na2CO3-&gt;PSEPVE(C7F14O4S)+2NaF+2CO2;PSEPVE+backboneTFE+2NaOH+HCl-&gt;acidPFSA+NaF+NaCl+H2O. ThisNaOH/HClworkupis anexplicitbalancedengineeringvariant,not a claim ofHarzerKOH/HNO3industrialreagentchoice. Allupstreamintermediateconversionsassumed100%,overallfinishedpolymerretention90%asWeberreference. No2nd90%factoronprecursorinputs. Knownnetingredientsperkgfinished={'TFE': 1.0666093025141414, 'SO3': 0.08086565656565657, 'NaOCl': 0.15038135208080808, 'Na2CO3': 0.10705811975757576, 'NaOH': 0.0808015541010101, 'HCl': 0.03682626262626263};byproducts/reject={'NaCl': 0.17709020993939395, 'NaF': 0.1272368861909091, 'water': 0.018196969696969698, 'CO2': 0.08890707070707071, 'reject_PFSA': 0.11111111111111116}. BuyactualTFE,SO3,NaOCl,Na2CO3,NaOH,HCl,directlyatnetchainfeed;doNOTalsoaddcompleteWebermembranes orunsupportedHFP-&gt;hexafluoroethaneproxy. SaltoutputsNaCl/NaFandstoichiometricwatergotooneaqueouseffluentwith10kgprocesswater/kgfinished (explicitengineeringdilution,1-100kgsensitivity),1000kg/m3densityproxy. Fluoride-specificabatement/isolationanddissolvedsaltfateareunresolved;genericwastewaterisNOTvalidatedNaFdisposal. Polymerrejectgoestoexistingplasticincinerationwithoutcredit;stoichiometricCO2emittedonce.39.31MJ/kgWeberheat isoneaggregateon-sitechemicalsynthesis/filmformingallowance,notaddedagainateachmodeledintermediate;1kWh/kgsiteelectricityassumed. Existingnativeupstreamfeedproductionburdensremainseparate. TestEW1000-1200,finishedretention80-100%,heat20-80MJ/kg,andnonidealintermediateyields;thebalancednetrecipeis a stoichiometricengineeringreferencewithyield,NOTmeasuredindustrialgrosschemicalconsumption. Actualco-monomerpurification,catalysts,solventcirculation,intermediatescrap,PFASemissions,membranewatercontent,reinforcementandlong-termperformancearecoveragegaps. Finished16kgmasskept,notinferredfromfilmthicknessorcellarea. No native/runtime/YAMLorprimary-secondarysharechanges.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 MW PEM electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years per single stack, @ 8000 hours/year. Iridium mining process is NOT from ecoinvent. Produced amount of H2 over 20 years: 2964315.35 kg. According to a study called IndWEDe, it is assumed that the stacks are replaced 3 times during the 20 years lifespan, based on the 2030’s scenario for 1 MW systems which predicts a lifetime of 50,000 h or more for the stacks of the different water electrolysis technologies. In comparison to AEC electrolyzers, PEMEC electrolyzers are less mature. Furthermore, the PEMEC technology is commercially available and operates with a similar system efficiency as the AEC technology. However, the current density and the gas purity are higher with values in between 0.6–2.0 A/cm2 and &gt; 99.99%, respectively. Besides this, the operating pressure (below 200 bar) is significantly higher in comparison to AEC systems, while the operating temperature (50 °C to 80 °C) and the system energy (4.2–6.6 kWh/m3H2) are similar to AEC systems. The PEMEC BoP and stack components data stem from Bareiß et al. and correspond to a 1 MW system. Moreover, some further BoP components like water purifier &amp; feed tank, buffer tank, and heat exchanger have been added, derived from a 300 kW AEC system, under the assumption that the components are also suitable for a PEMEC system. The values have been scaled up from 300 kW to 1 MW. Values have already been multiplied by 3 to reflect 2 stack replacements over 20 years of use.</t>
+        </is>
       </c>
       <c r="K165" s="12"/>
       <c r="L165" s="12"/>
@@ -8460,14 +8464,18 @@
       <c r="R174"/>
     </row>
     <row r="175" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A175" s="11" t="s">
-        <v>21</v>
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+        </is>
       </c>
       <c r="B175" s="12">
         <v>16</v>
       </c>
-      <c r="C175" s="11" t="s">
-        <v>17</v>
+      <c r="C175" s="11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D175" s="11" t="s">
         <v>13</v>
@@ -8475,11 +8483,15 @@
       <c r="F175" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G175" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H175" s="11" t="s">
-        <v>62</v>
+      <c r="G175" s="11" t="inlineStr">
+        <is>
+          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+        </is>
+      </c>
+      <c r="H175" s="11" t="inlineStr">
+        <is>
+          <t>APPROVED FINISHED PFSA MEMBRANE REFERENCE, issue90, 2026-10-18. Weber et al.2018 DOI10.1021/acs.est.8b02073 SISec1.2.1/TableS2 describesTFE+SO3-&gt;FDA,HFPoxidationwithNaOCl-&gt;HFPO,FDA+2HFPOadduct,Na2CO3pyrolysistoPSEPVE,polymerization90%yieldand39.31MJ/kgformingheat. Harzer2021PhD https://mediatum.ub.tum.de/doc/1634530/1634530.pdf synthesisfigurecorroboratesPSEPVE/alkalihydrolysis/acidconversion. ElectrolyzermembraneEW1100reference:Mechanical Characterization of Electrolyzer Membranes and Components Under Compression,2024 DOI10.1149/1945-7111/ad7a26. Theseareseparatechemistry/referenceproperties,not a measuredcompleteNafionfactory. Replace16kgTFEmonomerby16kgfinishedunreinforceddryacid-formPFSAperexisting1MWePEMstack. PreserveapprovedPt/Ir/coatingreferencesandlifetimepurchases. UseexplicitbalancednetengineeringchemistrywithEW1100g/molSO3H;n=6.557783744855004TFEbackboneunitsperC7F13O5SHacid-sidechainunit. FDA=C2F4O3SfromTFE+SO3;HFPO=C3F6OfromHFP+NaOCl,HFPfromTFEat1:1mass(rearrangementreference). FDA+2HFPO+Na2CO3-&gt;PSEPVE(C7F14O4S)+2NaF+2CO2;PSEPVE+backboneTFE+2NaOH+HCl-&gt;acidPFSA+NaF+NaCl+H2O. ThisNaOH/HClworkupis anexplicitbalancedengineeringvariant,not a claim ofHarzerKOH/HNO3industrialreagentchoice. Allupstreamintermediateconversionsassumed100%,overallfinishedpolymerretention90%asWeberreference. No2nd90%factoronprecursorinputs. Knownnetingredientsperkgfinished={'TFE': 1.0666093025141414, 'SO3': 0.08086565656565657, 'NaOCl': 0.15038135208080808, 'Na2CO3': 0.10705811975757576, 'NaOH': 0.0808015541010101, 'HCl': 0.03682626262626263};byproducts/reject={'NaCl': 0.17709020993939395, 'NaF': 0.1272368861909091, 'water': 0.018196969696969698, 'CO2': 0.08890707070707071, 'reject_PFSA': 0.11111111111111116}. BuyactualTFE,SO3,NaOCl,Na2CO3,NaOH,HCl,directlyatnetchainfeed;doNOTalsoaddcompleteWebermembranes orunsupportedHFP-&gt;hexafluoroethaneproxy. SaltoutputsNaCl/NaFandstoichiometricwatergotooneaqueouseffluentwith10kgprocesswater/kgfinished (explicitengineeringdilution,1-100kgsensitivity),1000kg/m3densityproxy. Fluoride-specificabatement/isolationanddissolvedsaltfateareunresolved;genericwastewaterisNOTvalidatedNaFdisposal. Polymerrejectgoestoexistingplasticincinerationwithoutcredit;stoichiometricCO2emittedonce.39.31MJ/kgWeberheat isoneaggregateon-sitechemicalsynthesis/filmformingallowance,notaddedagainateachmodeledintermediate;1kWh/kgsiteelectricityassumed. Existingnativeupstreamfeedproductionburdensremainseparate. TestEW1000-1200,finishedretention80-100%,heat20-80MJ/kg,andnonidealintermediateyields;thebalancednetrecipeis a stoichiometricengineeringreferencewithyield,NOTmeasuredindustrialgrosschemicalconsumption. Actualco-monomerpurification,catalysts,solventcirculation,intermediatescrap,PFASemissions,membranewatercontent,reinforcementandlong-termperformancearecoveragegaps. Finished16kgmasskept,notinferredfromfilmthicknessorcellarea. No native/runtime/YAMLorprimary-secondarysharechanges.</t>
+        </is>
       </c>
       <c r="I175" s="11">
         <v>0</v>
@@ -21361,6 +21373,592 @@
       </c>
       <c r="I633">
         <v>0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B638">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Weber et al.2018 DOI10.1021/acs.est.8b02073 SISec1.2.1/TableS2 describesTFE+SO3-&gt;FDA,HFPoxidationwithNaOCl-&gt;HFPO,FDA+2HFPOadduct,Na2CO3pyrolysistoPSEPVE,polymerization90%yieldand39.31MJ/kgformingheat. Harzer2021PhD https://mediatum.ub.tum.de/doc/1634530/1634530.pdf synthesisfigurecorroboratesPSEPVE/alkalihydrolysis/acidconversion. ElectrolyzermembraneEW1100reference:Mechanical Characterization of Electrolyzer Membranes and Components Under Compression,2024 DOI10.1149/1945-7111/ad7a26. Theseareseparatechemistry/referenceproperties,not a measuredcompleteNafionfactory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>APPROVED FINISHED PFSA MEMBRANE REFERENCE, issue90, 2026-10-18. Weber et al.2018 DOI10.1021/acs.est.8b02073 SISec1.2.1/TableS2 describesTFE+SO3-&gt;FDA,HFPoxidationwithNaOCl-&gt;HFPO,FDA+2HFPOadduct,Na2CO3pyrolysistoPSEPVE,polymerization90%yieldand39.31MJ/kgformingheat. Harzer2021PhD https://mediatum.ub.tum.de/doc/1634530/1634530.pdf synthesisfigurecorroboratesPSEPVE/alkalihydrolysis/acidconversion. ElectrolyzermembraneEW1100reference:Mechanical Characterization of Electrolyzer Membranes and Components Under Compression,2024 DOI10.1149/1945-7111/ad7a26. Theseareseparatechemistry/referenceproperties,not a measuredcompleteNafionfactory. Replace16kgTFEmonomerby16kgfinishedunreinforceddryacid-formPFSAperexisting1MWePEMstack. PreserveapprovedPt/Ir/coatingreferencesandlifetimepurchases. UseexplicitbalancednetengineeringchemistrywithEW1100g/molSO3H;n=6.557783744855004TFEbackboneunitsperC7F13O5SHacid-sidechainunit. FDA=C2F4O3SfromTFE+SO3;HFPO=C3F6OfromHFP+NaOCl,HFPfromTFEat1:1mass(rearrangementreference). FDA+2HFPO+Na2CO3-&gt;PSEPVE(C7F14O4S)+2NaF+2CO2;PSEPVE+backboneTFE+2NaOH+HCl-&gt;acidPFSA+NaF+NaCl+H2O. ThisNaOH/HClworkupis anexplicitbalancedengineeringvariant,not a claim ofHarzerKOH/HNO3industrialreagentchoice. Allupstreamintermediateconversionsassumed100%,overallfinishedpolymerretention90%asWeberreference. No2nd90%factoronprecursorinputs. Knownnetingredientsperkgfinished={'TFE': 1.0666093025141414, 'SO3': 0.08086565656565657, 'NaOCl': 0.15038135208080808, 'Na2CO3': 0.10705811975757576, 'NaOH': 0.0808015541010101, 'HCl': 0.03682626262626263};byproducts/reject={'NaCl': 0.17709020993939395, 'NaF': 0.1272368861909091, 'water': 0.018196969696969698, 'CO2': 0.08890707070707071, 'reject_PFSA': 0.11111111111111116}. BuyactualTFE,SO3,NaOCl,Na2CO3,NaOH,HCl,directlyatnetchainfeed;doNOTalsoaddcompleteWebermembranes orunsupportedHFP-&gt;hexafluoroethaneproxy. SaltoutputsNaCl/NaFandstoichiometricwatergotooneaqueouseffluentwith10kgprocesswater/kgfinished (explicitengineeringdilution,1-100kgsensitivity),1000kg/m3densityproxy. Fluoride-specificabatement/isolationanddissolvedsaltfateareunresolved;genericwastewaterisNOTvalidatedNaFdisposal. Polymerrejectgoestoexistingplasticincinerationwithoutcredit;stoichiometricCO2emittedonce.39.31MJ/kgWeberheat isoneaggregateon-sitechemicalsynthesis/filmformingallowance,notaddedagainateachmodeledintermediate;1kWh/kgsiteelectricityassumed. Existingnativeupstreamfeedproductionburdensremainseparate. TestEW1000-1200,finishedretention80-100%,heat20-80MJ/kg,andnonidealintermediateyields;thebalancednetrecipeis a stoichiometricengineeringreferencewithyield,NOTmeasuredindustrialgrosschemicalconsumption. Actualco-monomerpurification,catalysts,solventcirculation,intermediatescrap,PFASemissions,membranewatercontent,reinforcementandlong-termperformancearecoveragegaps. Finished16kgmasskept,notinferredfromfilmthicknessorcellarea. No native/runtime/YAMLorprimary-secondarysharechanges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+        </is>
+      </c>
+      <c r="B645">
+        <v>1</v>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>market for tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="B646">
+        <v>1.0666093025141414</v>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>market for sulfur trioxide</t>
+        </is>
+      </c>
+      <c r="B647">
+        <v>0.08086565656565657</v>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>sulfur trioxide</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>sulfur trioxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>market for sodium hypochlorite, without water, in 15% solution state</t>
+        </is>
+      </c>
+      <c r="B648">
+        <v>0.15038135208080808</v>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>sodium hypochlorite, without water, in 15% solution state</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>sodium hypochlorite, without water, in 15% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>market for soda ash, dense</t>
+        </is>
+      </c>
+      <c r="B649">
+        <v>0.10705811975757576</v>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>soda ash, dense</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>soda ash, dense</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>market for sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+      <c r="B650">
+        <v>0.0808015541010101</v>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>market for hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+      <c r="B651">
+        <v>0.03682626262626263</v>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>market for tap water</t>
+        </is>
+      </c>
+      <c r="B652">
+        <v>10</v>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B653">
+        <v>-0.010322524065827272</v>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>treatment of waste plastic, mixture, municipal incineration</t>
+        </is>
+      </c>
+      <c r="B654">
+        <v>-0.11111111111111116</v>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B655">
+        <v>39.31</v>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B656">
+        <v>1</v>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, fossil</t>
+        </is>
+      </c>
+      <c r="B657">
+        <v>0.08890707070707071</v>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U657"/>
+  <dimension ref="A1:U676"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -16797,7 +16797,9 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>1 MWe Solid Oxide electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years. Produced amount of H2 over 20 years: 3779894.18 kg. Amounts of lanthanum oxide and strontium carbonate are unsure. 
+          <t>APPROVED SOEC INORGANIC GLASS-SEAL REFERENCE, issue91, 2026-10-18. Sun,Xiao,Guo,Hong2010,CeramicsInternational36:821-826,DOI10.1016/j.ceramint.2009.09.045,experimentalBaO-Al2O3-B2O3-SiO2glassfamily:base40BaO/20B2O3/40SiO2mol%,Al2O3replacesB2O3/SiO2atconstant2:1Si/Boxide-moleratio;5mol%Alvariantidentifiedasstable,melting1400-1500Cfor1hour. https://www.sciencedirect.com/science/article/pii/S0272884209003812 . ExistingGerloff2021sealantmass4*6.4kg retained. SiliconepolymerisnotSiO2glassformer. Replacefour6.4kgingredients(Al2O3,B2O3,BaO,silicone)by25.6kgofonefinishedglassreference. Select/reconstruct5mol%Al2O3member:40BaO,5Al2O3,18.333333B2O3,36.666667SiO2mol%;theseareoxideMOLfractions,notweightfractions. Correspondingretainedweightfractions={'BaO': 0.6059001794302946, 'Al2O3': 0.05036460625483175, 'B2O3': 0.12609040016734147, 'SiO2': 0.21764481414753226}. Total25.6kgfinishedsealisinheritedengineeringmass,notmeasuredfromthispublishedglassdesign;sourceTable1fullcompositionwasnotindependentlyrecovered,recipeisexplicitreconstructionfrompublishedseriesdescription. UsingSOFCsealingglassasSOECanalogue doesnotdemonstrateactualstacksealgeometry,thermalcycling,dual-atmospherecompatibilityorleaktightness. PurchaseactualBaO,Al2O3,B2O3,SiO2equivalentsscaledby1/0.95forselected95%melting/formingretention,withmatchedsolidglassreject1/.95-1kg/kgtoexistingmixedhazardoustreatmentproxy;volatilizedB/alkalicomponentsandactualwasteclassificationunresolved.6MJ/kgthermaland1kWh/kgmilling/formingareexplicitengineeringutilityallowancesfor1450Cmelting/quenching,notmeasuredsourceutilities;test3-12MJ/kg,0.2-2kWh/kgand90-100%retention. SilicasandisbulkSiO2purityproxy,nonmetallurgicalaluminaisspecialtyoxideproxy;semiconductorgradepurificationnotclaimed. ExistingapprovedYSZ/YDCchemistryandfutureY/Ce/Zrco-scaling,Ni/La/Sr/Prpurchases,steel,stackreplacementandhydrogenoutputallocationunchanged. Do notreduceentirestackorapplyfuturedensitylearningtosealwithoutsource. No newnative/runtime/YAMLchangesorprimary-secondarycredit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 MWe Solid Oxide electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years. Produced amount of H2 over 20 years: 3779894.18 kg. Amounts of lanthanum oxide and strontium carbonate are unsure. 
 SOEC matched ceramic reference v1. YSZ: 8 mol% Y2O3 among binary oxides; YDC: Ce0.8Y0.2O1.9 (20% Y on cation sites). Gerloff 2021 capacity scaling of the attributed Haefele 2016 component masses, not concentrate mass treated as pure oxide. Mixed Sm/Eu/Gd proxy replaced by stoichiometric Y2O3. See data/metals/soec_ceramic_reference.json for source-access limits, explicit composition/scaling assumptions and remaining whole-stack gaps.</t>
         </is>
       </c>
@@ -17284,14 +17286,18 @@
       <c r="R482"/>
     </row>
     <row r="483" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A483" s="11" t="s">
-        <v>168</v>
+      <c r="A483" s="11" t="inlineStr">
+        <is>
+          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+        </is>
       </c>
       <c r="B483" s="12">
-        <v>6.4</v>
-      </c>
-      <c r="C483" s="11" t="s">
-        <v>169</v>
+        <v>25.6</v>
+      </c>
+      <c r="C483" s="11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D483" s="11" t="s">
         <v>13</v>
@@ -17299,11 +17305,15 @@
       <c r="F483" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G483" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="H483" s="11" t="s">
-        <v>171</v>
+      <c r="G483" s="11" t="inlineStr">
+        <is>
+          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+        </is>
+      </c>
+      <c r="H483" s="11" t="inlineStr">
+        <is>
+          <t>APPROVED SOEC INORGANIC GLASS-SEAL REFERENCE, issue91, 2026-10-18. Sun,Xiao,Guo,Hong2010,CeramicsInternational36:821-826,DOI10.1016/j.ceramint.2009.09.045,experimentalBaO-Al2O3-B2O3-SiO2glassfamily:base40BaO/20B2O3/40SiO2mol%,Al2O3replacesB2O3/SiO2atconstant2:1Si/Boxide-moleratio;5mol%Alvariantidentifiedasstable,melting1400-1500Cfor1hour. https://www.sciencedirect.com/science/article/pii/S0272884209003812 . ExistingGerloff2021sealantmass4*6.4kg retained. SiliconepolymerisnotSiO2glassformer. Replacefour6.4kgingredients(Al2O3,B2O3,BaO,silicone)by25.6kgofonefinishedglassreference. Select/reconstruct5mol%Al2O3member:40BaO,5Al2O3,18.333333B2O3,36.666667SiO2mol%;theseareoxideMOLfractions,notweightfractions. Correspondingretainedweightfractions={'BaO': 0.6059001794302946, 'Al2O3': 0.05036460625483175, 'B2O3': 0.12609040016734147, 'SiO2': 0.21764481414753226}. Total25.6kgfinishedsealisinheritedengineeringmass,notmeasuredfromthispublishedglassdesign;sourceTable1fullcompositionwasnotindependentlyrecovered,recipeisexplicitreconstructionfrompublishedseriesdescription. UsingSOFCsealingglassasSOECanalogue doesnotdemonstrateactualstacksealgeometry,thermalcycling,dual-atmospherecompatibilityorleaktightness. PurchaseactualBaO,Al2O3,B2O3,SiO2equivalentsscaledby1/0.95forselected95%melting/formingretention,withmatchedsolidglassreject1/.95-1kg/kgtoexistingmixedhazardoustreatmentproxy;volatilizedB/alkalicomponentsandactualwasteclassificationunresolved.6MJ/kgthermaland1kWh/kgmilling/formingareexplicitengineeringutilityallowancesfor1450Cmelting/quenching,notmeasuredsourceutilities;test3-12MJ/kg,0.2-2kWh/kgand90-100%retention. SilicasandisbulkSiO2purityproxy,nonmetallurgicalaluminaisspecialtyoxideproxy;semiconductorgradepurificationnotclaimed. ExistingapprovedYSZ/YDCchemistryandfutureY/Ce/Zrco-scaling,Ni/La/Sr/Prpurchases,steel,stackreplacementandhydrogenoutputallocationunchanged. Do notreduceentirestackorapplyfuturedensitylearningtosealwithoutsource. No newnative/runtime/YAMLchangesorprimary-secondarycredit.</t>
+        </is>
       </c>
       <c r="J483"/>
       <c r="K483" s="19"/>
@@ -17316,27 +17326,13 @@
       <c r="R483"/>
     </row>
     <row r="484" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A484" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B484" s="12">
-        <v>6.4</v>
-      </c>
-      <c r="C484" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D484" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F484" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G484" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="H484" s="11" t="s">
-        <v>171</v>
-      </c>
+      <c r="A484" s="11"/>
+      <c r="B484" s="12"/>
+      <c r="C484" s="11"/>
+      <c r="D484" s="11"/>
+      <c r="F484" s="11"/>
+      <c r="G484" s="11"/>
+      <c r="H484" s="11"/>
       <c r="J484"/>
       <c r="K484" s="19"/>
       <c r="L484" s="19"/>
@@ -17348,27 +17344,13 @@
       <c r="R484"/>
     </row>
     <row r="485" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A485" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B485" s="12">
-        <v>6.4</v>
-      </c>
-      <c r="C485" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D485" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F485" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G485" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="H485" s="11" t="s">
-        <v>171</v>
-      </c>
+      <c r="A485" s="11"/>
+      <c r="B485" s="12"/>
+      <c r="C485" s="11"/>
+      <c r="D485" s="11"/>
+      <c r="F485" s="11"/>
+      <c r="G485" s="11"/>
+      <c r="H485" s="11"/>
       <c r="J485"/>
       <c r="K485" s="19"/>
       <c r="L485" s="19"/>
@@ -17380,27 +17362,13 @@
       <c r="R485"/>
     </row>
     <row r="486" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A486" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="B486" s="12">
-        <v>6.4</v>
-      </c>
-      <c r="C486" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D486" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F486" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G486" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="H486" s="11" t="s">
-        <v>171</v>
-      </c>
+      <c r="A486" s="11"/>
+      <c r="B486" s="12"/>
+      <c r="C486" s="11"/>
+      <c r="D486" s="11"/>
+      <c r="F486" s="11"/>
+      <c r="G486" s="11"/>
+      <c r="H486" s="11"/>
       <c r="J486"/>
       <c r="K486" s="19"/>
       <c r="L486" s="19"/>
@@ -21958,6 +21926,422 @@
       <c r="H657" t="inlineStr">
         <is>
           <t/>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B662">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Sun,Xiao,Guo,Hong2010,CeramicsInternational36:821-826,DOI10.1016/j.ceramint.2009.09.045,experimentalBaO-Al2O3-B2O3-SiO2glassfamily:base40BaO/20B2O3/40SiO2mol%,Al2O3replacesB2O3/SiO2atconstant2:1Si/Boxide-moleratio;5mol%Alvariantidentifiedasstable,melting1400-1500Cfor1hour. https://www.sciencedirect.com/science/article/pii/S0272884209003812 . ExistingGerloff2021sealantmass4*6.4kg retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>APPROVED SOEC INORGANIC GLASS-SEAL REFERENCE, issue91, 2026-10-18. Sun,Xiao,Guo,Hong2010,CeramicsInternational36:821-826,DOI10.1016/j.ceramint.2009.09.045,experimentalBaO-Al2O3-B2O3-SiO2glassfamily:base40BaO/20B2O3/40SiO2mol%,Al2O3replacesB2O3/SiO2atconstant2:1Si/Boxide-moleratio;5mol%Alvariantidentifiedasstable,melting1400-1500Cfor1hour. https://www.sciencedirect.com/science/article/pii/S0272884209003812 . ExistingGerloff2021sealantmass4*6.4kg retained. SiliconepolymerisnotSiO2glassformer. Replacefour6.4kgingredients(Al2O3,B2O3,BaO,silicone)by25.6kgofonefinishedglassreference. Select/reconstruct5mol%Al2O3member:40BaO,5Al2O3,18.333333B2O3,36.666667SiO2mol%;theseareoxideMOLfractions,notweightfractions. Correspondingretainedweightfractions={'BaO': 0.6059001794302946, 'Al2O3': 0.05036460625483175, 'B2O3': 0.12609040016734147, 'SiO2': 0.21764481414753226}. Total25.6kgfinishedsealisinheritedengineeringmass,notmeasuredfromthispublishedglassdesign;sourceTable1fullcompositionwasnotindependentlyrecovered,recipeisexplicitreconstructionfrompublishedseriesdescription. UsingSOFCsealingglassasSOECanalogue doesnotdemonstrateactualstacksealgeometry,thermalcycling,dual-atmospherecompatibilityorleaktightness. PurchaseactualBaO,Al2O3,B2O3,SiO2equivalentsscaledby1/0.95forselected95%melting/formingretention,withmatchedsolidglassreject1/.95-1kg/kgtoexistingmixedhazardoustreatmentproxy;volatilizedB/alkalicomponentsandactualwasteclassificationunresolved.6MJ/kgthermaland1kWh/kgmilling/formingareexplicitengineeringutilityallowancesfor1450Cmelting/quenching,notmeasuredsourceutilities;test3-12MJ/kg,0.2-2kWh/kgand90-100%retention. SilicasandisbulkSiO2purityproxy,nonmetallurgicalaluminaisspecialtyoxideproxy;semiconductorgradepurificationnotclaimed. ExistingapprovedYSZ/YDCchemistryandfutureY/Ce/Zrco-scaling,Ni/La/Sr/Prpurchases,steel,stackreplacementandhydrogenoutputallocationunchanged. Do notreduceentirestackorapplyfuturedensitylearningtosealwithoutsource. No newnative/runtime/YAMLchangesorprimary-secondarycredit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+        </is>
+      </c>
+      <c r="B669">
+        <v>1</v>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>market for barium oxide</t>
+        </is>
+      </c>
+      <c r="B670">
+        <v>0.6377896625582049</v>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>barium oxide</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>barium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>market for aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="B671">
+        <v>0.05301537500508606</v>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>market for boric oxide</t>
+        </is>
+      </c>
+      <c r="B672">
+        <v>0.1327267370182542</v>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>boric oxide</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>boric oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B673">
+        <v>0.22909980436582345</v>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B674">
+        <v>6</v>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B675">
+        <v>1</v>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B676">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -9237,8 +9237,12 @@
       <c r="A204" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B204" s="14" t="s">
-        <v>81</v>
+      <c r="B204" s="14" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 MW PEM electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years per single stack, @ 8000 hours/year. Iridium mining process is NOT from ecoinvent. Produced amount of H2 over 20 years: 2964315.35 kg. According to a study called IndWEDe, it is assumed that the stacks are replaced 3 times during the 20 years lifespan, based on the 2030’s scenario for 1 MW systems which predicts a lifetime of 50,000 h or more for the stacks of the different water electrolysis technologies. In comparison to AEC electrolyzers, PEMEC electrolyzers are less mature. Furthermore, the PEMEC technology is commercially available and operates with a similar system efficiency as the AEC technology. However, the current density and the gas purity are higher with values in between 0.6-2.0 A/cm2 and &gt; 99.99%, respectively. Besides this, the operating pressure (below 200 bar) is significantly higher in comparison to AEC systems, while the operating temperature (50 °C to 80 °C) and the system energy (4.2-6.6 kWh/m3H2) are similar to AEC systems. The PEMEC BoP and stack components data stem from Bareiß et al. and correspond to a 1 MW system. Moreover, some further BoP components like water purifier &amp; feed tank, buffer tank, and heat exchanger have been added, derived from a 300 kW AEC system, under the assumption that the components are also suitable for a PEMEC system. The values have been scaled up from 300 kW to 1 MW.</t>
+        </is>
       </c>
       <c r="K204" s="12"/>
       <c r="L204" s="25"/>
@@ -9621,8 +9625,10 @@
       <c r="G218" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H218" s="10" t="s">
-        <v>87</v>
+      <c r="H218" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.</t>
+        </is>
       </c>
       <c r="J218"/>
       <c r="K218" s="19"/>
@@ -12854,8 +12860,12 @@
       <c r="A334" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B334" s="14" t="s">
-        <v>139</v>
+      <c r="B334" s="14" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 MWe Alkaline electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Single stack lifetime of 7-8 years @ 8000 hours/year, hence 3 replacements over 20 years. Produced amount of H2 over 20 years: 3085961.12 kg. The technology is available for large plant sizes and operates with a stack efficiency of up to 67 % (based on the lower heating value (LHV) of the generated H2). The operating temperature is in between 60–80 °C, and the current density is around 0.2–0.4 A/cm2. Moreover, the system energy –including the stack and periphery energy– is in the range of 4.4–6.6 kWh/m3H2, while the gas purity is higher than 99.5%, and the operating pressure is below 30 bar. While the LCI data of the BoP components either originate from Zhang et al., based on a 300-kW system and, therefore, scaled-up to 1 MW by a factor of 0.7, the LCI data of the other BoP components originate from manufacturer offers or have been estimated by own calculations using additional information by the producers.</t>
+        </is>
       </c>
       <c r="K334" s="12"/>
       <c r="L334" s="25"/>
@@ -13239,8 +13249,10 @@
       <c r="G348" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H348" s="10" t="s">
-        <v>87</v>
+      <c r="H348" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.</t>
+        </is>
       </c>
       <c r="J348"/>
       <c r="K348" s="19"/>
@@ -17696,8 +17708,12 @@
       <c r="A503" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B503" s="14" t="s">
-        <v>180</v>
+      <c r="B503" s="14" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 MWe Solid Oxide electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years. Produced amount of H2 over 20 years: 3779894.18 kg.</t>
+        </is>
       </c>
       <c r="K503" s="12"/>
       <c r="L503" s="25"/>
@@ -18638,8 +18654,10 @@
       <c r="G534" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H534" s="10" t="s">
-        <v>186</v>
+      <c r="H534" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.</t>
+        </is>
       </c>
       <c r="J534"/>
       <c r="K534" s="19"/>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U676"/>
+  <dimension ref="A1:U824"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -9239,7 +9239,9 @@
       </c>
       <c r="B204" s="14" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 1 MW PEM electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years per single stack, @ 8000 hours/year. Iridium mining process is NOT from ecoinvent. Produced amount of H2 over 20 years: 2964315.35 kg. According to a study called IndWEDe, it is assumed that the stacks are replaced 3 times during the 20 years lifespan, based on the 2030’s scenario for 1 MW systems which predicts a lifetime of 50,000 h or more for the stacks of the different water electrolysis technologies. In comparison to AEC electrolyzers, PEMEC electrolyzers are less mature. Furthermore, the PEMEC technology is commercially available and operates with a similar system efficiency as the AEC technology. However, the current density and the gas purity are higher with values in between 0.6-2.0 A/cm2 and &gt; 99.99%, respectively. Besides this, the operating pressure (below 200 bar) is significantly higher in comparison to AEC systems, while the operating temperature (50 °C to 80 °C) and the system energy (4.2-6.6 kWh/m3H2) are similar to AEC systems. The PEMEC BoP and stack components data stem from Bareiß et al. and correspond to a 1 MW system. Moreover, some further BoP components like water purifier &amp; feed tank, buffer tank, and heat exchanger have been added, derived from a 300 kW AEC system, under the assumption that the components are also suitable for a PEMEC system. The values have been scaled up from 300 kW to 1 MW.</t>
         </is>
@@ -9383,26 +9385,36 @@
       <c r="P210" s="26"/>
     </row>
     <row r="211" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A211" s="11" t="s">
-        <v>18</v>
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+        </is>
       </c>
       <c r="B211" s="16">
-        <v>100</v>
-      </c>
-      <c r="C211" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D211" s="11" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="C211" s="11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D211" s="11" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="F211" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G211" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H211" s="27" t="s">
-        <v>82</v>
+      <c r="G211" s="11" t="inlineStr">
+        <is>
+          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+        </is>
+      </c>
+      <c r="H211" s="27" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J211"/>
       <c r="K211" s="19"/>
@@ -9415,27 +9427,13 @@
       <c r="R211"/>
     </row>
     <row r="212" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A212" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B212" s="16">
-        <v>200</v>
-      </c>
-      <c r="C212" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D212" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F212" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G212" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H212" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="A212" s="11"/>
+      <c r="B212" s="16"/>
+      <c r="C212" s="11"/>
+      <c r="D212" s="11"/>
+      <c r="F212" s="11"/>
+      <c r="G212" s="11"/>
+      <c r="H212" s="27"/>
       <c r="J212"/>
       <c r="K212" s="19"/>
       <c r="L212" s="19"/>
@@ -9447,27 +9445,13 @@
       <c r="R212"/>
     </row>
     <row r="213" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A213" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B213" s="16">
-        <v>600</v>
-      </c>
-      <c r="C213" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D213" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F213" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G213" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H213" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="A213" s="11"/>
+      <c r="B213" s="16"/>
+      <c r="C213" s="11"/>
+      <c r="D213" s="11"/>
+      <c r="F213" s="11"/>
+      <c r="G213" s="11"/>
+      <c r="H213" s="27"/>
       <c r="J213"/>
       <c r="K213" s="19"/>
       <c r="L213" s="19"/>
@@ -9479,27 +9463,13 @@
       <c r="R213"/>
     </row>
     <row r="214" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A214" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B214" s="16">
-        <v>100</v>
-      </c>
-      <c r="C214" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D214" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F214" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G214" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="H214" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="A214" s="11"/>
+      <c r="B214" s="16"/>
+      <c r="C214" s="11"/>
+      <c r="D214" s="11"/>
+      <c r="F214" s="11"/>
+      <c r="G214" s="11"/>
+      <c r="H214" s="27"/>
       <c r="J214"/>
       <c r="K214" s="19"/>
       <c r="L214" s="19"/>
@@ -9511,27 +9481,13 @@
       <c r="R214"/>
     </row>
     <row r="215" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A215" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B215" s="16">
-        <v>600</v>
-      </c>
-      <c r="C215" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D215" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F215" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G215" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H215" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="A215" s="11"/>
+      <c r="B215" s="16"/>
+      <c r="C215" s="11"/>
+      <c r="D215" s="11"/>
+      <c r="F215" s="11"/>
+      <c r="G215" s="11"/>
+      <c r="H215" s="27"/>
       <c r="J215"/>
       <c r="K215" s="19"/>
       <c r="L215" s="19"/>
@@ -9543,27 +9499,13 @@
       <c r="R215"/>
     </row>
     <row r="216" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A216" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B216" s="16">
-        <v>100</v>
-      </c>
-      <c r="C216" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D216" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F216" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G216" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="H216" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="A216" s="11"/>
+      <c r="B216" s="16"/>
+      <c r="C216" s="11"/>
+      <c r="D216" s="11"/>
+      <c r="F216" s="11"/>
+      <c r="G216" s="11"/>
+      <c r="H216" s="27"/>
       <c r="J216"/>
       <c r="K216" s="19"/>
       <c r="L216" s="19"/>
@@ -9575,27 +9517,13 @@
       <c r="R216"/>
     </row>
     <row r="217" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A217" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B217" s="16">
-        <v>200</v>
-      </c>
-      <c r="C217" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D217" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F217" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G217" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="H217" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="A217" s="11"/>
+      <c r="B217" s="16"/>
+      <c r="C217" s="11"/>
+      <c r="D217" s="11"/>
+      <c r="F217" s="11"/>
+      <c r="G217" s="11"/>
+      <c r="H217" s="27"/>
       <c r="J217"/>
       <c r="K217" s="19"/>
       <c r="L217" s="19"/>
@@ -10961,8 +10889,12 @@
       <c r="A262" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B262" s="14" t="s">
-        <v>56</v>
+      <c r="B262" s="14" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 MW PEM electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years per single stack, @ 8000 hours/year. Iridium mining process is NOT from ecoinvent. Produced amount of H2 over 20 years: 2964315.35 kg. According to a study called IndWEDe, it is assumed that the stacks are replaced 3 times during the 20 years lifespan, based on the 2030’s scenario for 1 MW systems which predicts a lifetime of 50,000 h or more for the stacks of the different water electrolysis technologies. In comparison to AEC electrolyzers, PEMEC electrolyzers are less mature. Furthermore, the PEMEC technology is commercially available and operates with a similar system efficiency as the AEC technology. However, the current density and the gas purity are higher with values in between 0.6–2.0 A/cm2 and &gt; 99.99%, respectively. Besides this, the operating pressure (below 200 bar) is significantly higher in comparison to AEC systems, while the operating temperature (50 °C to 80 °C) and the system energy (4.2–6.6 kWh/m3H2) are similar to AEC systems. The PEMEC BoP and stack components data stem from Bareiß et al. and correspond to a 1 MW system. Moreover, some further BoP components like water purifier &amp; feed tank, buffer tank, and heat exchanger have been added, derived from a 300 kW AEC system, under the assumption that the components are also suitable for a PEMEC system. The values have been scaled up from 300 kW to 1 MW. Values have already been multiplied by 3 to reflect 2 stack replacements over 20 years of use.</t>
+        </is>
       </c>
       <c r="K262" s="12"/>
       <c r="L262" s="12"/>
@@ -11135,7 +11067,7 @@
         <v>449</v>
       </c>
       <c r="B270" s="11">
-        <v>-3312</v>
+        <v>-2712</v>
       </c>
       <c r="C270" s="11" t="s">
         <v>217</v>
@@ -11148,6 +11080,11 @@
       </c>
       <c r="G270" s="16" t="s">
         <v>216</v>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J270"/>
       <c r="K270" s="19"/>
@@ -11164,7 +11101,7 @@
         <v>206</v>
       </c>
       <c r="B271" s="11">
-        <v>-260</v>
+        <v>-160</v>
       </c>
       <c r="C271" s="11" t="s">
         <v>37</v>
@@ -11177,6 +11114,11 @@
       </c>
       <c r="G271" s="11" t="s">
         <v>207</v>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J271"/>
       <c r="K271" s="19"/>
@@ -11338,7 +11280,7 @@
         <v>208</v>
       </c>
       <c r="B277" s="11">
-        <v>-345</v>
+        <v>-145</v>
       </c>
       <c r="C277" s="11" t="s">
         <v>37</v>
@@ -11351,6 +11293,11 @@
       </c>
       <c r="G277" s="11" t="s">
         <v>209</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J277"/>
       <c r="K277" s="19"/>
@@ -11367,7 +11314,7 @@
         <v>210</v>
       </c>
       <c r="B278" s="11">
-        <v>-147</v>
+        <v>-47</v>
       </c>
       <c r="C278" s="11" t="s">
         <v>212</v>
@@ -11380,6 +11327,11 @@
       </c>
       <c r="G278" s="11" t="s">
         <v>211</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J278"/>
       <c r="K278" s="19"/>
@@ -11450,7 +11402,39 @@
       <c r="R280"/>
     </row>
     <row r="281" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B281" s="16"/>
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="B281" s="16">
+        <v>-1</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
+      </c>
       <c r="K281" s="12"/>
       <c r="L281" s="12"/>
       <c r="M281" s="12"/>
@@ -12862,7 +12846,9 @@
       </c>
       <c r="B334" s="14" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 1 MWe Alkaline electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Single stack lifetime of 7-8 years @ 8000 hours/year, hence 3 replacements over 20 years. Produced amount of H2 over 20 years: 3085961.12 kg. The technology is available for large plant sizes and operates with a stack efficiency of up to 67 % (based on the lower heating value (LHV) of the generated H2). The operating temperature is in between 60–80 °C, and the current density is around 0.2–0.4 A/cm2. Moreover, the system energy –including the stack and periphery energy– is in the range of 4.4–6.6 kWh/m3H2, while the gas purity is higher than 99.5%, and the operating pressure is below 30 bar. While the LCI data of the BoP components either originate from Zhang et al., based on a 300-kW system and, therefore, scaled-up to 1 MW by a factor of 0.7, the LCI data of the other BoP components originate from manufacturer offers or have been estimated by own calculations using additional information by the producers.</t>
         </is>
@@ -13007,26 +12993,36 @@
       <c r="P340" s="12"/>
     </row>
     <row r="341" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A341" s="11" t="s">
-        <v>18</v>
+      <c r="A341" s="11" t="inlineStr">
+        <is>
+          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+        </is>
       </c>
       <c r="B341" s="16">
-        <v>100</v>
-      </c>
-      <c r="C341" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D341" s="11" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="C341" s="11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D341" s="11" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="F341" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G341" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H341" s="27" t="s">
-        <v>82</v>
+      <c r="G341" s="11" t="inlineStr">
+        <is>
+          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+        </is>
+      </c>
+      <c r="H341" s="27" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J341"/>
       <c r="K341" s="19"/>
@@ -13039,27 +13035,13 @@
       <c r="R341"/>
     </row>
     <row r="342" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A342" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B342" s="16">
-        <v>200</v>
-      </c>
-      <c r="C342" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D342" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F342" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G342" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H342" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="A342" s="11"/>
+      <c r="B342" s="16"/>
+      <c r="C342" s="11"/>
+      <c r="D342" s="11"/>
+      <c r="F342" s="11"/>
+      <c r="G342" s="11"/>
+      <c r="H342" s="27"/>
       <c r="J342"/>
       <c r="K342" s="19"/>
       <c r="L342" s="19"/>
@@ -13071,27 +13053,13 @@
       <c r="R342"/>
     </row>
     <row r="343" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A343" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B343" s="16">
-        <v>600</v>
-      </c>
-      <c r="C343" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D343" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F343" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G343" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H343" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="A343" s="11"/>
+      <c r="B343" s="16"/>
+      <c r="C343" s="11"/>
+      <c r="D343" s="11"/>
+      <c r="F343" s="11"/>
+      <c r="G343" s="11"/>
+      <c r="H343" s="27"/>
       <c r="J343"/>
       <c r="K343" s="19"/>
       <c r="L343" s="19"/>
@@ -13103,27 +13071,13 @@
       <c r="R343"/>
     </row>
     <row r="344" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A344" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B344" s="16">
-        <v>100</v>
-      </c>
-      <c r="C344" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D344" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F344" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G344" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="H344" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="A344" s="11"/>
+      <c r="B344" s="16"/>
+      <c r="C344" s="11"/>
+      <c r="D344" s="11"/>
+      <c r="F344" s="11"/>
+      <c r="G344" s="11"/>
+      <c r="H344" s="27"/>
       <c r="J344"/>
       <c r="K344" s="19"/>
       <c r="L344" s="19"/>
@@ -13135,27 +13089,13 @@
       <c r="R344"/>
     </row>
     <row r="345" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A345" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B345" s="16">
-        <v>600</v>
-      </c>
-      <c r="C345" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D345" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F345" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G345" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H345" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="A345" s="11"/>
+      <c r="B345" s="16"/>
+      <c r="C345" s="11"/>
+      <c r="D345" s="11"/>
+      <c r="F345" s="11"/>
+      <c r="G345" s="11"/>
+      <c r="H345" s="27"/>
       <c r="J345"/>
       <c r="K345" s="19"/>
       <c r="L345" s="19"/>
@@ -13167,27 +13107,13 @@
       <c r="R345"/>
     </row>
     <row r="346" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A346" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B346" s="16">
-        <v>100</v>
-      </c>
-      <c r="C346" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D346" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F346" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G346" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="H346" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="A346" s="11"/>
+      <c r="B346" s="16"/>
+      <c r="C346" s="11"/>
+      <c r="D346" s="11"/>
+      <c r="F346" s="11"/>
+      <c r="G346" s="11"/>
+      <c r="H346" s="27"/>
       <c r="J346"/>
       <c r="K346" s="19"/>
       <c r="L346" s="19"/>
@@ -13199,27 +13125,13 @@
       <c r="R346"/>
     </row>
     <row r="347" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A347" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B347" s="16">
-        <v>200</v>
-      </c>
-      <c r="C347" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D347" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F347" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G347" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="H347" s="27" t="s">
-        <v>82</v>
-      </c>
+      <c r="A347" s="11"/>
+      <c r="B347" s="16"/>
+      <c r="C347" s="11"/>
+      <c r="D347" s="11"/>
+      <c r="F347" s="11"/>
+      <c r="G347" s="11"/>
+      <c r="H347" s="27"/>
       <c r="J347"/>
       <c r="K347" s="19"/>
       <c r="L347" s="19"/>
@@ -14942,8 +14854,12 @@
       <c r="A403" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B403" s="14" t="s">
-        <v>56</v>
+      <c r="B403" s="14" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 MW PEM electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years per single stack, @ 8000 hours/year. Iridium mining process is NOT from ecoinvent. Produced amount of H2 over 20 years: 2964315.35 kg. According to a study called IndWEDe, it is assumed that the stacks are replaced 3 times during the 20 years lifespan, based on the 2030’s scenario for 1 MW systems which predicts a lifetime of 50,000 h or more for the stacks of the different water electrolysis technologies. In comparison to AEC electrolyzers, PEMEC electrolyzers are less mature. Furthermore, the PEMEC technology is commercially available and operates with a similar system efficiency as the AEC technology. However, the current density and the gas purity are higher with values in between 0.6–2.0 A/cm2 and &gt; 99.99%, respectively. Besides this, the operating pressure (below 200 bar) is significantly higher in comparison to AEC systems, while the operating temperature (50 °C to 80 °C) and the system energy (4.2–6.6 kWh/m3H2) are similar to AEC systems. The PEMEC BoP and stack components data stem from Bareiß et al. and correspond to a 1 MW system. Moreover, some further BoP components like water purifier &amp; feed tank, buffer tank, and heat exchanger have been added, derived from a 300 kW AEC system, under the assumption that the components are also suitable for a PEMEC system. The values have been scaled up from 300 kW to 1 MW. Values have already been multiplied by 3 to reflect 2 stack replacements over 20 years of use.</t>
+        </is>
       </c>
       <c r="K403" s="12"/>
       <c r="L403" s="12"/>
@@ -15115,7 +15031,7 @@
         <v>449</v>
       </c>
       <c r="B411" s="11">
-        <v>-5134.3999999999996</v>
+        <v>-4534.4</v>
       </c>
       <c r="C411" s="11" t="s">
         <v>217</v>
@@ -15128,6 +15044,11 @@
       </c>
       <c r="G411" s="16" t="s">
         <v>216</v>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J411"/>
       <c r="K411" s="19"/>
@@ -15144,7 +15065,7 @@
         <v>206</v>
       </c>
       <c r="B412" s="11">
-        <v>-160</v>
+        <v>-60</v>
       </c>
       <c r="C412" s="11" t="s">
         <v>37</v>
@@ -15157,6 +15078,11 @@
       </c>
       <c r="G412" s="11" t="s">
         <v>207</v>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J412"/>
       <c r="K412" s="19"/>
@@ -15318,7 +15244,7 @@
         <v>208</v>
       </c>
       <c r="B418" s="11">
-        <v>-617</v>
+        <v>-417</v>
       </c>
       <c r="C418" s="11" t="s">
         <v>37</v>
@@ -15331,6 +15257,11 @@
       </c>
       <c r="G418" s="11" t="s">
         <v>209</v>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J418"/>
       <c r="K418" s="19"/>
@@ -15347,7 +15278,7 @@
         <v>210</v>
       </c>
       <c r="B419" s="11">
-        <v>-208</v>
+        <v>-108</v>
       </c>
       <c r="C419" s="11" t="s">
         <v>212</v>
@@ -15360,6 +15291,11 @@
       </c>
       <c r="G419" s="11" t="s">
         <v>211</v>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J419"/>
       <c r="K419" s="19"/>
@@ -15401,7 +15337,39 @@
       <c r="R420"/>
     </row>
     <row r="421" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B421" s="16"/>
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="B421" s="16">
+        <v>-1</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
+      </c>
       <c r="K421" s="12"/>
       <c r="L421" s="12"/>
       <c r="M421" s="12"/>
@@ -17710,7 +17678,9 @@
       </c>
       <c r="B503" s="14" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 1 MWe Solid Oxide electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years. Produced amount of H2 over 20 years: 3779894.18 kg.</t>
         </is>
@@ -18412,26 +18382,36 @@
       <c r="R526"/>
     </row>
     <row r="527" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A527" s="16" t="s">
-        <v>18</v>
+      <c r="A527" s="16" t="inlineStr">
+        <is>
+          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+        </is>
       </c>
       <c r="B527" s="16">
-        <v>100</v>
-      </c>
-      <c r="C527" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D527" s="11" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="C527" s="11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D527" s="11" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="F527" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G527" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H527" s="10" t="s">
-        <v>185</v>
+      <c r="G527" s="16" t="inlineStr">
+        <is>
+          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+        </is>
+      </c>
+      <c r="H527" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J527"/>
       <c r="K527" s="19"/>
@@ -18444,27 +18424,13 @@
       <c r="R527"/>
     </row>
     <row r="528" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A528" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B528" s="16">
-        <v>200</v>
-      </c>
-      <c r="C528" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D528" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F528" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G528" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="H528" s="10" t="s">
-        <v>185</v>
-      </c>
+      <c r="A528" s="16"/>
+      <c r="B528" s="16"/>
+      <c r="C528" s="11"/>
+      <c r="D528" s="11"/>
+      <c r="F528" s="11"/>
+      <c r="G528" s="16"/>
+      <c r="H528" s="10"/>
       <c r="J528"/>
       <c r="K528" s="19"/>
       <c r="L528" s="19"/>
@@ -18476,27 +18442,13 @@
       <c r="R528"/>
     </row>
     <row r="529" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A529" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B529" s="16">
-        <v>600</v>
-      </c>
-      <c r="C529" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D529" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F529" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G529" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H529" s="10" t="s">
-        <v>185</v>
-      </c>
+      <c r="A529" s="16"/>
+      <c r="B529" s="16"/>
+      <c r="C529" s="11"/>
+      <c r="D529" s="11"/>
+      <c r="F529" s="11"/>
+      <c r="G529" s="16"/>
+      <c r="H529" s="10"/>
       <c r="J529"/>
       <c r="K529" s="19"/>
       <c r="L529" s="19"/>
@@ -18508,27 +18460,13 @@
       <c r="R529"/>
     </row>
     <row r="530" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A530" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B530" s="16">
-        <v>100</v>
-      </c>
-      <c r="C530" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D530" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F530" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G530" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="H530" s="10" t="s">
-        <v>185</v>
-      </c>
+      <c r="A530" s="16"/>
+      <c r="B530" s="16"/>
+      <c r="C530" s="11"/>
+      <c r="D530" s="11"/>
+      <c r="F530" s="11"/>
+      <c r="G530" s="16"/>
+      <c r="H530" s="10"/>
       <c r="J530"/>
       <c r="K530" s="19"/>
       <c r="L530" s="19"/>
@@ -18540,27 +18478,13 @@
       <c r="R530"/>
     </row>
     <row r="531" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A531" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B531" s="16">
-        <v>600</v>
-      </c>
-      <c r="C531" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D531" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F531" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G531" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H531" s="10" t="s">
-        <v>185</v>
-      </c>
+      <c r="A531" s="16"/>
+      <c r="B531" s="16"/>
+      <c r="C531" s="11"/>
+      <c r="D531" s="11"/>
+      <c r="F531" s="11"/>
+      <c r="G531" s="16"/>
+      <c r="H531" s="10"/>
       <c r="J531"/>
       <c r="K531" s="19"/>
       <c r="L531" s="19"/>
@@ -18572,27 +18496,13 @@
       <c r="R531"/>
     </row>
     <row r="532" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A532" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B532" s="16">
-        <v>100</v>
-      </c>
-      <c r="C532" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D532" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F532" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G532" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="H532" s="10" t="s">
-        <v>185</v>
-      </c>
+      <c r="A532" s="16"/>
+      <c r="B532" s="16"/>
+      <c r="C532" s="11"/>
+      <c r="D532" s="11"/>
+      <c r="F532" s="11"/>
+      <c r="G532" s="16"/>
+      <c r="H532" s="10"/>
       <c r="J532"/>
       <c r="K532" s="19"/>
       <c r="L532" s="19"/>
@@ -18604,27 +18514,13 @@
       <c r="R532"/>
     </row>
     <row r="533" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A533" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B533" s="16">
-        <v>200</v>
-      </c>
-      <c r="C533" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D533" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F533" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G533" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="H533" s="10" t="s">
-        <v>185</v>
-      </c>
+      <c r="A533" s="16"/>
+      <c r="B533" s="16"/>
+      <c r="C533" s="11"/>
+      <c r="D533" s="11"/>
+      <c r="F533" s="11"/>
+      <c r="G533" s="16"/>
+      <c r="H533" s="10"/>
       <c r="J533"/>
       <c r="K533" s="19"/>
       <c r="L533" s="19"/>
@@ -19975,8 +19871,12 @@
       <c r="A577" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B577" s="14" t="s">
-        <v>56</v>
+      <c r="B577" s="14" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 MW PEM electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years per single stack, @ 8000 hours/year. Iridium mining process is NOT from ecoinvent. Produced amount of H2 over 20 years: 2964315.35 kg. According to a study called IndWEDe, it is assumed that the stacks are replaced 3 times during the 20 years lifespan, based on the 2030’s scenario for 1 MW systems which predicts a lifetime of 50,000 h or more for the stacks of the different water electrolysis technologies. In comparison to AEC electrolyzers, PEMEC electrolyzers are less mature. Furthermore, the PEMEC technology is commercially available and operates with a similar system efficiency as the AEC technology. However, the current density and the gas purity are higher with values in between 0.6–2.0 A/cm2 and &gt; 99.99%, respectively. Besides this, the operating pressure (below 200 bar) is significantly higher in comparison to AEC systems, while the operating temperature (50 °C to 80 °C) and the system energy (4.2–6.6 kWh/m3H2) are similar to AEC systems. The PEMEC BoP and stack components data stem from Bareiß et al. and correspond to a 1 MW system. Moreover, some further BoP components like water purifier &amp; feed tank, buffer tank, and heat exchanger have been added, derived from a 300 kW AEC system, under the assumption that the components are also suitable for a PEMEC system. The values have been scaled up from 300 kW to 1 MW. Values have already been multiplied by 3 to reflect 2 stack replacements over 20 years of use.</t>
+        </is>
       </c>
       <c r="K577" s="12"/>
       <c r="L577" s="12"/>
@@ -20148,7 +20048,7 @@
         <v>449</v>
       </c>
       <c r="B585" s="11">
-        <v>-13730</v>
+        <v>-13130</v>
       </c>
       <c r="C585" s="11" t="s">
         <v>217</v>
@@ -20161,6 +20061,11 @@
       </c>
       <c r="G585" s="16" t="s">
         <v>216</v>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J585"/>
       <c r="K585" s="19"/>
@@ -20177,7 +20082,7 @@
         <v>206</v>
       </c>
       <c r="B586" s="11">
-        <v>-401</v>
+        <v>-301</v>
       </c>
       <c r="C586" s="11" t="s">
         <v>37</v>
@@ -20190,6 +20095,11 @@
       </c>
       <c r="G586" s="11" t="s">
         <v>207</v>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J586"/>
       <c r="K586" s="19"/>
@@ -20351,7 +20261,7 @@
         <v>208</v>
       </c>
       <c r="B592" s="11">
-        <v>-429</v>
+        <v>-229</v>
       </c>
       <c r="C592" s="11" t="s">
         <v>37</v>
@@ -20364,6 +20274,11 @@
       </c>
       <c r="G592" s="11" t="s">
         <v>209</v>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J592"/>
       <c r="K592" s="19"/>
@@ -20380,7 +20295,7 @@
         <v>210</v>
       </c>
       <c r="B593" s="11">
-        <v>-210</v>
+        <v>-110</v>
       </c>
       <c r="C593" s="11" t="s">
         <v>212</v>
@@ -20393,6 +20308,11 @@
       </c>
       <c r="G593" s="11" t="s">
         <v>211</v>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
       </c>
       <c r="J593"/>
       <c r="K593" s="19"/>
@@ -20434,7 +20354,39 @@
       <c r="R594"/>
     </row>
     <row r="595" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B595" s="16"/>
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="B595" s="16">
+        <v>-1</v>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
+      </c>
       <c r="K595" s="12"/>
       <c r="L595" s="12"/>
       <c r="M595" s="12"/>
@@ -22360,6 +22312,3443 @@
       <c r="I676" t="inlineStr">
         <is>
           <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>silicon nitride, power-module ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B681">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>silicon nitride, power-module ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016).</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>silicon nitride, power-module ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="B688">
+        <v>1</v>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>silicon nitride, power-module ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>silicon nitride, power-module ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>market for silicon, metallurgical grade</t>
+        </is>
+      </c>
+      <c r="B689">
+        <v>0.6006073437266098</v>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>silicon, metallurgical grade</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>silicon, metallurgical grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>market for nitrogen, liquid</t>
+        </is>
+      </c>
+      <c r="B690">
+        <v>0.39939265627339027</v>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>nitrogen, liquid</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>nitrogen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B691">
+        <v>3</v>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B692">
+        <v>1</v>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>lead oxide, power-module trace engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B697">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>lead oxide, power-module trace engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016).</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>lead oxide, power-module trace engineering reference</t>
+        </is>
+      </c>
+      <c r="B704">
+        <v>1</v>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>lead oxide, power-module trace engineering reference</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>lead oxide, power-module trace engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>market for lead</t>
+        </is>
+      </c>
+      <c r="B705">
+        <v>0.9283195713242443</v>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>market for oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="B706">
+        <v>0.07168042867575572</v>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B707">
+        <v>3</v>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>SiC half-bridge module, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B712">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>SiC half-bridge module, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016).</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>SiC half-bridge module, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B719">
+        <v>1</v>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>SiC half-bridge module, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>SiC half-bridge module, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B720">
+        <v>0.68</v>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B721">
+        <v>0.016</v>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>market for silicon carbide</t>
+        </is>
+      </c>
+      <c r="B722">
+        <v>0.001</v>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>silicon carbide</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>silicon carbide</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>silicon nitride, power-module ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="B723">
+        <v>0.009</v>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>silicon nitride, power-module ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>silicon nitride, power-module ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B724">
+        <v>0.001</v>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>market for antimony</t>
+        </is>
+      </c>
+      <c r="B725">
+        <v>0.001</v>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B726">
+        <v>0.001</v>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>market for silicone product</t>
+        </is>
+      </c>
+      <c r="B727">
+        <v>0.084</v>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>market for nylon 6</t>
+        </is>
+      </c>
+      <c r="B728">
+        <v>0.089</v>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>market for glass fibre</t>
+        </is>
+      </c>
+      <c r="B729">
+        <v>0.046</v>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>market for organophosphorus-compound, unspecified</t>
+        </is>
+      </c>
+      <c r="B730">
+        <v>0.015</v>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>organophosphorus-compound, unspecified</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>organophosphorus-compound, unspecified</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B731">
+        <v>0.05</v>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B732">
+        <v>0.001</v>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>lead oxide, power-module trace engineering reference</t>
+        </is>
+      </c>
+      <c r="B733">
+        <v>1.8e-05</v>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>lead oxide, power-module trace engineering reference</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>lead oxide, power-module trace engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B738">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016).</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+        </is>
+      </c>
+      <c r="B745">
+        <v>1</v>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>market for acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+      <c r="B746">
+        <v>8.12501282614425</v>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>market for nylon 6</t>
+        </is>
+      </c>
+      <c r="B747">
+        <v>6.658547096547483</v>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>market for glass fibre</t>
+        </is>
+      </c>
+      <c r="B748">
+        <v>2.2591499077571817</v>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B749">
+        <v>53.308010981287886</v>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B750">
+        <v>42.80494562066239</v>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B751">
+        <v>39.832379952560835</v>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>SiC half-bridge module, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B752">
+        <v>3.0509999999999997</v>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>SiC half-bridge module, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>SiC half-bridge module, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B753">
+        <v>8</v>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B754">
+        <v>14</v>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>market for fan, for power supply unit, desktop computer</t>
+        </is>
+      </c>
+      <c r="B755">
+        <v>1</v>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>fan, for power supply unit, desktop computer</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>fan, for power supply unit, desktop computer</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B756">
+        <v>53.308010981287886</v>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B757">
+        <v>42.80494562066239</v>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B758">
+        <v>39.832379952560835</v>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B763">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016).</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+        </is>
+      </c>
+      <c r="B770">
+        <v>1</v>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>market for steel, unalloyed</t>
+        </is>
+      </c>
+      <c r="B771">
+        <v>918.9004000000001</v>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>steel, unalloyed</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>steel, unalloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>market for silicon, metallurgical grade</t>
+        </is>
+      </c>
+      <c r="B772">
+        <v>28.419600000000006</v>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>silicon, metallurgical grade</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>silicon, metallurgical grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>market for hot rolling, steel</t>
+        </is>
+      </c>
+      <c r="B773">
+        <v>947.3200000000002</v>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>hot rolling, steel</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>hot rolling, steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>sheet rolling, steel</t>
+        </is>
+      </c>
+      <c r="B774">
+        <v>1894.6400000000003</v>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>sheet rolling, steel</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>sheet rolling, steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B775">
+        <v>1042.0520000000001</v>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>heat production, natural gas, at industrial furnace &gt;100kW</t>
+        </is>
+      </c>
+      <c r="B776">
+        <v>4357.6720000000005</v>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>market for lubricating oil</t>
+        </is>
+      </c>
+      <c r="B777">
+        <v>466.40000000000003</v>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>lubricating oil</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>lubricating oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B778">
+        <v>271.92</v>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="B779">
+        <v>271.92</v>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B780">
+        <v>271.92</v>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B781">
+        <v>763.1888000000001</v>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>market for kraft paper</t>
+        </is>
+      </c>
+      <c r="B782">
+        <v>15.008400000000002</v>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>kraft paper</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>kraft paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>market for fibreboard, hard</t>
+        </is>
+      </c>
+      <c r="B783">
+        <v>0.016262400000000003</v>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>fibreboard, hard</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>fibreboard, hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B784">
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B785">
+        <v>0.9240000000000002</v>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B786">
+        <v>1.1</v>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>market for synthetic rubber</t>
+        </is>
+      </c>
+      <c r="B787">
+        <v>0.08800000000000002</v>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>synthetic rubber</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>synthetic rubber</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>market for alkyd paint, white, without water, in 60% solution state</t>
+        </is>
+      </c>
+      <c r="B788">
+        <v>5.9884</v>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>alkyd paint, white, without water, in 60% solution state</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>alkyd paint, white, without water, in 60% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B793">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016).</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+        </is>
+      </c>
+      <c r="B800">
+        <v>1</v>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+        </is>
+      </c>
+      <c r="B801">
+        <v>1</v>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+        </is>
+      </c>
+      <c r="B802">
+        <v>1</v>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B807">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016).</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="B814">
+        <v>-1</v>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>market for scrap steel</t>
+        </is>
+      </c>
+      <c r="B815">
+        <v>-1764.916810981288</v>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>scrap steel</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>scrap steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>market for scrap aluminium</t>
+        </is>
+      </c>
+      <c r="B816">
+        <v>-314.7249456206624</v>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>scrap aluminium</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>scrap aluminium</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>market for scrap copper</t>
+        </is>
+      </c>
+      <c r="B817">
+        <v>-40.756379952560835</v>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>scrap copper</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>scrap copper</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>treatment of scrap printed wiring boards, shredding and separation</t>
+        </is>
+      </c>
+      <c r="B818">
+        <v>-8</v>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>used printed wiring boards</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>used printed wiring boards</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>market for waste electric and electronic equipment</t>
+        </is>
+      </c>
+      <c r="B819">
+        <v>-43.054663445488906</v>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>waste electric and electronic equipment</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>waste electric and electronic equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>market for waste mineral oil</t>
+        </is>
+      </c>
+      <c r="B820">
+        <v>-466.40000000000003</v>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>waste mineral oil</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>waste mineral oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>market for waste paperboard</t>
+        </is>
+      </c>
+      <c r="B821">
+        <v>-31.2708</v>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>waste paperboard</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>waste paperboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>market for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B822">
+        <v>-6.6000000000000005</v>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>market for waste rubber, unspecified</t>
+        </is>
+      </c>
+      <c r="B823">
+        <v>-0.08800000000000002</v>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>waste rubber, unspecified</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>waste rubber, unspecified</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>treatment of waste paint on metal, collection for final disposal</t>
+        </is>
+      </c>
+      <c r="B824">
+        <v>-5.9884</v>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>waste paint on metal</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>waste paint on metal</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U824"/>
+  <dimension ref="A1:U844"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -16777,7 +16777,9 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>APPROVED SOEC INORGANIC GLASS-SEAL REFERENCE, issue91, 2026-10-18. Sun,Xiao,Guo,Hong2010,CeramicsInternational36:821-826,DOI10.1016/j.ceramint.2009.09.045,experimentalBaO-Al2O3-B2O3-SiO2glassfamily:base40BaO/20B2O3/40SiO2mol%,Al2O3replacesB2O3/SiO2atconstant2:1Si/Boxide-moleratio;5mol%Alvariantidentifiedasstable,melting1400-1500Cfor1hour. https://www.sciencedirect.com/science/article/pii/S0272884209003812 . ExistingGerloff2021sealantmass4*6.4kg retained. SiliconepolymerisnotSiO2glassformer. Replacefour6.4kgingredients(Al2O3,B2O3,BaO,silicone)by25.6kgofonefinishedglassreference. Select/reconstruct5mol%Al2O3member:40BaO,5Al2O3,18.333333B2O3,36.666667SiO2mol%;theseareoxideMOLfractions,notweightfractions. Correspondingretainedweightfractions={'BaO': 0.6059001794302946, 'Al2O3': 0.05036460625483175, 'B2O3': 0.12609040016734147, 'SiO2': 0.21764481414753226}. Total25.6kgfinishedsealisinheritedengineeringmass,notmeasuredfromthispublishedglassdesign;sourceTable1fullcompositionwasnotindependentlyrecovered,recipeisexplicitreconstructionfrompublishedseriesdescription. UsingSOFCsealingglassasSOECanalogue doesnotdemonstrateactualstacksealgeometry,thermalcycling,dual-atmospherecompatibilityorleaktightness. PurchaseactualBaO,Al2O3,B2O3,SiO2equivalentsscaledby1/0.95forselected95%melting/formingretention,withmatchedsolidglassreject1/.95-1kg/kgtoexistingmixedhazardoustreatmentproxy;volatilizedB/alkalicomponentsandactualwasteclassificationunresolved.6MJ/kgthermaland1kWh/kgmilling/formingareexplicitengineeringutilityallowancesfor1450Cmelting/quenching,notmeasuredsourceutilities;test3-12MJ/kg,0.2-2kWh/kgand90-100%retention. SilicasandisbulkSiO2purityproxy,nonmetallurgicalaluminaisspecialtyoxideproxy;semiconductorgradepurificationnotclaimed. ExistingapprovedYSZ/YDCchemistryandfutureY/Ce/Zrco-scaling,Ni/La/Sr/Prpurchases,steel,stackreplacementandhydrogenoutputallocationunchanged. Do notreduceentirestackorapplyfuturedensitylearningtosealwithoutsource. No newnative/runtime/YAMLchangesorprimary-secondarycredit.
+          <t>APPROVED COMPLETE SOEC LSM REFERENCE, issue94, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis. Replace uncertain21kgLa2O3+21kgSrCO3 placeholders (both formerly to-check) by2.1kgfinishedLa0.8Sr0.2MnO3 perexistingMWstack. This is an explicit published-reference adoption, NOT recovered manufacturer BOM or proof that originalGerloff21kg meant2.1kg. Source-dose sensitivity2.1-21kgfinishedLSM required; old42kgrawsalts is not a chemically defined alternative. La0.8Sr0.2MnO3 is selected nominal oxygen-stoichiometric LSM; actual Sr doping/oxygen nonstoichiometry/contact-layer loading remain gaps. Net reaction0.4La2O3+0.2SrCO3+MnO2 -&gt;La0.8Sr0.2MnO3+0.2CO2+0.2O2. Use95% finished-solid retention,100% conversion before5%handlingreject; yields90-100%sensitivity. Perkgfinished feeds={'La2O3': 0.5923666319735489, 'SrCO3': 0.13420468074687047, 'MnO2': 0.3951562044603966};CO2=0.040007409129630044kg,O2=0.02908852910381745kg,reject=0.05263157894736836kg.6MJ/kgheat+1kWh/kgmilling/sintering is an engineering allowance,not measured industrial calcination (3-12MJ and0.5-2kWhsensitivity). All stoichiometric C/La/Sr/Mn/O and mass close. No nitric-acid/chloroacetic-acid/ammonia route or unsupported metal-free binder is silently copied. Keep totalfinished2.1kg distinct from grossprecursorfeed. Newsolidwaste andfinishedceramic EOL use genericinertdisposal,not validated heavy-metal-specific treatment/recovery. Existing Pr/Ni air-electrode,YSZ/YDCfutureco-scaling,glassseal,steelmass,lifetimes andoperatingH2energy unchanged. No primary/secondary-share or runtime changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED SOEC INORGANIC GLASS-SEAL REFERENCE, issue91, 2026-10-18. Sun,Xiao,Guo,Hong2010,CeramicsInternational36:821-826,DOI10.1016/j.ceramint.2009.09.045,experimentalBaO-Al2O3-B2O3-SiO2glassfamily:base40BaO/20B2O3/40SiO2mol%,Al2O3replacesB2O3/SiO2atconstant2:1Si/Boxide-moleratio;5mol%Alvariantidentifiedasstable,melting1400-1500Cfor1hour. https://www.sciencedirect.com/science/article/pii/S0272884209003812 . ExistingGerloff2021sealantmass4*6.4kg retained. SiliconepolymerisnotSiO2glassformer. Replacefour6.4kgingredients(Al2O3,B2O3,BaO,silicone)by25.6kgofonefinishedglassreference. Select/reconstruct5mol%Al2O3member:40BaO,5Al2O3,18.333333B2O3,36.666667SiO2mol%;theseareoxideMOLfractions,notweightfractions. Correspondingretainedweightfractions={'BaO': 0.6059001794302946, 'Al2O3': 0.05036460625483175, 'B2O3': 0.12609040016734147, 'SiO2': 0.21764481414753226}. Total25.6kgfinishedsealisinheritedengineeringmass,notmeasuredfromthispublishedglassdesign;sourceTable1fullcompositionwasnotindependentlyrecovered,recipeisexplicitreconstructionfrompublishedseriesdescription. UsingSOFCsealingglassasSOECanalogue doesnotdemonstrateactualstacksealgeometry,thermalcycling,dual-atmospherecompatibilityorleaktightness. PurchaseactualBaO,Al2O3,B2O3,SiO2equivalentsscaledby1/0.95forselected95%melting/formingretention,withmatchedsolidglassreject1/.95-1kg/kgtoexistingmixedhazardoustreatmentproxy;volatilizedB/alkalicomponentsandactualwasteclassificationunresolved.6MJ/kgthermaland1kWh/kgmilling/formingareexplicitengineeringutilityallowancesfor1450Cmelting/quenching,notmeasuredsourceutilities;test3-12MJ/kg,0.2-2kWh/kgand90-100%retention. SilicasandisbulkSiO2purityproxy,nonmetallurgicalaluminaisspecialtyoxideproxy;semiconductorgradepurificationnotclaimed. ExistingapprovedYSZ/YDCchemistryandfutureY/Ce/Zrco-scaling,Ni/La/Sr/Prpurchases,steel,stackreplacementandhydrogenoutputallocationunchanged. Do notreduceentirestackorapplyfuturedensitylearningtosealwithoutsource. No newnative/runtime/YAMLchangesorprimary-secondarycredit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 1 MWe Solid Oxide electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years. Produced amount of H2 over 20 years: 3779894.18 kg. Amounts of lanthanum oxide and strontium carbonate are unsure. 
 SOEC matched ceramic reference v1. YSZ: 8 mol% Y2O3 among binary oxides; YDC: Ce0.8Y0.2O1.9 (20% Y on cation sites). Gerloff 2021 capacity scaling of the attributed Haefele 2016 component masses, not concentrate mass treated as pure oxide. Mixed Sm/Eu/Gd proxy replaced by stoichiometric Y2O3. See data/metals/soec_ceramic_reference.json for source-access limits, explicit composition/scaling assumptions and remaining whole-stack gaps.</t>
@@ -16912,6 +16914,11 @@
         <f>B467</f>
         <v>electrolyzer, 1MWe, SOEC, Stack</v>
       </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>APPROVED COMPLETE SOEC LSM REFERENCE, issue94, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis. Replace uncertain21kgLa2O3+21kgSrCO3 placeholders (both formerly to-check) by2.1kgfinishedLa0.8Sr0.2MnO3 perexistingMWstack. This is an explicit published-reference adoption, NOT recovered manufacturer BOM or proof that originalGerloff21kg meant2.1kg. Source-dose sensitivity2.1-21kgfinishedLSM required; old42kgrawsalts is not a chemically defined alternative. La0.8Sr0.2MnO3 is selected nominal oxygen-stoichiometric LSM; actual Sr doping/oxygen nonstoichiometry/contact-layer loading remain gaps. Net reaction0.4La2O3+0.2SrCO3+MnO2 -&gt;La0.8Sr0.2MnO3+0.2CO2+0.2O2. Use95% finished-solid retention,100% conversion before5%handlingreject; yields90-100%sensitivity. Perkgfinished feeds={'La2O3': 0.5923666319735489, 'SrCO3': 0.13420468074687047, 'MnO2': 0.3951562044603966};CO2=0.040007409129630044kg,O2=0.02908852910381745kg,reject=0.05263157894736836kg.6MJ/kgheat+1kWh/kgmilling/sintering is an engineering allowance,not measured industrial calcination (3-12MJ and0.5-2kWhsensitivity). All stoichiometric C/La/Sr/Mn/O and mass close. No nitric-acid/chloroacetic-acid/ammonia route or unsupported metal-free binder is silently copied. Keep totalfinished2.1kg distinct from grossprecursorfeed. Newsolidwaste andfinishedceramic EOL use genericinertdisposal,not validated heavy-metal-specific treatment/recovery. Existing Pr/Ni air-electrode,YSZ/YDCfutureco-scaling,glassseal,steelmass,lifetimes andoperatingH2energy unchanged. No primary/secondary-share or runtime changes.</t>
+        </is>
+      </c>
       <c r="K472" s="12"/>
       <c r="L472" s="12"/>
       <c r="M472" s="12"/>
@@ -17200,15 +17207,19 @@
       <c r="R480"/>
     </row>
     <row r="481" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A481" s="11" t="s">
-        <v>163</v>
+      <c r="A481" s="11" t="inlineStr">
+        <is>
+          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+        </is>
       </c>
       <c r="B481" s="12">
-        <f>42/2</f>
-        <v>21</v>
-      </c>
-      <c r="C481" s="11" t="s">
-        <v>17</v>
+        <f>2.1</f>
+        <v>2.1</v>
+      </c>
+      <c r="C481" s="11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D481" s="11" t="s">
         <v>13</v>
@@ -17216,11 +17227,15 @@
       <c r="F481" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G481" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="H481" s="11" t="s">
-        <v>165</v>
+      <c r="G481" s="11" t="inlineStr">
+        <is>
+          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+        </is>
+      </c>
+      <c r="H481" s="11" t="inlineStr">
+        <is>
+          <t>APPROVED COMPLETE SOEC LSM REFERENCE, issue94, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis. Replace uncertain21kgLa2O3+21kgSrCO3 placeholders (both formerly to-check) by2.1kgfinishedLa0.8Sr0.2MnO3 perexistingMWstack. This is an explicit published-reference adoption, NOT recovered manufacturer BOM or proof that originalGerloff21kg meant2.1kg. Source-dose sensitivity2.1-21kgfinishedLSM required; old42kgrawsalts is not a chemically defined alternative. La0.8Sr0.2MnO3 is selected nominal oxygen-stoichiometric LSM; actual Sr doping/oxygen nonstoichiometry/contact-layer loading remain gaps. Net reaction0.4La2O3+0.2SrCO3+MnO2 -&gt;La0.8Sr0.2MnO3+0.2CO2+0.2O2. Use95% finished-solid retention,100% conversion before5%handlingreject; yields90-100%sensitivity. Perkgfinished feeds={'La2O3': 0.5923666319735489, 'SrCO3': 0.13420468074687047, 'MnO2': 0.3951562044603966};CO2=0.040007409129630044kg,O2=0.02908852910381745kg,reject=0.05263157894736836kg.6MJ/kgheat+1kWh/kgmilling/sintering is an engineering allowance,not measured industrial calcination (3-12MJ and0.5-2kWhsensitivity). All stoichiometric C/La/Sr/Mn/O and mass close. No nitric-acid/chloroacetic-acid/ammonia route or unsupported metal-free binder is silently copied. Keep totalfinished2.1kg distinct from grossprecursorfeed. Newsolidwaste andfinishedceramic EOL use genericinertdisposal,not validated heavy-metal-specific treatment/recovery. Existing Pr/Ni air-electrode,YSZ/YDCfutureco-scaling,glassseal,steelmass,lifetimes andoperatingH2energy unchanged. No primary/secondary-share or runtime changes.</t>
+        </is>
       </c>
       <c r="J481"/>
       <c r="K481" s="19"/>
@@ -17233,28 +17248,13 @@
       <c r="R481"/>
     </row>
     <row r="482" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A482" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B482" s="12">
-        <f>42/2</f>
-        <v>21</v>
-      </c>
-      <c r="C482" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D482" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F482" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G482" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="H482" s="11" t="s">
-        <v>165</v>
-      </c>
+      <c r="A482" s="11"/>
+      <c r="B482" s="12"/>
+      <c r="C482" s="11"/>
+      <c r="D482" s="11"/>
+      <c r="F482" s="11"/>
+      <c r="G482" s="11"/>
+      <c r="H482" s="11"/>
       <c r="J482"/>
       <c r="K482" s="19"/>
       <c r="L482" s="19"/>
@@ -17466,8 +17466,12 @@
       <c r="A492" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B492" s="14" t="s">
-        <v>56</v>
+      <c r="B492" s="14" t="inlineStr">
+        <is>
+          <t>APPROVED COMPLETE SOEC LSM REFERENCE, issue94, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis. Replace uncertain21kgLa2O3+21kgSrCO3 placeholders (both formerly to-check) by2.1kgfinishedLa0.8Sr0.2MnO3 perexistingMWstack. This is an explicit published-reference adoption, NOT recovered manufacturer BOM or proof that originalGerloff21kg meant2.1kg. Source-dose sensitivity2.1-21kgfinishedLSM required; old42kgrawsalts is not a chemically defined alternative. La0.8Sr0.2MnO3 is selected nominal oxygen-stoichiometric LSM; actual Sr doping/oxygen nonstoichiometry/contact-layer loading remain gaps. Net reaction0.4La2O3+0.2SrCO3+MnO2 -&gt;La0.8Sr0.2MnO3+0.2CO2+0.2O2. Use95% finished-solid retention,100% conversion before5%handlingreject; yields90-100%sensitivity. Perkgfinished feeds={'La2O3': 0.5923666319735489, 'SrCO3': 0.13420468074687047, 'MnO2': 0.3951562044603966};CO2=0.040007409129630044kg,O2=0.02908852910381745kg,reject=0.05263157894736836kg.6MJ/kgheat+1kWh/kgmilling/sintering is an engineering allowance,not measured industrial calcination (3-12MJ and0.5-2kWhsensitivity). All stoichiometric C/La/Sr/Mn/O and mass close. No nitric-acid/chloroacetic-acid/ammonia route or unsupported metal-free binder is silently copied. Keep totalfinished2.1kg distinct from grossprecursorfeed. Newsolidwaste andfinishedceramic EOL use genericinertdisposal,not validated heavy-metal-specific treatment/recovery. Existing Pr/Ni air-electrode,YSZ/YDCfutureco-scaling,glassseal,steelmass,lifetimes andoperatingH2energy unchanged. No primary/secondary-share or runtime changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 MW PEM electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years per single stack, @ 8000 hours/year. Iridium mining process is NOT from ecoinvent. Produced amount of H2 over 20 years: 2964315.35 kg. According to a study called IndWEDe, it is assumed that the stacks are replaced 3 times during the 20 years lifespan, based on the 2030’s scenario for 1 MW systems which predicts a lifetime of 50,000 h or more for the stacks of the different water electrolysis technologies. In comparison to AEC electrolyzers, PEMEC electrolyzers are less mature. Furthermore, the PEMEC technology is commercially available and operates with a similar system efficiency as the AEC technology. However, the current density and the gas purity are higher with values in between 0.6–2.0 A/cm2 and &gt; 99.99%, respectively. Besides this, the operating pressure (below 200 bar) is significantly higher in comparison to AEC systems, while the operating temperature (50 °C to 80 °C) and the system energy (4.2–6.6 kWh/m3H2) are similar to AEC systems. The PEMEC BoP and stack components data stem from Bareiß et al. and correspond to a 1 MW system. Moreover, some further BoP components like water purifier &amp; feed tank, buffer tank, and heat exchanger have been added, derived from a 300 kW AEC system, under the assumption that the components are also suitable for a PEMEC system. The values have been scaled up from 300 kW to 1 MW. Values have already been multiplied by 3 to reflect 2 stack replacements over 20 years of use.</t>
+        </is>
       </c>
       <c r="K492" s="12"/>
       <c r="L492" s="12"/>
@@ -17598,6 +17602,11 @@
         <f>B493</f>
         <v>used electrolyzer stack, 1MWe, SOEC</v>
       </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>APPROVED COMPLETE SOEC LSM REFERENCE, issue94, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis. Replace uncertain21kgLa2O3+21kgSrCO3 placeholders (both formerly to-check) by2.1kgfinishedLa0.8Sr0.2MnO3 perexistingMWstack. This is an explicit published-reference adoption, NOT recovered manufacturer BOM or proof that originalGerloff21kg meant2.1kg. Source-dose sensitivity2.1-21kgfinishedLSM required; old42kgrawsalts is not a chemically defined alternative. La0.8Sr0.2MnO3 is selected nominal oxygen-stoichiometric LSM; actual Sr doping/oxygen nonstoichiometry/contact-layer loading remain gaps. Net reaction0.4La2O3+0.2SrCO3+MnO2 -&gt;La0.8Sr0.2MnO3+0.2CO2+0.2O2. Use95% finished-solid retention,100% conversion before5%handlingreject; yields90-100%sensitivity. Perkgfinished feeds={'La2O3': 0.5923666319735489, 'SrCO3': 0.13420468074687047, 'MnO2': 0.3951562044603966};CO2=0.040007409129630044kg,O2=0.02908852910381745kg,reject=0.05263157894736836kg.6MJ/kgheat+1kWh/kgmilling/sintering is an engineering allowance,not measured industrial calcination (3-12MJ and0.5-2kWhsensitivity). All stoichiometric C/La/Sr/Mn/O and mass close. No nitric-acid/chloroacetic-acid/ammonia route or unsupported metal-free binder is silently copied. Keep totalfinished2.1kg distinct from grossprecursorfeed. Newsolidwaste andfinishedceramic EOL use genericinertdisposal,not validated heavy-metal-specific treatment/recovery. Existing Pr/Ni air-electrode,YSZ/YDCfutureco-scaling,glassseal,steelmass,lifetimes andoperatingH2energy unchanged. No primary/secondary-share or runtime changes.</t>
+        </is>
+      </c>
       <c r="K498" s="12"/>
       <c r="L498" s="12"/>
       <c r="M498" s="12"/>
@@ -17636,7 +17645,39 @@
       <c r="R499"/>
     </row>
     <row r="500" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B500" s="16"/>
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B500" s="16">
+        <v>-2.1</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>APPROVED COMPLETE SOEC LSM REFERENCE, issue94, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis. Replace uncertain21kgLa2O3+21kgSrCO3 placeholders (both formerly to-check) by2.1kgfinishedLa0.8Sr0.2MnO3 perexistingMWstack. This is an explicit published-reference adoption, NOT recovered manufacturer BOM or proof that originalGerloff21kg meant2.1kg. Source-dose sensitivity2.1-21kgfinishedLSM required; old42kgrawsalts is not a chemically defined alternative. La0.8Sr0.2MnO3 is selected nominal oxygen-stoichiometric LSM; actual Sr doping/oxygen nonstoichiometry/contact-layer loading remain gaps. Net reaction0.4La2O3+0.2SrCO3+MnO2 -&gt;La0.8Sr0.2MnO3+0.2CO2+0.2O2. Use95% finished-solid retention,100% conversion before5%handlingreject; yields90-100%sensitivity. Perkgfinished feeds={'La2O3': 0.5923666319735489, 'SrCO3': 0.13420468074687047, 'MnO2': 0.3951562044603966};CO2=0.040007409129630044kg,O2=0.02908852910381745kg,reject=0.05263157894736836kg.6MJ/kgheat+1kWh/kgmilling/sintering is an engineering allowance,not measured industrial calcination (3-12MJ and0.5-2kWhsensitivity). All stoichiometric C/La/Sr/Mn/O and mass close. No nitric-acid/chloroacetic-acid/ammonia route or unsupported metal-free binder is silently copied. Keep totalfinished2.1kg distinct from grossprecursorfeed. Newsolidwaste andfinishedceramic EOL use genericinertdisposal,not validated heavy-metal-specific treatment/recovery. Existing Pr/Ni air-electrode,YSZ/YDCfutureco-scaling,glassseal,steelmass,lifetimes andoperatingH2energy unchanged. No primary/secondary-share or runtime changes.</t>
+        </is>
+      </c>
       <c r="K500" s="12"/>
       <c r="L500" s="12"/>
       <c r="M500" s="12"/>
@@ -25749,6 +25790,447 @@
       <c r="I824" t="inlineStr">
         <is>
           <t>waste paint on metal</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B829">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>APPROVED COMPLETE SOEC LSM REFERENCE, issue94, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis. Replace uncertain21kgLa2O3+21kgSrCO3 placeholders (both formerly to-check) by2.1kgfinishedLa0.8Sr0.2MnO3 perexistingMWstack. This is an explicit published-reference adoption, NOT recovered manufacturer BOM or proof that originalGerloff21kg meant2.1kg. Source-dose sensitivity2.1-21kgfinishedLSM required; old42kgrawsalts is not a chemically defined alternative. La0.8Sr0.2MnO3 is selected nominal oxygen-stoichiometric LSM; actual Sr doping/oxygen nonstoichiometry/contact-layer loading remain gaps. Net reaction0.4La2O3+0.2SrCO3+MnO2 -&gt;La0.8Sr0.2MnO3+0.2CO2+0.2O2. Use95% finished-solid retention,100% conversion before5%handlingreject; yields90-100%sensitivity. Perkgfinished feeds={'La2O3': 0.5923666319735489, 'SrCO3': 0.13420468074687047, 'MnO2': 0.3951562044603966};CO2=0.040007409129630044kg,O2=0.02908852910381745kg,reject=0.05263157894736836kg.6MJ/kgheat+1kWh/kgmilling/sintering is an engineering allowance,not measured industrial calcination (3-12MJ and0.5-2kWhsensitivity). All stoichiometric C/La/Sr/Mn/O and mass close. No nitric-acid/chloroacetic-acid/ammonia route or unsupported metal-free binder is silently copied. Keep totalfinished2.1kg distinct from grossprecursorfeed. Newsolidwaste andfinishedceramic EOL use genericinertdisposal,not validated heavy-metal-specific treatment/recovery. Existing Pr/Ni air-electrode,YSZ/YDCfutureco-scaling,glassseal,steelmass,lifetimes andoperatingH2energy unchanged. No primary/secondary-share or runtime changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+        </is>
+      </c>
+      <c r="B836">
+        <v>1</v>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>market for lanthanum oxide</t>
+        </is>
+      </c>
+      <c r="B837">
+        <v>0.5923666319735489</v>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>lanthanum oxide</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>lanthanum oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>market for strontium carbonate</t>
+        </is>
+      </c>
+      <c r="B838">
+        <v>0.13420468074687047</v>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>strontium carbonate</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>strontium carbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>market for manganese dioxide</t>
+        </is>
+      </c>
+      <c r="B839">
+        <v>0.3951562044603966</v>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>manganese dioxide</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>manganese dioxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B840">
+        <v>6</v>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B841">
+        <v>1</v>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B842">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, fossil</t>
+        </is>
+      </c>
+      <c r="B843">
+        <v>0.040007409129630044</v>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Oxygen</t>
+        </is>
+      </c>
+      <c r="B844">
+        <v>0.02908852910381745</v>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U844"/>
+  <dimension ref="A1:U887"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -16777,7 +16777,9 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>APPROVED COMPLETE SOEC LSM REFERENCE, issue94, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis. Replace uncertain21kgLa2O3+21kgSrCO3 placeholders (both formerly to-check) by2.1kgfinishedLa0.8Sr0.2MnO3 perexistingMWstack. This is an explicit published-reference adoption, NOT recovered manufacturer BOM or proof that originalGerloff21kg meant2.1kg. Source-dose sensitivity2.1-21kgfinishedLSM required; old42kgrawsalts is not a chemically defined alternative. La0.8Sr0.2MnO3 is selected nominal oxygen-stoichiometric LSM; actual Sr doping/oxygen nonstoichiometry/contact-layer loading remain gaps. Net reaction0.4La2O3+0.2SrCO3+MnO2 -&gt;La0.8Sr0.2MnO3+0.2CO2+0.2O2. Use95% finished-solid retention,100% conversion before5%handlingreject; yields90-100%sensitivity. Perkgfinished feeds={'La2O3': 0.5923666319735489, 'SrCO3': 0.13420468074687047, 'MnO2': 0.3951562044603966};CO2=0.040007409129630044kg,O2=0.02908852910381745kg,reject=0.05263157894736836kg.6MJ/kgheat+1kWh/kgmilling/sintering is an engineering allowance,not measured industrial calcination (3-12MJ and0.5-2kWhsensitivity). All stoichiometric C/La/Sr/Mn/O and mass close. No nitric-acid/chloroacetic-acid/ammonia route or unsupported metal-free binder is silently copied. Keep totalfinished2.1kg distinct from grossprecursorfeed. Newsolidwaste andfinishedceramic EOL use genericinertdisposal,not validated heavy-metal-specific treatment/recovery. Existing Pr/Ni air-electrode,YSZ/YDCfutureco-scaling,glassseal,steelmass,lifetimes andoperatingH2energy unchanged. No primary/secondary-share or runtime changes.
+          <t>APPROVED SOEC FERRITIC INTERCONNECT REFERENCE, issue95, 2026-10-18. Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1:chromiumsteelplate-&gt;deepdrawing+LSMcoating-&gt;interconnect; main stackdescription2outer3kg and4inner145g plates. Gerloff2021 PtM SI pS16 retains8976.1kg18/8steel but labels air-electrode. VDM Crofer22APU datasheet4146rev01 March2022 Table2 andApplications p5 explicitly SOEC interconnects/bipolarplates:Cr20-24wt%,Mn0.30-0.80,Ti0.03-0.20,La0.04-0.20,Fe balance. https://www.vdm-metals.com/fileadmin/user_upload/Downloads/Data_Sheets/Data_Sheet_VDM_Crofer_22_APU.pdf . Sourceflow8976.1kg is treated as the interconnectplate package based on originalmanufacturingdiagram,not9tair-electrodecatalyst. AdoptCrofer22APU-type reference for THIS stackinput only; do not replace ordinaryBoP18/8heat exchangers. Preserve8976.1kgfinishedsteel and8976.1kgexistingrollingservice; mass derives labstackscaleup and is NOT independently validated industrialMWgeometry. Preserve priorLSM,PrNi,ceramics,stackreplacement andlearning. Reference alloy massfractions={'Cr': 0.22, 'Mn': 0.005, 'Ti': 0.001, 'La': 0.001, 'Si': 0.001, 'Al': 0.0005, 'Cu': 0.0005, 'C': 0.0001, 'P': 5e-05, 'S': 5e-05, 'Fe': 0.7708}. Midrange/lowresidual choices are explicit assumptions within publishedranges,not measured heat assay. No intentionalNi addition; unknownresidualNi/othertraceimpurities are NOT provenzero. ActualoldNi8% cannot be claimed quantitatively without suppliercomposition; compareold18/8 as sensitivity. Cr20-24,Mn0.3-0.8,La0.04-0.20wt% sensitivities. Fe usesunalloyedsteel as feed-gradeproxy,withitsownminoralloys unresolved; completecomponentmetaluse is not identical toelementalpureFe. Addalloyingmaterialsonce and0.5kWh+2MJ/kgremeltingreference (0.25-1kWh/1-4MJsensitivity),not a completeCrsteel production dataset on top. Matchfinishedsteelmass1kgwith100%finalalloyretention; alloyingyield/slag andtracepickup remain gaps. La metal unavailable: explicit netoxide/carbon electrolyticreference La2O3+1.5C-&gt;2La+1.5CO2,95%metalretention,10kWh/kg+3MJ/kgassumed; fluoridebathmakeup,PFCemissions,purification andcalcium-route alternatives unresolved. Thisisstoichiometricnetelectrolysis,NOTthermal carbothermic reduction orvalidatedvendorLa process. Metalrejectgenericinertdisposal; La/C/O/massclose. FinishedinterconnectEOLexistingsteelcollection amount retained; genericsteelroute doesnotvalidatealloy-specificrecycling orrecoverycredits. Native/YAML/runtime/primary-secondaryshares untouched.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED COMPLETE SOEC LSM REFERENCE, issue94, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis. Replace uncertain21kgLa2O3+21kgSrCO3 placeholders (both formerly to-check) by2.1kgfinishedLa0.8Sr0.2MnO3 perexistingMWstack. This is an explicit published-reference adoption, NOT recovered manufacturer BOM or proof that originalGerloff21kg meant2.1kg. Source-dose sensitivity2.1-21kgfinishedLSM required; old42kgrawsalts is not a chemically defined alternative. La0.8Sr0.2MnO3 is selected nominal oxygen-stoichiometric LSM; actual Sr doping/oxygen nonstoichiometry/contact-layer loading remain gaps. Net reaction0.4La2O3+0.2SrCO3+MnO2 -&gt;La0.8Sr0.2MnO3+0.2CO2+0.2O2. Use95% finished-solid retention,100% conversion before5%handlingreject; yields90-100%sensitivity. Perkgfinished feeds={'La2O3': 0.5923666319735489, 'SrCO3': 0.13420468074687047, 'MnO2': 0.3951562044603966};CO2=0.040007409129630044kg,O2=0.02908852910381745kg,reject=0.05263157894736836kg.6MJ/kgheat+1kWh/kgmilling/sintering is an engineering allowance,not measured industrial calcination (3-12MJ and0.5-2kWhsensitivity). All stoichiometric C/La/Sr/Mn/O and mass close. No nitric-acid/chloroacetic-acid/ammonia route or unsupported metal-free binder is silently copied. Keep totalfinished2.1kg distinct from grossprecursorfeed. Newsolidwaste andfinishedceramic EOL use genericinertdisposal,not validated heavy-metal-specific treatment/recovery. Existing Pr/Ni air-electrode,YSZ/YDCfutureco-scaling,glassseal,steelmass,lifetimes andoperatingH2energy unchanged. No primary/secondary-share or runtime changes.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED SOEC INORGANIC GLASS-SEAL REFERENCE, issue91, 2026-10-18. Sun,Xiao,Guo,Hong2010,CeramicsInternational36:821-826,DOI10.1016/j.ceramint.2009.09.045,experimentalBaO-Al2O3-B2O3-SiO2glassfamily:base40BaO/20B2O3/40SiO2mol%,Al2O3replacesB2O3/SiO2atconstant2:1Si/Boxide-moleratio;5mol%Alvariantidentifiedasstable,melting1400-1500Cfor1hour. https://www.sciencedirect.com/science/article/pii/S0272884209003812 . ExistingGerloff2021sealantmass4*6.4kg retained. SiliconepolymerisnotSiO2glassformer. Replacefour6.4kgingredients(Al2O3,B2O3,BaO,silicone)by25.6kgofonefinishedglassreference. Select/reconstruct5mol%Al2O3member:40BaO,5Al2O3,18.333333B2O3,36.666667SiO2mol%;theseareoxideMOLfractions,notweightfractions. Correspondingretainedweightfractions={'BaO': 0.6059001794302946, 'Al2O3': 0.05036460625483175, 'B2O3': 0.12609040016734147, 'SiO2': 0.21764481414753226}. Total25.6kgfinishedsealisinheritedengineeringmass,notmeasuredfromthispublishedglassdesign;sourceTable1fullcompositionwasnotindependentlyrecovered,recipeisexplicitreconstructionfrompublishedseriesdescription. UsingSOFCsealingglassasSOECanalogue doesnotdemonstrateactualstacksealgeometry,thermalcycling,dual-atmospherecompatibilityorleaktightness. PurchaseactualBaO,Al2O3,B2O3,SiO2equivalentsscaledby1/0.95forselected95%melting/formingretention,withmatchedsolidglassreject1/.95-1kg/kgtoexistingmixedhazardoustreatmentproxy;volatilizedB/alkalicomponentsandactualwasteclassificationunresolved.6MJ/kgthermaland1kWh/kgmilling/formingareexplicitengineeringutilityallowancesfor1450Cmelting/quenching,notmeasuredsourceutilities;test3-12MJ/kg,0.2-2kWh/kgand90-100%retention. SilicasandisbulkSiO2purityproxy,nonmetallurgicalaluminaisspecialtyoxideproxy;semiconductorgradepurificationnotclaimed. ExistingapprovedYSZ/YDCchemistryandfutureY/Ce/Zrco-scaling,Ni/La/Sr/Prpurchases,steel,stackreplacementandhydrogenoutputallocationunchanged. Do notreduceentirestackorapplyfuturedensitylearningtosealwithoutsource. No newnative/runtime/YAMLchangesorprimary-secondarycredit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -16916,7 +16918,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>APPROVED COMPLETE SOEC LSM REFERENCE, issue94, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis. Replace uncertain21kgLa2O3+21kgSrCO3 placeholders (both formerly to-check) by2.1kgfinishedLa0.8Sr0.2MnO3 perexistingMWstack. This is an explicit published-reference adoption, NOT recovered manufacturer BOM or proof that originalGerloff21kg meant2.1kg. Source-dose sensitivity2.1-21kgfinishedLSM required; old42kgrawsalts is not a chemically defined alternative. La0.8Sr0.2MnO3 is selected nominal oxygen-stoichiometric LSM; actual Sr doping/oxygen nonstoichiometry/contact-layer loading remain gaps. Net reaction0.4La2O3+0.2SrCO3+MnO2 -&gt;La0.8Sr0.2MnO3+0.2CO2+0.2O2. Use95% finished-solid retention,100% conversion before5%handlingreject; yields90-100%sensitivity. Perkgfinished feeds={'La2O3': 0.5923666319735489, 'SrCO3': 0.13420468074687047, 'MnO2': 0.3951562044603966};CO2=0.040007409129630044kg,O2=0.02908852910381745kg,reject=0.05263157894736836kg.6MJ/kgheat+1kWh/kgmilling/sintering is an engineering allowance,not measured industrial calcination (3-12MJ and0.5-2kWhsensitivity). All stoichiometric C/La/Sr/Mn/O and mass close. No nitric-acid/chloroacetic-acid/ammonia route or unsupported metal-free binder is silently copied. Keep totalfinished2.1kg distinct from grossprecursorfeed. Newsolidwaste andfinishedceramic EOL use genericinertdisposal,not validated heavy-metal-specific treatment/recovery. Existing Pr/Ni air-electrode,YSZ/YDCfutureco-scaling,glassseal,steelmass,lifetimes andoperatingH2energy unchanged. No primary/secondary-share or runtime changes.</t>
+          <t>APPROVED SOEC FERRITIC INTERCONNECT REFERENCE, issue95, 2026-10-18. Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1:chromiumsteelplate-&gt;deepdrawing+LSMcoating-&gt;interconnect; main stackdescription2outer3kg and4inner145g plates. Gerloff2021 PtM SI pS16 retains8976.1kg18/8steel but labels air-electrode. VDM Crofer22APU datasheet4146rev01 March2022 Table2 andApplications p5 explicitly SOEC interconnects/bipolarplates:Cr20-24wt%,Mn0.30-0.80,Ti0.03-0.20,La0.04-0.20,Fe balance. https://www.vdm-metals.com/fileadmin/user_upload/Downloads/Data_Sheets/Data_Sheet_VDM_Crofer_22_APU.pdf . Sourceflow8976.1kg is treated as the interconnectplate package based on originalmanufacturingdiagram,not9tair-electrodecatalyst. AdoptCrofer22APU-type reference for THIS stackinput only; do not replace ordinaryBoP18/8heat exchangers. Preserve8976.1kgfinishedsteel and8976.1kgexistingrollingservice; mass derives labstackscaleup and is NOT independently validated industrialMWgeometry. Preserve priorLSM,PrNi,ceramics,stackreplacement andlearning. Reference alloy massfractions={'Cr': 0.22, 'Mn': 0.005, 'Ti': 0.001, 'La': 0.001, 'Si': 0.001, 'Al': 0.0005, 'Cu': 0.0005, 'C': 0.0001, 'P': 5e-05, 'S': 5e-05, 'Fe': 0.7708}. Midrange/lowresidual choices are explicit assumptions within publishedranges,not measured heat assay. No intentionalNi addition; unknownresidualNi/othertraceimpurities are NOT provenzero. ActualoldNi8% cannot be claimed quantitatively without suppliercomposition; compareold18/8 as sensitivity. Cr20-24,Mn0.3-0.8,La0.04-0.20wt% sensitivities. Fe usesunalloyedsteel as feed-gradeproxy,withitsownminoralloys unresolved; completecomponentmetaluse is not identical toelementalpureFe. Addalloyingmaterialsonce and0.5kWh+2MJ/kgremeltingreference (0.25-1kWh/1-4MJsensitivity),not a completeCrsteel production dataset on top. Matchfinishedsteelmass1kgwith100%finalalloyretention; alloyingyield/slag andtracepickup remain gaps. La metal unavailable: explicit netoxide/carbon electrolyticreference La2O3+1.5C-&gt;2La+1.5CO2,95%metalretention,10kWh/kg+3MJ/kgassumed; fluoridebathmakeup,PFCemissions,purification andcalcium-route alternatives unresolved. Thisisstoichiometricnetelectrolysis,NOTthermal carbothermic reduction orvalidatedvendorLa process. Metalrejectgenericinertdisposal; La/C/O/massclose. FinishedinterconnectEOLexistingsteelcollection amount retained; genericsteelroute doesnotvalidatealloy-specificrecycling orrecoverycredits. Native/YAML/runtime/primary-secondaryshares untouched.</t>
         </is>
       </c>
       <c r="K472" s="12"/>
@@ -16945,8 +16947,10 @@
       <c r="G473" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H473" s="11" t="s">
-        <v>154</v>
+      <c r="H473" s="11" t="inlineStr">
+        <is>
+          <t>APPROVED SOEC FERRITIC INTERCONNECT REFERENCE, issue95, 2026-10-18. Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1:chromiumsteelplate-&gt;deepdrawing+LSMcoating-&gt;interconnect; main stackdescription2outer3kg and4inner145g plates. Gerloff2021 PtM SI pS16 retains8976.1kg18/8steel but labels air-electrode. VDM Crofer22APU datasheet4146rev01 March2022 Table2 andApplications p5 explicitly SOEC interconnects/bipolarplates:Cr20-24wt%,Mn0.30-0.80,Ti0.03-0.20,La0.04-0.20,Fe balance. https://www.vdm-metals.com/fileadmin/user_upload/Downloads/Data_Sheets/Data_Sheet_VDM_Crofer_22_APU.pdf . Sourceflow8976.1kg is treated as the interconnectplate package based on originalmanufacturingdiagram,not9tair-electrodecatalyst. AdoptCrofer22APU-type reference for THIS stackinput only; do not replace ordinaryBoP18/8heat exchangers. Preserve8976.1kgfinishedsteel and8976.1kgexistingrollingservice; mass derives labstackscaleup and is NOT independently validated industrialMWgeometry. Preserve priorLSM,PrNi,ceramics,stackreplacement andlearning. Reference alloy massfractions={'Cr': 0.22, 'Mn': 0.005, 'Ti': 0.001, 'La': 0.001, 'Si': 0.001, 'Al': 0.0005, 'Cu': 0.0005, 'C': 0.0001, 'P': 5e-05, 'S': 5e-05, 'Fe': 0.7708}. Midrange/lowresidual choices are explicit assumptions within publishedranges,not measured heat assay. No intentionalNi addition; unknownresidualNi/othertraceimpurities are NOT provenzero. ActualoldNi8% cannot be claimed quantitatively without suppliercomposition; compareold18/8 as sensitivity. Cr20-24,Mn0.3-0.8,La0.04-0.20wt% sensitivities. Fe usesunalloyedsteel as feed-gradeproxy,withitsownminoralloys unresolved; completecomponentmetaluse is not identical toelementalpureFe. Addalloyingmaterialsonce and0.5kWh+2MJ/kgremeltingreference (0.25-1kWh/1-4MJsensitivity),not a completeCrsteel production dataset on top. Matchfinishedsteelmass1kgwith100%finalalloyretention; alloyingyield/slag andtracepickup remain gaps. La metal unavailable: explicit netoxide/carbon electrolyticreference La2O3+1.5C-&gt;2La+1.5CO2,95%metalretention,10kWh/kg+3MJ/kgassumed; fluoridebathmakeup,PFCemissions,purification andcalcium-route alternatives unresolved. Thisisstoichiometricnetelectrolysis,NOTthermal carbothermic reduction orvalidatedvendorLa process. Metalrejectgenericinertdisposal; La/C/O/massclose. FinishedinterconnectEOLexistingsteelcollection amount retained; genericsteelroute doesnotvalidatealloy-specificrecycling orrecoverycredits. Native/YAML/runtime/primary-secondaryshares untouched.</t>
+        </is>
       </c>
       <c r="J473"/>
       <c r="K473" s="19"/>
@@ -16959,14 +16963,18 @@
       <c r="R473"/>
     </row>
     <row r="474" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A474" s="11" t="s">
-        <v>20</v>
+      <c r="A474" s="11" t="inlineStr">
+        <is>
+          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+        </is>
       </c>
       <c r="B474" s="12">
         <v>8976.1</v>
       </c>
-      <c r="C474" s="11" t="s">
-        <v>17</v>
+      <c r="C474" s="11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D474" s="11" t="s">
         <v>13</v>
@@ -16974,11 +16982,15 @@
       <c r="F474" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G474" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H474" s="11" t="s">
-        <v>154</v>
+      <c r="G474" s="11" t="inlineStr">
+        <is>
+          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+        </is>
+      </c>
+      <c r="H474" s="11" t="inlineStr">
+        <is>
+          <t>APPROVED SOEC FERRITIC INTERCONNECT REFERENCE, issue95, 2026-10-18. Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1:chromiumsteelplate-&gt;deepdrawing+LSMcoating-&gt;interconnect; main stackdescription2outer3kg and4inner145g plates. Gerloff2021 PtM SI pS16 retains8976.1kg18/8steel but labels air-electrode. VDM Crofer22APU datasheet4146rev01 March2022 Table2 andApplications p5 explicitly SOEC interconnects/bipolarplates:Cr20-24wt%,Mn0.30-0.80,Ti0.03-0.20,La0.04-0.20,Fe balance. https://www.vdm-metals.com/fileadmin/user_upload/Downloads/Data_Sheets/Data_Sheet_VDM_Crofer_22_APU.pdf . Sourceflow8976.1kg is treated as the interconnectplate package based on originalmanufacturingdiagram,not9tair-electrodecatalyst. AdoptCrofer22APU-type reference for THIS stackinput only; do not replace ordinaryBoP18/8heat exchangers. Preserve8976.1kgfinishedsteel and8976.1kgexistingrollingservice; mass derives labstackscaleup and is NOT independently validated industrialMWgeometry. Preserve priorLSM,PrNi,ceramics,stackreplacement andlearning. Reference alloy massfractions={'Cr': 0.22, 'Mn': 0.005, 'Ti': 0.001, 'La': 0.001, 'Si': 0.001, 'Al': 0.0005, 'Cu': 0.0005, 'C': 0.0001, 'P': 5e-05, 'S': 5e-05, 'Fe': 0.7708}. Midrange/lowresidual choices are explicit assumptions within publishedranges,not measured heat assay. No intentionalNi addition; unknownresidualNi/othertraceimpurities are NOT provenzero. ActualoldNi8% cannot be claimed quantitatively without suppliercomposition; compareold18/8 as sensitivity. Cr20-24,Mn0.3-0.8,La0.04-0.20wt% sensitivities. Fe usesunalloyedsteel as feed-gradeproxy,withitsownminoralloys unresolved; completecomponentmetaluse is not identical toelementalpureFe. Addalloyingmaterialsonce and0.5kWh+2MJ/kgremeltingreference (0.25-1kWh/1-4MJsensitivity),not a completeCrsteel production dataset on top. Matchfinishedsteelmass1kgwith100%finalalloyretention; alloyingyield/slag andtracepickup remain gaps. La metal unavailable: explicit netoxide/carbon electrolyticreference La2O3+1.5C-&gt;2La+1.5CO2,95%metalretention,10kWh/kg+3MJ/kgassumed; fluoridebathmakeup,PFCemissions,purification andcalcium-route alternatives unresolved. Thisisstoichiometricnetelectrolysis,NOTthermal carbothermic reduction orvalidatedvendorLa process. Metalrejectgenericinertdisposal; La/C/O/massclose. FinishedinterconnectEOLexistingsteelcollection amount retained; genericsteelroute doesnotvalidatealloy-specificrecycling orrecoverycredits. Native/YAML/runtime/primary-secondaryshares untouched.</t>
+        </is>
       </c>
       <c r="J474"/>
       <c r="K474" s="19"/>
@@ -26231,6 +26243,1008 @@
       <c r="H844" t="inlineStr">
         <is>
           <t/>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B849">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1:chromiumsteelplate-&gt;deepdrawing+LSMcoating-&gt;interconnect; main stackdescription2outer3kg and4inner145g plates. Gerloff2021 PtM SI pS16 retains8976.1kg18/8steel but labels air-electrode. VDM Crofer22APU datasheet4146rev01 March2022 Table2 andApplications p5 explicitly SOEC interconnects/bipolarplates:Cr20-24wt%,Mn0.30-0.80,Ti0.03-0.20,La0.04-0.20,Fe balance. https://www.vdm-metals.com/fileadmin/user_upload/Downloads/Data_Sheets/Data_Sheet_VDM_Crofer_22_APU.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>APPROVED SOEC FERRITIC INTERCONNECT REFERENCE, issue95, 2026-10-18. Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1:chromiumsteelplate-&gt;deepdrawing+LSMcoating-&gt;interconnect; main stackdescription2outer3kg and4inner145g plates. Gerloff2021 PtM SI pS16 retains8976.1kg18/8steel but labels air-electrode. VDM Crofer22APU datasheet4146rev01 March2022 Table2 andApplications p5 explicitly SOEC interconnects/bipolarplates:Cr20-24wt%,Mn0.30-0.80,Ti0.03-0.20,La0.04-0.20,Fe balance. https://www.vdm-metals.com/fileadmin/user_upload/Downloads/Data_Sheets/Data_Sheet_VDM_Crofer_22_APU.pdf . Sourceflow8976.1kg is treated as the interconnectplate package based on originalmanufacturingdiagram,not9tair-electrodecatalyst. AdoptCrofer22APU-type reference for THIS stackinput only; do not replace ordinaryBoP18/8heat exchangers. Preserve8976.1kgfinishedsteel and8976.1kgexistingrollingservice; mass derives labstackscaleup and is NOT independently validated industrialMWgeometry. Preserve priorLSM,PrNi,ceramics,stackreplacement andlearning. Reference alloy massfractions={'Cr': 0.22, 'Mn': 0.005, 'Ti': 0.001, 'La': 0.001, 'Si': 0.001, 'Al': 0.0005, 'Cu': 0.0005, 'C': 0.0001, 'P': 5e-05, 'S': 5e-05, 'Fe': 0.7708}. Midrange/lowresidual choices are explicit assumptions within publishedranges,not measured heat assay. No intentionalNi addition; unknownresidualNi/othertraceimpurities are NOT provenzero. ActualoldNi8% cannot be claimed quantitatively without suppliercomposition; compareold18/8 as sensitivity. Cr20-24,Mn0.3-0.8,La0.04-0.20wt% sensitivities. Fe usesunalloyedsteel as feed-gradeproxy,withitsownminoralloys unresolved; completecomponentmetaluse is not identical toelementalpureFe. Addalloyingmaterialsonce and0.5kWh+2MJ/kgremeltingreference (0.25-1kWh/1-4MJsensitivity),not a completeCrsteel production dataset on top. Matchfinishedsteelmass1kgwith100%finalalloyretention; alloyingyield/slag andtracepickup remain gaps. La metal unavailable: explicit netoxide/carbon electrolyticreference La2O3+1.5C-&gt;2La+1.5CO2,95%metalretention,10kWh/kg+3MJ/kgassumed; fluoridebathmakeup,PFCemissions,purification andcalcium-route alternatives unresolved. Thisisstoichiometricnetelectrolysis,NOTthermal carbothermic reduction orvalidatedvendorLa process. Metalrejectgenericinertdisposal; La/C/O/massclose. FinishedinterconnectEOLexistingsteelcollection amount retained; genericsteelroute doesnotvalidatealloy-specificrecycling orrecoverycredits. Native/YAML/runtime/primary-secondaryshares untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+        </is>
+      </c>
+      <c r="B856">
+        <v>1</v>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>market for lanthanum oxide</t>
+        </is>
+      </c>
+      <c r="B857">
+        <v>1.234493235996356</v>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>lanthanum oxide</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>lanthanum oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>market for graphite</t>
+        </is>
+      </c>
+      <c r="B858">
+        <v>0.0682649028944118</v>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B859">
+        <v>10</v>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B860">
+        <v>3</v>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B861">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, fossil</t>
+        </is>
+      </c>
+      <c r="B862">
+        <v>0.2501265599433993</v>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B867">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1:chromiumsteelplate-&gt;deepdrawing+LSMcoating-&gt;interconnect; main stackdescription2outer3kg and4inner145g plates. Gerloff2021 PtM SI pS16 retains8976.1kg18/8steel but labels air-electrode. VDM Crofer22APU datasheet4146rev01 March2022 Table2 andApplications p5 explicitly SOEC interconnects/bipolarplates:Cr20-24wt%,Mn0.30-0.80,Ti0.03-0.20,La0.04-0.20,Fe balance. https://www.vdm-metals.com/fileadmin/user_upload/Downloads/Data_Sheets/Data_Sheet_VDM_Crofer_22_APU.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>APPROVED SOEC FERRITIC INTERCONNECT REFERENCE, issue95, 2026-10-18. Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1:chromiumsteelplate-&gt;deepdrawing+LSMcoating-&gt;interconnect; main stackdescription2outer3kg and4inner145g plates. Gerloff2021 PtM SI pS16 retains8976.1kg18/8steel but labels air-electrode. VDM Crofer22APU datasheet4146rev01 March2022 Table2 andApplications p5 explicitly SOEC interconnects/bipolarplates:Cr20-24wt%,Mn0.30-0.80,Ti0.03-0.20,La0.04-0.20,Fe balance. https://www.vdm-metals.com/fileadmin/user_upload/Downloads/Data_Sheets/Data_Sheet_VDM_Crofer_22_APU.pdf . Sourceflow8976.1kg is treated as the interconnectplate package based on originalmanufacturingdiagram,not9tair-electrodecatalyst. AdoptCrofer22APU-type reference for THIS stackinput only; do not replace ordinaryBoP18/8heat exchangers. Preserve8976.1kgfinishedsteel and8976.1kgexistingrollingservice; mass derives labstackscaleup and is NOT independently validated industrialMWgeometry. Preserve priorLSM,PrNi,ceramics,stackreplacement andlearning. Reference alloy massfractions={'Cr': 0.22, 'Mn': 0.005, 'Ti': 0.001, 'La': 0.001, 'Si': 0.001, 'Al': 0.0005, 'Cu': 0.0005, 'C': 0.0001, 'P': 5e-05, 'S': 5e-05, 'Fe': 0.7708}. Midrange/lowresidual choices are explicit assumptions within publishedranges,not measured heat assay. No intentionalNi addition; unknownresidualNi/othertraceimpurities are NOT provenzero. ActualoldNi8% cannot be claimed quantitatively without suppliercomposition; compareold18/8 as sensitivity. Cr20-24,Mn0.3-0.8,La0.04-0.20wt% sensitivities. Fe usesunalloyedsteel as feed-gradeproxy,withitsownminoralloys unresolved; completecomponentmetaluse is not identical toelementalpureFe. Addalloyingmaterialsonce and0.5kWh+2MJ/kgremeltingreference (0.25-1kWh/1-4MJsensitivity),not a completeCrsteel production dataset on top. Matchfinishedsteelmass1kgwith100%finalalloyretention; alloyingyield/slag andtracepickup remain gaps. La metal unavailable: explicit netoxide/carbon electrolyticreference La2O3+1.5C-&gt;2La+1.5CO2,95%metalretention,10kWh/kg+3MJ/kgassumed; fluoridebathmakeup,PFCemissions,purification andcalcium-route alternatives unresolved. Thisisstoichiometricnetelectrolysis,NOTthermal carbothermic reduction orvalidatedvendorLa process. Metalrejectgenericinertdisposal; La/C/O/massclose. FinishedinterconnectEOLexistingsteelcollection amount retained; genericsteelroute doesnotvalidatealloy-specificrecycling orrecoverycredits. Native/YAML/runtime/primary-secondaryshares untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+        </is>
+      </c>
+      <c r="B874">
+        <v>1</v>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>market for chromium</t>
+        </is>
+      </c>
+      <c r="B875">
+        <v>0.22</v>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>market for manganese</t>
+        </is>
+      </c>
+      <c r="B876">
+        <v>0.005</v>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>manganese</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>manganese</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>market for titanium</t>
+        </is>
+      </c>
+      <c r="B877">
+        <v>0.001</v>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>titanium</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>titanium</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+        </is>
+      </c>
+      <c r="B878">
+        <v>0.001</v>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>market for silicon, metallurgical grade</t>
+        </is>
+      </c>
+      <c r="B879">
+        <v>0.001</v>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>silicon, metallurgical grade</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>silicon, metallurgical grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B880">
+        <v>0.0005</v>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B881">
+        <v>0.0005</v>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>market for graphite</t>
+        </is>
+      </c>
+      <c r="B882">
+        <v>0.0001</v>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B883">
+        <v>5e-05</v>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>market for sulfur</t>
+        </is>
+      </c>
+      <c r="B884">
+        <v>5e-05</v>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>sulfur</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>sulfur</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>market for steel, unalloyed</t>
+        </is>
+      </c>
+      <c r="B885">
+        <v>0.7708</v>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>steel, unalloyed</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>steel, unalloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B886">
+        <v>0.5</v>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B887">
+        <v>2</v>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U887"/>
+  <dimension ref="A1:U908"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -12195,8 +12195,12 @@
       <c r="A305" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B305" s="14" t="s">
-        <v>129</v>
+      <c r="B305" s="14" t="inlineStr">
+        <is>
+          <t>APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 MWe Alkaline electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Single stack lifetime of 7-8 years @ 8000 hours/year, hence 3 replacements over 20 years. Produced amount of H2 over 20 years: 3085961.12 kg. The technology is available for large plant sizes and operates with a stack efficiency of up to 67 % (based on the lower heating value (LHV) of the generated H2). The operating temperature is in between 60–80 °C, and the current density is around 0.2–0.4 A/cm2. Moreover, the system energy –including the stack and periphery energy– is in the range of 4.4–6.6 kWh/m3H2, while the gas purity is higher than 99.5%, and the operating pressure is below 30 bar. While the LCI data of the BoP components either originate from Zhang et al., based on a 300-kW system and, therefore, scaled-up to 1 MW by a factor of 0.7, the LCI data of the other BoP components originate from manufacturer offers or have been estimated by own calculations using additional information by the producers.  Values have already been multiplied by 3 to reflect 2 stack replacements over 20 years of use.</t>
+        </is>
       </c>
       <c r="K305" s="12"/>
       <c r="L305" s="12"/>
@@ -12327,6 +12331,11 @@
         <f>B306</f>
         <v>electrolyzer, 1MWe, AEC, Stack</v>
       </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.</t>
+        </is>
+      </c>
       <c r="K311" s="12"/>
       <c r="L311" s="12"/>
       <c r="M311" s="12"/>
@@ -12463,14 +12472,18 @@
       <c r="R315"/>
     </row>
     <row r="316" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A316" s="11" t="s">
-        <v>133</v>
+      <c r="A316" s="11" t="inlineStr">
+        <is>
+          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+        </is>
       </c>
       <c r="B316" s="12">
-        <v>48.8</v>
-      </c>
-      <c r="C316" s="11" t="s">
-        <v>17</v>
+        <v>121.8</v>
+      </c>
+      <c r="C316" s="11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D316" s="11" t="s">
         <v>13</v>
@@ -12479,11 +12492,15 @@
       <c r="F316" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G316" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="H316" s="11" t="s">
-        <v>135</v>
+      <c r="G316" s="10" t="inlineStr">
+        <is>
+          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+        </is>
+      </c>
+      <c r="H316" s="11" t="inlineStr">
+        <is>
+          <t>APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.</t>
+        </is>
       </c>
       <c r="J316"/>
       <c r="K316" s="19"/>
@@ -12496,28 +12513,14 @@
       <c r="R316"/>
     </row>
     <row r="317" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A317" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B317" s="12">
-        <v>73</v>
-      </c>
-      <c r="C317" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D317" s="11" t="s">
-        <v>13</v>
-      </c>
+      <c r="A317" s="11"/>
+      <c r="B317" s="12"/>
+      <c r="C317" s="11"/>
+      <c r="D317" s="11"/>
       <c r="E317" s="10"/>
-      <c r="F317" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G317" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H317" s="11" t="s">
-        <v>135</v>
-      </c>
+      <c r="F317" s="11"/>
+      <c r="G317" s="10"/>
+      <c r="H317" s="11"/>
       <c r="J317"/>
       <c r="K317" s="19"/>
       <c r="L317" s="19"/>
@@ -12604,8 +12607,12 @@
       <c r="A322" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B322" s="14" t="s">
-        <v>56</v>
+      <c r="B322" s="14" t="inlineStr">
+        <is>
+          <t>APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+1 MW PEM electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years per single stack, @ 8000 hours/year. Iridium mining process is NOT from ecoinvent. Produced amount of H2 over 20 years: 2964315.35 kg. According to a study called IndWEDe, it is assumed that the stacks are replaced 3 times during the 20 years lifespan, based on the 2030’s scenario for 1 MW systems which predicts a lifetime of 50,000 h or more for the stacks of the different water electrolysis technologies. In comparison to AEC electrolyzers, PEMEC electrolyzers are less mature. Furthermore, the PEMEC technology is commercially available and operates with a similar system efficiency as the AEC technology. However, the current density and the gas purity are higher with values in between 0.6–2.0 A/cm2 and &gt; 99.99%, respectively. Besides this, the operating pressure (below 200 bar) is significantly higher in comparison to AEC systems, while the operating temperature (50 °C to 80 °C) and the system energy (4.2–6.6 kWh/m3H2) are similar to AEC systems. The PEMEC BoP and stack components data stem from Bareiß et al. and correspond to a 1 MW system. Moreover, some further BoP components like water purifier &amp; feed tank, buffer tank, and heat exchanger have been added, derived from a 300 kW AEC system, under the assumption that the components are also suitable for a PEMEC system. The values have been scaled up from 300 kW to 1 MW. Values have already been multiplied by 3 to reflect 2 stack replacements over 20 years of use.</t>
+        </is>
       </c>
       <c r="K322" s="12"/>
       <c r="L322" s="12"/>
@@ -12736,6 +12743,11 @@
         <f>B323</f>
         <v>used electrolyzer stack, 1MWe, AEC</v>
       </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.</t>
+        </is>
+      </c>
       <c r="K328" s="12"/>
       <c r="L328" s="12"/>
       <c r="M328" s="12"/>
@@ -12778,8 +12790,8 @@
         <v>210</v>
       </c>
       <c r="B330" s="11">
-        <f>-1*SUM(B312,B316)</f>
-        <v>-193</v>
+        <f>-185.52202907132846</f>
+        <v>-185.52202907132846</v>
       </c>
       <c r="C330" s="11" t="s">
         <v>212</v>
@@ -12792,6 +12804,11 @@
       </c>
       <c r="G330" s="11" t="s">
         <v>211</v>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.</t>
+        </is>
       </c>
       <c r="J330"/>
       <c r="K330" s="19"/>
@@ -12804,7 +12821,39 @@
       <c r="R330"/>
     </row>
     <row r="331" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B331" s="16"/>
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B331" s="16">
+        <v>-80.47797092867151</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.</t>
+        </is>
+      </c>
       <c r="K331" s="12"/>
       <c r="L331" s="12"/>
       <c r="M331" s="12"/>
@@ -27245,6 +27294,492 @@
       <c r="I887" t="inlineStr">
         <is>
           <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B892">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+        </is>
+      </c>
+      <c r="B899">
+        <v>1</v>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>market for zirconium oxide</t>
+        </is>
+      </c>
+      <c r="B900">
+        <v>0.6955143974476841</v>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>zirconium oxide</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>zirconium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>market for polysulfone</t>
+        </is>
+      </c>
+      <c r="B901">
+        <v>0.12273783484370895</v>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>polysulfone</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>polysulfone</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>market for polyphenylene sulfide</t>
+        </is>
+      </c>
+      <c r="B902">
+        <v>0.22266037932317662</v>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>polyphenylene sulfide</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>polyphenylene sulfide</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>market for N-methyl-2-pyrrolidone</t>
+        </is>
+      </c>
+      <c r="B903">
+        <v>0.1554679241353647</v>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>N-methyl-2-pyrrolidone</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>N-methyl-2-pyrrolidone</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>market for spent solvent mixture</t>
+        </is>
+      </c>
+      <c r="B904">
+        <v>-0.1554679241353647</v>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>spent solvent mixture</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>spent solvent mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B905">
+        <v>-0.040912611614569605</v>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>market for tap water</t>
+        </is>
+      </c>
+      <c r="B906">
+        <v>10</v>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B907">
+        <v>-0.01</v>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B908">
+        <v>1</v>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U908"/>
+  <dimension ref="A1:U1178"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -9239,7 +9239,9 @@
       </c>
       <c r="B204" s="14" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -9375,7 +9377,11 @@
         <f>B205</f>
         <v>electrolyzer, 1MWe, PEM, Balance of Plant</v>
       </c>
-      <c r="H210" s="10"/>
+      <c r="H210" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
       <c r="I210" s="10"/>
       <c r="K210" s="12"/>
       <c r="L210" s="12"/>
@@ -10145,26 +10151,38 @@
       <c r="R236"/>
     </row>
     <row r="237" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A237" s="11" t="s">
-        <v>18</v>
+      <c r="A237" s="11" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
       </c>
       <c r="B237" s="16">
-        <v>60</v>
-      </c>
-      <c r="C237" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D237" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F237" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G237" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H237" s="10" t="s">
-        <v>107</v>
+        <v>1</v>
+      </c>
+      <c r="C237" s="11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D237" s="11" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F237" s="11" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G237" s="11" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+      <c r="H237" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
       </c>
       <c r="J237"/>
       <c r="K237" s="19"/>
@@ -10177,27 +10195,13 @@
       <c r="R237"/>
     </row>
     <row r="238" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A238" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B238" s="16">
-        <v>45</v>
-      </c>
-      <c r="C238" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D238" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F238" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G238" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H238" s="10" t="s">
-        <v>107</v>
-      </c>
+      <c r="A238" s="11"/>
+      <c r="B238" s="16"/>
+      <c r="C238" s="11"/>
+      <c r="D238" s="11"/>
+      <c r="F238" s="11"/>
+      <c r="G238" s="11"/>
+      <c r="H238" s="10"/>
       <c r="J238"/>
       <c r="K238" s="19"/>
       <c r="L238" s="19"/>
@@ -10209,27 +10213,13 @@
       <c r="R238"/>
     </row>
     <row r="239" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A239" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B239" s="16">
-        <v>180</v>
-      </c>
-      <c r="C239" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D239" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F239" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G239" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H239" s="10" t="s">
-        <v>107</v>
-      </c>
+      <c r="A239" s="11"/>
+      <c r="B239" s="16"/>
+      <c r="C239" s="11"/>
+      <c r="D239" s="11"/>
+      <c r="F239" s="11"/>
+      <c r="G239" s="11"/>
+      <c r="H239" s="10"/>
       <c r="J239"/>
       <c r="K239" s="19"/>
       <c r="L239" s="19"/>
@@ -10241,27 +10231,13 @@
       <c r="R239"/>
     </row>
     <row r="240" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A240" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B240" s="16">
-        <v>15</v>
-      </c>
-      <c r="C240" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D240" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F240" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G240" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="H240" s="10" t="s">
-        <v>107</v>
-      </c>
+      <c r="A240" s="11"/>
+      <c r="B240" s="16"/>
+      <c r="C240" s="11"/>
+      <c r="D240" s="11"/>
+      <c r="F240" s="11"/>
+      <c r="G240" s="11"/>
+      <c r="H240" s="10"/>
       <c r="J240"/>
       <c r="K240" s="19"/>
       <c r="L240" s="19"/>
@@ -10273,27 +10249,13 @@
       <c r="R240"/>
     </row>
     <row r="241" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A241" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B241" s="16">
-        <v>45</v>
-      </c>
-      <c r="C241" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D241" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F241" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G241" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="H241" s="10" t="s">
-        <v>107</v>
-      </c>
+      <c r="A241" s="11"/>
+      <c r="B241" s="16"/>
+      <c r="C241" s="11"/>
+      <c r="D241" s="11"/>
+      <c r="F241" s="11"/>
+      <c r="G241" s="11"/>
+      <c r="H241" s="10"/>
       <c r="J241"/>
       <c r="K241" s="19"/>
       <c r="L241" s="19"/>
@@ -10891,7 +10853,9 @@
       </c>
       <c r="B262" s="14" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 1 MW PEM electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years per single stack, @ 8000 hours/year. Iridium mining process is NOT from ecoinvent. Produced amount of H2 over 20 years: 2964315.35 kg. According to a study called IndWEDe, it is assumed that the stacks are replaced 3 times during the 20 years lifespan, based on the 2030’s scenario for 1 MW systems which predicts a lifetime of 50,000 h or more for the stacks of the different water electrolysis technologies. In comparison to AEC electrolyzers, PEMEC electrolyzers are less mature. Furthermore, the PEMEC technology is commercially available and operates with a similar system efficiency as the AEC technology. However, the current density and the gas purity are higher with values in between 0.6–2.0 A/cm2 and &gt; 99.99%, respectively. Besides this, the operating pressure (below 200 bar) is significantly higher in comparison to AEC systems, while the operating temperature (50 °C to 80 °C) and the system energy (4.2–6.6 kWh/m3H2) are similar to AEC systems. The PEMEC BoP and stack components data stem from Bareiß et al. and correspond to a 1 MW system. Moreover, some further BoP components like water purifier &amp; feed tank, buffer tank, and heat exchanger have been added, derived from a 300 kW AEC system, under the assumption that the components are also suitable for a PEMEC system. The values have been scaled up from 300 kW to 1 MW. Values have already been multiplied by 3 to reflect 2 stack replacements over 20 years of use.</t>
         </is>
@@ -11025,6 +10989,11 @@
         <f>B263</f>
         <v>used electrolyzer balance of plant, 1MWe, PEM</v>
       </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
       <c r="K268" s="12"/>
       <c r="L268" s="12"/>
       <c r="M268" s="12"/>
@@ -11067,7 +11036,7 @@
         <v>449</v>
       </c>
       <c r="B270" s="11">
-        <v>-2712</v>
+        <v>-2532</v>
       </c>
       <c r="C270" s="11" t="s">
         <v>217</v>
@@ -11083,7 +11052,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="J270"/>
@@ -11101,7 +11070,7 @@
         <v>206</v>
       </c>
       <c r="B271" s="11">
-        <v>-160</v>
+        <v>-100</v>
       </c>
       <c r="C271" s="11" t="s">
         <v>37</v>
@@ -11117,7 +11086,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="J271"/>
@@ -11280,7 +11249,7 @@
         <v>208</v>
       </c>
       <c r="B277" s="11">
-        <v>-145</v>
+        <v>-100</v>
       </c>
       <c r="C277" s="11" t="s">
         <v>37</v>
@@ -11296,7 +11265,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="J277"/>
@@ -11314,7 +11283,7 @@
         <v>210</v>
       </c>
       <c r="B278" s="11">
-        <v>-47</v>
+        <v>-32</v>
       </c>
       <c r="C278" s="11" t="s">
         <v>212</v>
@@ -11330,7 +11299,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="J278"/>
@@ -11404,7 +11373,7 @@
     <row r="281" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A281" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
         </is>
       </c>
       <c r="B281" s="16">
@@ -11427,12 +11396,12 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="K281" s="12"/>
@@ -12895,7 +12864,9 @@
       </c>
       <c r="B334" s="14" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -13031,7 +13002,11 @@
         <f>B335</f>
         <v>electrolyzer, 1MWe, AEC, Balance of Plant</v>
       </c>
-      <c r="H340" s="10"/>
+      <c r="H340" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
       <c r="I340" s="10"/>
       <c r="J340" s="10"/>
       <c r="K340" s="12"/>
@@ -13514,26 +13489,38 @@
       <c r="R357"/>
     </row>
     <row r="358" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A358" s="11" t="s">
-        <v>18</v>
+      <c r="A358" s="11" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
       </c>
       <c r="B358" s="16">
-        <v>60</v>
-      </c>
-      <c r="C358" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D358" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F358" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G358" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H358" s="10" t="s">
-        <v>107</v>
+        <v>1</v>
+      </c>
+      <c r="C358" s="11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D358" s="11" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F358" s="11" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G358" s="11" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+      <c r="H358" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
       </c>
       <c r="J358"/>
       <c r="K358" s="19"/>
@@ -13546,27 +13533,13 @@
       <c r="R358"/>
     </row>
     <row r="359" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A359" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B359" s="16">
-        <v>45</v>
-      </c>
-      <c r="C359" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D359" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F359" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G359" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H359" s="10" t="s">
-        <v>107</v>
-      </c>
+      <c r="A359" s="11"/>
+      <c r="B359" s="16"/>
+      <c r="C359" s="11"/>
+      <c r="D359" s="11"/>
+      <c r="F359" s="11"/>
+      <c r="G359" s="11"/>
+      <c r="H359" s="10"/>
       <c r="J359"/>
       <c r="K359" s="19"/>
       <c r="L359" s="19"/>
@@ -13578,27 +13551,13 @@
       <c r="R359"/>
     </row>
     <row r="360" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A360" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B360" s="16">
-        <v>180</v>
-      </c>
-      <c r="C360" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D360" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F360" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G360" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H360" s="10" t="s">
-        <v>107</v>
-      </c>
+      <c r="A360" s="11"/>
+      <c r="B360" s="16"/>
+      <c r="C360" s="11"/>
+      <c r="D360" s="11"/>
+      <c r="F360" s="11"/>
+      <c r="G360" s="11"/>
+      <c r="H360" s="10"/>
       <c r="J360"/>
       <c r="K360" s="19"/>
       <c r="L360" s="19"/>
@@ -13610,27 +13569,13 @@
       <c r="R360"/>
     </row>
     <row r="361" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A361" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B361" s="16">
-        <v>15</v>
-      </c>
-      <c r="C361" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D361" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F361" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G361" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="H361" s="10" t="s">
-        <v>107</v>
-      </c>
+      <c r="A361" s="11"/>
+      <c r="B361" s="16"/>
+      <c r="C361" s="11"/>
+      <c r="D361" s="11"/>
+      <c r="F361" s="11"/>
+      <c r="G361" s="11"/>
+      <c r="H361" s="10"/>
       <c r="J361"/>
       <c r="K361" s="19"/>
       <c r="L361" s="19"/>
@@ -13642,27 +13587,13 @@
       <c r="R361"/>
     </row>
     <row r="362" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A362" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B362" s="16">
-        <v>45</v>
-      </c>
-      <c r="C362" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D362" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F362" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G362" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="H362" s="10" t="s">
-        <v>107</v>
-      </c>
+      <c r="A362" s="11"/>
+      <c r="B362" s="16"/>
+      <c r="C362" s="11"/>
+      <c r="D362" s="11"/>
+      <c r="F362" s="11"/>
+      <c r="G362" s="11"/>
+      <c r="H362" s="10"/>
       <c r="J362"/>
       <c r="K362" s="19"/>
       <c r="L362" s="19"/>
@@ -14905,7 +14836,9 @@
       </c>
       <c r="B403" s="14" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 1 MW PEM electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years per single stack, @ 8000 hours/year. Iridium mining process is NOT from ecoinvent. Produced amount of H2 over 20 years: 2964315.35 kg. According to a study called IndWEDe, it is assumed that the stacks are replaced 3 times during the 20 years lifespan, based on the 2030’s scenario for 1 MW systems which predicts a lifetime of 50,000 h or more for the stacks of the different water electrolysis technologies. In comparison to AEC electrolyzers, PEMEC electrolyzers are less mature. Furthermore, the PEMEC technology is commercially available and operates with a similar system efficiency as the AEC technology. However, the current density and the gas purity are higher with values in between 0.6–2.0 A/cm2 and &gt; 99.99%, respectively. Besides this, the operating pressure (below 200 bar) is significantly higher in comparison to AEC systems, while the operating temperature (50 °C to 80 °C) and the system energy (4.2–6.6 kWh/m3H2) are similar to AEC systems. The PEMEC BoP and stack components data stem from Bareiß et al. and correspond to a 1 MW system. Moreover, some further BoP components like water purifier &amp; feed tank, buffer tank, and heat exchanger have been added, derived from a 300 kW AEC system, under the assumption that the components are also suitable for a PEMEC system. The values have been scaled up from 300 kW to 1 MW. Values have already been multiplied by 3 to reflect 2 stack replacements over 20 years of use.</t>
         </is>
@@ -15039,6 +14972,11 @@
         <f>B404</f>
         <v>used electrolyzer balance of plant, 1MWe, AEC</v>
       </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
       <c r="K409" s="12"/>
       <c r="L409" s="12"/>
       <c r="M409" s="12"/>
@@ -15080,7 +15018,7 @@
         <v>449</v>
       </c>
       <c r="B411" s="11">
-        <v>-4534.4</v>
+        <v>-4354.4</v>
       </c>
       <c r="C411" s="11" t="s">
         <v>217</v>
@@ -15096,7 +15034,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="J411"/>
@@ -15114,7 +15052,7 @@
         <v>206</v>
       </c>
       <c r="B412" s="11">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="C412" s="11" t="s">
         <v>37</v>
@@ -15130,7 +15068,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="J412"/>
@@ -15293,7 +15231,7 @@
         <v>208</v>
       </c>
       <c r="B418" s="11">
-        <v>-417</v>
+        <v>-372</v>
       </c>
       <c r="C418" s="11" t="s">
         <v>37</v>
@@ -15309,7 +15247,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="J418"/>
@@ -15327,7 +15265,7 @@
         <v>210</v>
       </c>
       <c r="B419" s="11">
-        <v>-108</v>
+        <v>-93</v>
       </c>
       <c r="C419" s="11" t="s">
         <v>212</v>
@@ -15343,7 +15281,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="J419"/>
@@ -15388,7 +15326,7 @@
     <row r="421" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A421" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
         </is>
       </c>
       <c r="B421" s="16">
@@ -15411,12 +15349,12 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="K421" s="12"/>
@@ -17780,7 +17718,9 @@
       </c>
       <c r="B503" s="14" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ELECTROLYZER CONTROL-ASSEMBLY COVERAGE CLARIFICATION, issue92, 2026-10-18. Bareiss et al.2019 DOI10.1016/j.apenergy.2019.01.001 Sec3.2.2 states100kgGROSScontrolelectronicsper1MW;Gerloff2021componentmapping;ecoinventindustrial electronicsproductionforcontrolunits documents46%steelhousing32%plastics14%mountedboards8%cables. CriticalauditofactualsupplierconfirmsitALREADYincludessteelhousing,plastics,circuitboardsandcables.The100kginputisNOT100kgofbarecircuitboards,andthemasswasnotshownwrong. Retaintheexistingmarketforelectronicsforcontrolunitsat100kgineachPEM/AEC/SOECBoP;documentitsactualassemblyboundaryinsteadofinventingametalreductionoraddinganothercabinet. Ecoinvent3.9RER/RoWrecipesper100kgassemblyinclude46kgsteelfeed+rolling,32.193kgHDPEgrossfeed+32kginjectionmoulding,14kgmountedPCB(7kgPbcontainingand7kgPbfree,halfsurface/halfthroughhole),3.2kgribboncable+12.3mcomputerconnectorcable+111mnetworkcable,andoriginalboardfacility. Source8%nominalcablemassmustNOTbesummedwithmetresaskg;completecableproviderssupplyCu/plastics. NoadditionalPCB,connector,preciousmetalorsteelenclosureon topofcompleteexistingassembly. Thedescriptive32%plasticsisnominal;retainactual32.193kggrossfeed,notblanketnormalization. Retainnativecurrent-versionrecipesandmarkets,dynamicallyresolvedbypremise. Validationofalocal3.9recipecopyrevealed3.12GLO-HDPE migrationwouldalterregionalplasticsourcingrelative tocurrentnativecontrolunits;thatcopywasrejectedandNOnewlocalcontrolprovidersareintroduced. Thusalloriginalamounts,provideridentities,regionalshares,freight,facilityandutilitiesremainunchangedacrossversions,notjustthedeclaredtotalmass. ExistingBoPassemblyelectricityalreadycoversfinalassembly;doNOTaddanextraassembly-energyallowance. Genericindustrialcontrolarchitectureis a legacyestimatedassembly,notmanufacturercertifiedelectrolyzerpanel;actualI/Ocounts,HMI,safetyPLC,boardmetallizationandtraceAu/Pd/Ta remainreference-designgaps. Thisitemcorrectstheinterpretationanddocumentscoverage;itdoesNOTclaimanumericalmetalcorrectionorfullqualifiedcontrolsystemdesign. Item93scopesconverterinternalgate/controlboardsseparatelyfromthisplant-levelcabinet;existingcontrolsareincludedonce. ExistingmatchingEOL14kgboards/32kgindustrialplastic/8kgcablesretained;thisdoesnotvalidateotherBoPwastecoefficients. Lifetimesandserviceallocationunchanged. Onlyactivity/exchangecommentsmodified;no native/globalmarket,runtime,YAMLorprimary-secondarysharechanges.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -17916,7 +17856,11 @@
         <f>B504</f>
         <v>electrolyzer, 1MWe, SOEC, Balance of Plant</v>
       </c>
-      <c r="H509" s="10"/>
+      <c r="H509" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
       <c r="I509" s="10"/>
       <c r="J509" s="10"/>
       <c r="K509" s="12"/>
@@ -17991,26 +17935,38 @@
       <c r="R511"/>
     </row>
     <row r="512" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A512" s="16" t="s">
-        <v>18</v>
+      <c r="A512" s="16" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
       </c>
       <c r="B512" s="16">
-        <v>300</v>
-      </c>
-      <c r="C512" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D512" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F512" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G512" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H512" s="10" t="s">
-        <v>182</v>
+        <v>1</v>
+      </c>
+      <c r="C512" s="11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D512" s="11" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F512" s="11" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G512" s="16" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+      <c r="H512" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
       </c>
       <c r="J512"/>
       <c r="K512" s="19"/>
@@ -18023,27 +17979,13 @@
       <c r="R512"/>
     </row>
     <row r="513" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A513" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B513" s="16">
-        <v>225</v>
-      </c>
-      <c r="C513" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D513" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F513" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G513" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="H513" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="A513" s="16"/>
+      <c r="B513" s="16"/>
+      <c r="C513" s="11"/>
+      <c r="D513" s="11"/>
+      <c r="F513" s="11"/>
+      <c r="G513" s="16"/>
+      <c r="H513" s="10"/>
       <c r="J513"/>
       <c r="K513" s="19"/>
       <c r="L513" s="19"/>
@@ -18055,28 +17997,13 @@
       <c r="R513"/>
     </row>
     <row r="514" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A514" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B514" s="16">
-        <f>180*5</f>
-        <v>900</v>
-      </c>
-      <c r="C514" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D514" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F514" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G514" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H514" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="A514" s="16"/>
+      <c r="B514" s="16"/>
+      <c r="C514" s="11"/>
+      <c r="D514" s="11"/>
+      <c r="F514" s="11"/>
+      <c r="G514" s="16"/>
+      <c r="H514" s="10"/>
       <c r="J514"/>
       <c r="K514" s="19"/>
       <c r="L514" s="19"/>
@@ -18088,28 +18015,13 @@
       <c r="R514"/>
     </row>
     <row r="515" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A515" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B515" s="16">
-        <f>15*5</f>
-        <v>75</v>
-      </c>
-      <c r="C515" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D515" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F515" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G515" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="H515" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="A515" s="16"/>
+      <c r="B515" s="16"/>
+      <c r="C515" s="11"/>
+      <c r="D515" s="11"/>
+      <c r="F515" s="11"/>
+      <c r="G515" s="16"/>
+      <c r="H515" s="10"/>
       <c r="J515"/>
       <c r="K515" s="19"/>
       <c r="L515" s="19"/>
@@ -18121,28 +18033,13 @@
       <c r="R515"/>
     </row>
     <row r="516" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A516" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B516" s="16">
-        <f>45*5</f>
-        <v>225</v>
-      </c>
-      <c r="C516" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D516" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F516" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G516" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="H516" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="A516" s="16"/>
+      <c r="B516" s="16"/>
+      <c r="C516" s="11"/>
+      <c r="D516" s="11"/>
+      <c r="F516" s="11"/>
+      <c r="G516" s="16"/>
+      <c r="H516" s="10"/>
       <c r="J516"/>
       <c r="K516" s="19"/>
       <c r="L516" s="19"/>
@@ -19355,27 +19252,13 @@
       <c r="R555"/>
     </row>
     <row r="556" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A556" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B556" s="16">
-        <v>1</v>
-      </c>
-      <c r="C556" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D556" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F556" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G556" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H556" s="10" t="s">
-        <v>197</v>
-      </c>
+      <c r="A556" s="16"/>
+      <c r="B556" s="16"/>
+      <c r="C556" s="11"/>
+      <c r="D556" s="11"/>
+      <c r="F556" s="11"/>
+      <c r="G556" s="16"/>
+      <c r="H556" s="10"/>
       <c r="J556"/>
       <c r="K556" s="19"/>
       <c r="L556" s="19"/>
@@ -19387,27 +19270,13 @@
       <c r="R556"/>
     </row>
     <row r="557" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A557" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B557" s="16">
-        <v>0.7</v>
-      </c>
-      <c r="C557" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D557" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F557" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G557" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="H557" s="10" t="s">
-        <v>197</v>
-      </c>
+      <c r="A557" s="16"/>
+      <c r="B557" s="16"/>
+      <c r="C557" s="11"/>
+      <c r="D557" s="11"/>
+      <c r="F557" s="11"/>
+      <c r="G557" s="16"/>
+      <c r="H557" s="10"/>
       <c r="J557"/>
       <c r="K557" s="19"/>
       <c r="L557" s="19"/>
@@ -19419,27 +19288,13 @@
       <c r="R557"/>
     </row>
     <row r="558" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A558" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B558" s="16">
-        <v>3</v>
-      </c>
-      <c r="C558" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D558" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F558" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G558" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="H558" s="10" t="s">
-        <v>197</v>
-      </c>
+      <c r="A558" s="16"/>
+      <c r="B558" s="16"/>
+      <c r="C558" s="11"/>
+      <c r="D558" s="11"/>
+      <c r="F558" s="11"/>
+      <c r="G558" s="16"/>
+      <c r="H558" s="10"/>
       <c r="J558"/>
       <c r="K558" s="19"/>
       <c r="L558" s="19"/>
@@ -19451,27 +19306,13 @@
       <c r="R558"/>
     </row>
     <row r="559" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A559" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B559" s="16">
-        <v>0.2</v>
-      </c>
-      <c r="C559" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D559" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F559" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G559" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="H559" s="10" t="s">
-        <v>197</v>
-      </c>
+      <c r="A559" s="16"/>
+      <c r="B559" s="16"/>
+      <c r="C559" s="11"/>
+      <c r="D559" s="11"/>
+      <c r="F559" s="11"/>
+      <c r="G559" s="16"/>
+      <c r="H559" s="10"/>
       <c r="J559"/>
       <c r="K559" s="19"/>
       <c r="L559" s="19"/>
@@ -19483,27 +19324,13 @@
       <c r="R559"/>
     </row>
     <row r="560" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A560" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B560" s="16">
-        <v>0.7</v>
-      </c>
-      <c r="C560" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D560" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F560" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G560" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="H560" s="10" t="s">
-        <v>197</v>
-      </c>
+      <c r="A560" s="16"/>
+      <c r="B560" s="16"/>
+      <c r="C560" s="11"/>
+      <c r="D560" s="11"/>
+      <c r="F560" s="11"/>
+      <c r="G560" s="16"/>
+      <c r="H560" s="10"/>
       <c r="J560"/>
       <c r="K560" s="19"/>
       <c r="L560" s="19"/>
@@ -19975,7 +19802,9 @@
       </c>
       <c r="B577" s="14" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 1 MW PEM electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Lifetime of 7-8 years per single stack, @ 8000 hours/year. Iridium mining process is NOT from ecoinvent. Produced amount of H2 over 20 years: 2964315.35 kg. According to a study called IndWEDe, it is assumed that the stacks are replaced 3 times during the 20 years lifespan, based on the 2030’s scenario for 1 MW systems which predicts a lifetime of 50,000 h or more for the stacks of the different water electrolysis technologies. In comparison to AEC electrolyzers, PEMEC electrolyzers are less mature. Furthermore, the PEMEC technology is commercially available and operates with a similar system efficiency as the AEC technology. However, the current density and the gas purity are higher with values in between 0.6–2.0 A/cm2 and &gt; 99.99%, respectively. Besides this, the operating pressure (below 200 bar) is significantly higher in comparison to AEC systems, while the operating temperature (50 °C to 80 °C) and the system energy (4.2–6.6 kWh/m3H2) are similar to AEC systems. The PEMEC BoP and stack components data stem from Bareiß et al. and correspond to a 1 MW system. Moreover, some further BoP components like water purifier &amp; feed tank, buffer tank, and heat exchanger have been added, derived from a 300 kW AEC system, under the assumption that the components are also suitable for a PEMEC system. The values have been scaled up from 300 kW to 1 MW. Values have already been multiplied by 3 to reflect 2 stack replacements over 20 years of use.</t>
         </is>
@@ -20109,6 +19938,11 @@
         <f>B578</f>
         <v>used electrolyzer balance of plant, 1MWe, SOEC</v>
       </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
       <c r="K583" s="12"/>
       <c r="L583" s="12"/>
       <c r="M583" s="12"/>
@@ -20150,7 +19984,7 @@
         <v>449</v>
       </c>
       <c r="B585" s="11">
-        <v>-13130</v>
+        <v>-12227</v>
       </c>
       <c r="C585" s="11" t="s">
         <v>217</v>
@@ -20166,7 +20000,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="J585"/>
@@ -20184,7 +20018,7 @@
         <v>206</v>
       </c>
       <c r="B586" s="11">
-        <v>-301</v>
+        <v>0</v>
       </c>
       <c r="C586" s="11" t="s">
         <v>37</v>
@@ -20200,7 +20034,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="J586"/>
@@ -20363,7 +20197,7 @@
         <v>208</v>
       </c>
       <c r="B592" s="11">
-        <v>-229</v>
+        <v>-3.3000000000000114</v>
       </c>
       <c r="C592" s="11" t="s">
         <v>37</v>
@@ -20379,7 +20213,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="J592"/>
@@ -20397,7 +20231,7 @@
         <v>210</v>
       </c>
       <c r="B593" s="11">
-        <v>-110</v>
+        <v>-34.8</v>
       </c>
       <c r="C593" s="11" t="s">
         <v>212</v>
@@ -20413,7 +20247,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="J593"/>
@@ -20458,7 +20292,7 @@
     <row r="595" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A595" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
         </is>
       </c>
       <c r="B595" s="16">
@@ -20481,12 +20315,12 @@
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
       <c r="K595" s="12"/>
@@ -27780,6 +27614,5721 @@
       <c r="I908" t="inlineStr">
         <is>
           <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B913">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+      <c r="B920">
+        <v>1</v>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>market for silicon carbide</t>
+        </is>
+      </c>
+      <c r="B921">
+        <v>4.941e-06</v>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>silicon carbide</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>silicon carbide</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B922">
+        <v>1.192e-06</v>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B923">
+        <v>3.972e-06</v>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B924">
+        <v>0.003967074</v>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B925">
+        <v>4.257e-06</v>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B926">
+        <v>2.0032e-05</v>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B927">
+        <v>0.000380613</v>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B928">
+        <v>0.00160258</v>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B929">
+        <v>3.3233e-05</v>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B930">
+        <v>2.9065e-05</v>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>market for antimony</t>
+        </is>
+      </c>
+      <c r="B931">
+        <v>2.0899999999999998e-07</v>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B932">
+        <v>5.23e-07</v>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B933">
+        <v>0.006047690999999999</v>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B938">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+      <c r="B945">
+        <v>1</v>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>market for silicon carbide</t>
+        </is>
+      </c>
+      <c r="B946">
+        <v>2.6459999999999997e-06</v>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>silicon carbide</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>silicon carbide</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B947">
+        <v>1.192e-06</v>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B948">
+        <v>3.972e-06</v>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B949">
+        <v>0.003967074</v>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B950">
+        <v>5.601e-06</v>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B951">
+        <v>2.0046e-05</v>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B952">
+        <v>0.00038086799999999997</v>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B953">
+        <v>0.0016036569999999999</v>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B954">
+        <v>3.2692e-05</v>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B955">
+        <v>2.9065e-05</v>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>market for antimony</t>
+        </is>
+      </c>
+      <c r="B956">
+        <v>1.26e-07</v>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B957">
+        <v>3.14e-07</v>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B958">
+        <v>0.006047253</v>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B963">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+        </is>
+      </c>
+      <c r="B970">
+        <v>1</v>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B971">
+        <v>0.190154304</v>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>market for aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="B972">
+        <v>0.0085995</v>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>market for nylon 6-6</t>
+        </is>
+      </c>
+      <c r="B973">
+        <v>0.051300000000000005</v>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>nylon 6-6</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>nylon 6-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>market for silicone product</t>
+        </is>
+      </c>
+      <c r="B974">
+        <v>0.02425</v>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>market for silicon, electronics grade</t>
+        </is>
+      </c>
+      <c r="B975">
+        <v>0.001</v>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B976">
+        <v>0.0005</v>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>market for solder, bar, Sn95.5Ag3.9Cu0.6, for electronics industry</t>
+        </is>
+      </c>
+      <c r="B977">
+        <v>0.004</v>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>solder, bar, Sn95.5Ag3.9Cu0.6, for electronics industry</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>solder, bar, Sn95.5Ag3.9Cu0.6, for electronics industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B978">
+        <v>0.01</v>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B979">
+        <v>0.34</v>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 75kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B984">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 75kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients. Thisframe:installedmass=41.2016kg;EPDbulkledger={'steel': 21.069, 'Al': 6.74208, 'Cu': 3.37104, 'PC': 2.4814599999999998, 'ABS': 1.73234, 'electronics': 3.60514};unresolvedotherelectronics=0.11513999999999995kg;unresolvedtotaloutsidepackage=2.3156800000000035kg,pluscomponentmoduleunknownwhereapplicable. Packagingpaperusescorrugated-boxproxy,EPPusesPPresinwithoutverifiedfoamprocessing,SEBSusesgeneric syntheticrubberproxywithunvalidatedhydrogenation/grade,PCusesRoWproductionproxytoavoidunsupportedpre3.10regionalmarket.1kWh/driveon-siteassemblyallowanceassumed,notEPDmeasuredenergy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 75kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="B991">
+        <v>1</v>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 75kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 75kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B992">
+        <v>21.069</v>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B993">
+        <v>6.74208</v>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B994">
+        <v>3.37104</v>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>polycarbonate production</t>
+        </is>
+      </c>
+      <c r="B995">
+        <v>2.4814599999999998</v>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>polycarbonate</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>polycarbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>market for acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+      <c r="B996">
+        <v>1.73234</v>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+        </is>
+      </c>
+      <c r="B997">
+        <v>6</v>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B998">
+        <v>0.75</v>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B999">
+        <v>0.65</v>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>market for fan, for power supply unit, desktop computer</t>
+        </is>
+      </c>
+      <c r="B1000">
+        <v>0.05</v>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>fan, for power supply unit, desktop computer</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>fan, for power supply unit, desktop computer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1001">
+        <v>1</v>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>market for sawnwood, board, softwood, raw, dried (u=10%)</t>
+        </is>
+      </c>
+      <c r="B1002">
+        <v>0.010019479999999999</v>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>sawnwood, board, softwood, raw, dried (u=10%)</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>sawnwood, board, softwood, raw, dried (u=10%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>market for waste wood, untreated</t>
+        </is>
+      </c>
+      <c r="B1003">
+        <v>-5.00974</v>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>waste wood, untreated</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>waste wood, untreated</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>market for corrugated board box</t>
+        </is>
+      </c>
+      <c r="B1004">
+        <v>0.60866</v>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>corrugated board box</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>corrugated board box</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>market for waste paperboard</t>
+        </is>
+      </c>
+      <c r="B1005">
+        <v>-0.60866</v>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>waste paperboard</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>waste paperboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 15kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1010">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 15kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients. Thisframe:installedmass=10.3292kg;EPDbulkledger={'steel': 2.3205, 'Al': 2.6299, 'PC': 2.2491, 'ABS': 0.6069, 'SEBS': 0.1071, 'electronics': 1.8683};unresolvedotherelectronics=0.14572770800000007kg;unresolvedtotaloutsidepackage=0.6931277079999998kg,pluscomponentmoduleunknownwhereapplicable. Packagingpaperusescorrugated-boxproxy,EPPusesPPresinwithoutverifiedfoamprocessing,SEBSusesgeneric syntheticrubberproxywithunvalidatedhydrogenation/grade,PCusesRoWproductionproxytoavoidunsupportedpre3.10regionalmarket.1kWh/driveon-siteassemblyallowanceassumed,notEPDmeasuredenergy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 15kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="B1017">
+        <v>1</v>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 15kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 15kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1018">
+        <v>2.3205</v>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1019">
+        <v>2.6299</v>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>polycarbonate production</t>
+        </is>
+      </c>
+      <c r="B1020">
+        <v>2.2491</v>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>polycarbonate</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>polycarbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>market for acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+      <c r="B1021">
+        <v>0.6069</v>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>market for synthetic rubber</t>
+        </is>
+      </c>
+      <c r="B1022">
+        <v>0.1071</v>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>synthetic rubber</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>synthetic rubber</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+      <c r="B1023">
+        <v>12</v>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1024">
+        <v>1</v>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B1025">
+        <v>0.6</v>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>market for fan, for power supply unit, desktop computer</t>
+        </is>
+      </c>
+      <c r="B1026">
+        <v>0.05</v>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>fan, for power supply unit, desktop computer</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>fan, for power supply unit, desktop computer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1027">
+        <v>1</v>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>market for corrugated board box</t>
+        </is>
+      </c>
+      <c r="B1028">
+        <v>1.3685</v>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>corrugated board box</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>corrugated board box</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>market for waste paperboard</t>
+        </is>
+      </c>
+      <c r="B1029">
+        <v>-1.3685</v>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>waste paperboard</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>waste paperboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>market for corrugated board box</t>
+        </is>
+      </c>
+      <c r="B1030">
+        <v>0.2023</v>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>corrugated board box</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>corrugated board box</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>market for waste paperboard</t>
+        </is>
+      </c>
+      <c r="B1031">
+        <v>-0.2023</v>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>waste paperboard</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>waste paperboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1036">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients. Thisframe:installedmass=7.586410000000001kg;EPDbulkledger={'steel': 1.4545700000000001, 'Al': 1.4284400000000002, 'Cu': 0.29614000000000007, 'PC': 1.9162000000000001, 'ABS': 0.7403500000000002, 'electronics': 1.3413400000000002};unresolvedotherelectronics=0.20877296400000028kg;unresolvedtotaloutsidepackage=0.6181429639999994kg,pluscomponentmoduleunknownwhereapplicable. Packagingpaperusescorrugated-boxproxy,EPPusesPPresinwithoutverifiedfoamprocessing,SEBSusesgeneric syntheticrubberproxywithunvalidatedhydrogenation/grade,PCusesRoWproductionproxytoavoidunsupportedpre3.10regionalmarket.1kWh/driveon-siteassemblyallowanceassumed,notEPDmeasuredenergy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="B1043">
+        <v>1</v>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1044">
+        <v>1.4545700000000001</v>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1045">
+        <v>1.4284400000000002</v>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1046">
+        <v>0.29614000000000007</v>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>polycarbonate production</t>
+        </is>
+      </c>
+      <c r="B1047">
+        <v>1.9162000000000001</v>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>polycarbonate</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>polycarbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>market for acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+      <c r="B1048">
+        <v>0.7403500000000002</v>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+      <c r="B1049">
+        <v>12</v>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1050">
+        <v>0.65</v>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B1051">
+        <v>0.35</v>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>market for fan, for power supply unit, desktop computer</t>
+        </is>
+      </c>
+      <c r="B1052">
+        <v>0.06</v>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>fan, for power supply unit, desktop computer</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>fan, for power supply unit, desktop computer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1053">
+        <v>1</v>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>market for corrugated board box</t>
+        </is>
+      </c>
+      <c r="B1054">
+        <v>0.76648</v>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>corrugated board box</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>corrugated board box</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>market for waste paperboard</t>
+        </is>
+      </c>
+      <c r="B1055">
+        <v>-0.76648</v>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>waste paperboard</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>waste paperboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>market for polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="B1056">
+        <v>0.35711000000000004</v>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>market for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B1057">
+        <v>-0.35711000000000004</v>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1062">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+      <c r="B1069">
+        <v>1</v>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 75kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="B1070">
+        <v>2</v>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 75kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 75kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1075">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+      <c r="B1082">
+        <v>-1</v>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>market for waste electric and electronic equipment</t>
+        </is>
+      </c>
+      <c r="B1083">
+        <v>-82.4032</v>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>waste electric and electronic equipment</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>waste electric and electronic equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1088">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
+        </is>
+      </c>
+      <c r="B1095">
+        <v>-1</v>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1096">
+        <v>-1</v>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+      <c r="B1097">
+        <v>-1</v>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+      <c r="B1109">
+        <v>1</v>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 75kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="B1110">
+        <v>2</v>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 75kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 75kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+      <c r="B1122">
+        <v>-1</v>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>market for waste electric and electronic equipment</t>
+        </is>
+      </c>
+      <c r="B1123">
+        <v>-82.4032</v>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>waste electric and electronic equipment</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>waste electric and electronic equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
+        </is>
+      </c>
+      <c r="B1135">
+        <v>-1</v>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1136">
+        <v>-1</v>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+      <c r="B1137">
+        <v>-1</v>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+      <c r="B1149">
+        <v>1</v>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 15kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="B1150">
+        <v>10</v>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 15kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 15kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="B1151">
+        <v>2</v>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+      <c r="B1163">
+        <v>-1</v>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>market for waste electric and electronic equipment</t>
+        </is>
+      </c>
+      <c r="B1164">
+        <v>-118.46482</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>waste electric and electronic equipment</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>waste electric and electronic equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
+        </is>
+      </c>
+      <c r="B1176">
+        <v>-1</v>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1177">
+        <v>-1</v>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+      <c r="B1178">
+        <v>-1</v>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1178"/>
+  <dimension ref="A1:U1194"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -12166,7 +12166,9 @@
       </c>
       <c r="B305" s="14" t="inlineStr">
         <is>
-          <t>APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.
+          <t>APPROVED FINISHED AEC PTFE GASKETS, issue100, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 andPtM DOI10.1021/acssuschemeng.1c02002 SI pS12 identify144.2kgTFEinputasgasket. FinishedPTFEproperties/polymerization:Hintzer et al.2014 Ullmann Fluoropolymers DOI10.1002/14356007.a11_393.pub2;ecoinvent3.12hasPTFEemulsionpolymerizationbut3.8-3.11lackafinishedprovider. Engineeringallowancesbelowuse3.12polymerizationenergy7.5MJ+0.5kWh/kgplus3MJ+0.2kWhforming,notacopyofwholebackgroundinventory. Replace144.2kgvolatileTFEmonomerby144.2kgfinishedPTFEgasketreference,maintainingallversionbehaviorwithoneworkbookprovider. nC2F4-&gt;(C2F4)n;100%chemicalconversionthen95%finishedsolidretention(includingforming/machiningreject). Perkgfinished1/0.95=1.0526315789473684kgTFE,solidPTFEreject=0.05263157894736836kg. Thisyieldisassumed,90-100%sensitivity;notmeasuredindustrialpolymerizationyield. Aggregatemanufacture10.5MJheat+0.7kWh/kgfinishedincludespolymerizationandformingonce(5-20MJ,.35-1.4kWhsensitivity). ExistingTFEsupplyupstreamburdensretainedonce. Initiator,emulsionwater/surfactant,polymerdrying,highpressureequipment,purification,PFAS/TFEfugitiveemissionsandactualgasketshapesareunresolved;solid-rejectreferenceisnotclaimofzeroindustrialairloss. No nativePTFEpurchaseontopofmonomer,nomassivegasgasketinterpretation. FinishedAECgasketEOL144.2kgoldplasticroutepreserved;fluoropolymer-specificHFabatementnotvalidatedbygenericroute. Stacklifetimesandmetalinputsunchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 1 MWe Alkaline electrolyzer based on Niklas Gerloff, Comparative Life-Cycle-Assessment analysis of three major water electrolysis technologies while applying various energy scenarios for a greener hydrogen production, Journal of Energy Storage, Volume 43, 2021, https://doi.org/10.1016/j.est.2021.102759. Single stack lifetime of 7-8 years @ 8000 hours/year, hence 3 replacements over 20 years. Produced amount of H2 over 20 years: 3085961.12 kg. The technology is available for large plant sizes and operates with a stack efficiency of up to 67 % (based on the lower heating value (LHV) of the generated H2). The operating temperature is in between 60–80 °C, and the current density is around 0.2–0.4 A/cm2. Moreover, the system energy –including the stack and periphery energy– is in the range of 4.4–6.6 kWh/m3H2, while the gas purity is higher than 99.5%, and the operating pressure is below 30 bar. While the LCI data of the BoP components either originate from Zhang et al., based on a 300-kW system and, therefore, scaled-up to 1 MW by a factor of 0.7, the LCI data of the other BoP components originate from manufacturer offers or have been estimated by own calculations using additional information by the producers.  Values have already been multiplied by 3 to reflect 2 stack replacements over 20 years of use.</t>
         </is>
@@ -12302,7 +12304,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.</t>
+          <t>APPROVED FINISHED AEC PTFE GASKETS, issue100, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 andPtM DOI10.1021/acssuschemeng.1c02002 SI pS12 identify144.2kgTFEinputasgasket. FinishedPTFEproperties/polymerization:Hintzer et al.2014 Ullmann Fluoropolymers DOI10.1002/14356007.a11_393.pub2;ecoinvent3.12hasPTFEemulsionpolymerizationbut3.8-3.11lackafinishedprovider. Engineeringallowancesbelowuse3.12polymerizationenergy7.5MJ+0.5kWh/kgplus3MJ+0.2kWhforming,notacopyofwholebackgroundinventory. Replace144.2kgvolatileTFEmonomerby144.2kgfinishedPTFEgasketreference,maintainingallversionbehaviorwithoneworkbookprovider. nC2F4-&gt;(C2F4)n;100%chemicalconversionthen95%finishedsolidretention(includingforming/machiningreject). Perkgfinished1/0.95=1.0526315789473684kgTFE,solidPTFEreject=0.05263157894736836kg. Thisyieldisassumed,90-100%sensitivity;notmeasuredindustrialpolymerizationyield. Aggregatemanufacture10.5MJheat+0.7kWh/kgfinishedincludespolymerizationandformingonce(5-20MJ,.35-1.4kWhsensitivity). ExistingTFEsupplyupstreamburdensretainedonce. Initiator,emulsionwater/surfactant,polymerdrying,highpressureequipment,purification,PFAS/TFEfugitiveemissionsandactualgasketshapesareunresolved;solid-rejectreferenceisnotclaimofzeroindustrialairloss. No nativePTFEpurchaseontopofmonomer,nomassivegasgasketinterpretation. FinishedAECgasketEOL144.2kgoldplasticroutepreserved;fluoropolymer-specificHFabatementnotvalidatedbygenericroute. Stacklifetimesandmetalinputsunchanged.</t>
         </is>
       </c>
       <c r="K311" s="12"/>
@@ -12313,14 +12315,18 @@
       <c r="P311" s="12"/>
     </row>
     <row r="312" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A312" s="11" t="s">
-        <v>21</v>
+      <c r="A312" s="11" t="inlineStr">
+        <is>
+          <t>PTFE gasket, polymerization and forming engineering reference</t>
+        </is>
       </c>
       <c r="B312" s="12">
         <v>144.19999999999999</v>
       </c>
-      <c r="C312" s="11" t="s">
-        <v>17</v>
+      <c r="C312" s="11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D312" s="11" t="s">
         <v>13</v>
@@ -12328,11 +12334,15 @@
       <c r="F312" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G312" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H312" s="11" t="s">
-        <v>78</v>
+      <c r="G312" s="11" t="inlineStr">
+        <is>
+          <t>PTFE gasket, polymerization and forming engineering reference</t>
+        </is>
+      </c>
+      <c r="H312" s="11" t="inlineStr">
+        <is>
+          <t>APPROVED FINISHED AEC PTFE GASKETS, issue100, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 andPtM DOI10.1021/acssuschemeng.1c02002 SI pS12 identify144.2kgTFEinputasgasket. FinishedPTFEproperties/polymerization:Hintzer et al.2014 Ullmann Fluoropolymers DOI10.1002/14356007.a11_393.pub2;ecoinvent3.12hasPTFEemulsionpolymerizationbut3.8-3.11lackafinishedprovider. Engineeringallowancesbelowuse3.12polymerizationenergy7.5MJ+0.5kWh/kgplus3MJ+0.2kWhforming,notacopyofwholebackgroundinventory. Replace144.2kgvolatileTFEmonomerby144.2kgfinishedPTFEgasketreference,maintainingallversionbehaviorwithoneworkbookprovider. nC2F4-&gt;(C2F4)n;100%chemicalconversionthen95%finishedsolidretention(includingforming/machiningreject). Perkgfinished1/0.95=1.0526315789473684kgTFE,solidPTFEreject=0.05263157894736836kg. Thisyieldisassumed,90-100%sensitivity;notmeasuredindustrialpolymerizationyield. Aggregatemanufacture10.5MJheat+0.7kWh/kgfinishedincludespolymerizationandformingonce(5-20MJ,.35-1.4kWhsensitivity). ExistingTFEsupplyupstreamburdensretainedonce. Initiator,emulsionwater/surfactant,polymerdrying,highpressureequipment,purification,PFAS/TFEfugitiveemissionsandactualgasketshapesareunresolved;solid-rejectreferenceisnotclaimofzeroindustrialairloss. No nativePTFEpurchaseontopofmonomer,nomassivegasgasketinterpretation. FinishedAECgasketEOL144.2kgoldplasticroutepreserved;fluoropolymer-specificHFabatementnotvalidatedbygenericroute. Stacklifetimesandmetalinputsunchanged.</t>
+        </is>
       </c>
       <c r="J312"/>
       <c r="K312" s="19"/>
@@ -33329,6 +33339,317 @@
       <c r="I1178" t="inlineStr">
         <is>
           <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>PTFE gasket, polymerization and forming engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>PTFE gasket, polymerization and forming engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Gerloff2021 DOI10.1016/j.est.2021.102759 andPtM DOI10.1021/acssuschemeng.1c02002 SI pS12 identify144.2kgTFEinputasgasket. FinishedPTFEproperties/polymerization:Hintzer et al.2014 Ullmann Fluoropolymers DOI10.1002/14356007.a11_393.pub2;ecoinvent3.12hasPTFEemulsionpolymerizationbut3.8-3.11lackafinishedprovider. Engineeringallowancesbelowuse3.12polymerizationenergy7.5MJ+0.5kWh/kgplus3MJ+0.2kWhforming,notacopyofwholebackgroundinventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>APPROVED FINISHED AEC PTFE GASKETS, issue100, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 andPtM DOI10.1021/acssuschemeng.1c02002 SI pS12 identify144.2kgTFEinputasgasket. FinishedPTFEproperties/polymerization:Hintzer et al.2014 Ullmann Fluoropolymers DOI10.1002/14356007.a11_393.pub2;ecoinvent3.12hasPTFEemulsionpolymerizationbut3.8-3.11lackafinishedprovider. Engineeringallowancesbelowuse3.12polymerizationenergy7.5MJ+0.5kWh/kgplus3MJ+0.2kWhforming,notacopyofwholebackgroundinventory. Replace144.2kgvolatileTFEmonomerby144.2kgfinishedPTFEgasketreference,maintainingallversionbehaviorwithoneworkbookprovider. nC2F4-&gt;(C2F4)n;100%chemicalconversionthen95%finishedsolidretention(includingforming/machiningreject). Perkgfinished1/0.95=1.0526315789473684kgTFE,solidPTFEreject=0.05263157894736836kg. Thisyieldisassumed,90-100%sensitivity;notmeasuredindustrialpolymerizationyield. Aggregatemanufacture10.5MJheat+0.7kWh/kgfinishedincludespolymerizationandformingonce(5-20MJ,.35-1.4kWhsensitivity). ExistingTFEsupplyupstreamburdensretainedonce. Initiator,emulsionwater/surfactant,polymerdrying,highpressureequipment,purification,PFAS/TFEfugitiveemissionsandactualgasketshapesareunresolved;solid-rejectreferenceisnotclaimofzeroindustrialairloss. No nativePTFEpurchaseontopofmonomer,nomassivegasgasketinterpretation. FinishedAECgasketEOL144.2kgoldplasticroutepreserved;fluoropolymer-specificHFabatementnotvalidatedbygenericroute. Stacklifetimesandmetalinputsunchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>PTFE gasket, polymerization and forming engineering reference</t>
+        </is>
+      </c>
+      <c r="B1190">
+        <v>1</v>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>PTFE gasket, polymerization and forming engineering reference</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>PTFE gasket, polymerization and forming engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>market for tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="B1191">
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1192">
+        <v>10.5</v>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1193">
+        <v>0.7</v>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>market for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B1194">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -8466,7 +8466,7 @@
     <row r="175" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+          <t xml:space="preserve">PFSA membrane production, electrolysis, EW1100</t>
         </is>
       </c>
       <c r="B175" s="12">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
-          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+          <t xml:space="preserve">PFSA membrane, electrolysis, EW1100</t>
         </is>
       </c>
       <c r="H175" s="11" t="inlineStr">
@@ -9393,7 +9393,7 @@
     <row r="211" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+          <t xml:space="preserve">power conversion system production, electrolysis, transformer and rectifier, 1 MW</t>
         </is>
       </c>
       <c r="B211" s="16">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="G211" s="11" t="inlineStr">
         <is>
-          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+          <t xml:space="preserve">power conversion system, electrolysis, transformer and rectifier, 1 MW</t>
         </is>
       </c>
       <c r="H211" s="27" t="inlineStr">
@@ -10153,7 +10153,7 @@
     <row r="237" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">motor drive assembly production, electrolysis, PEM</t>
         </is>
       </c>
       <c r="B237" s="16">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="G237" s="11" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">motor drive assembly, electrolysis, PEM</t>
         </is>
       </c>
       <c r="H237" s="10" t="inlineStr">
@@ -11373,7 +11373,7 @@
     <row r="281" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A281" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
+          <t xml:space="preserve">treatment of used power conversion system and motor drives, electrolysis, PEM</t>
         </is>
       </c>
       <c r="B281" s="16">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
+          <t xml:space="preserve">used power conversion system and motor drives, electrolysis, PEM</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -12317,7 +12317,7 @@
     <row r="312" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>PTFE gasket, polymerization and forming engineering reference</t>
+          <t xml:space="preserve">PTFE gasket production, polymerization and forming</t>
         </is>
       </c>
       <c r="B312" s="12">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="G312" s="11" t="inlineStr">
         <is>
-          <t>PTFE gasket, polymerization and forming engineering reference</t>
+          <t xml:space="preserve">PTFE gasket, polymerization and forming</t>
         </is>
       </c>
       <c r="H312" s="11" t="inlineStr">
@@ -12453,7 +12453,7 @@
     <row r="316" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+          <t xml:space="preserve">diaphragm production, alkaline electrolysis, zirconia-polysulfone with PPS mesh</t>
         </is>
       </c>
       <c r="B316" s="12">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="G316" s="10" t="inlineStr">
         <is>
-          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+          <t xml:space="preserve">diaphragm, alkaline electrolysis, zirconia-polysulfone with PPS mesh</t>
         </is>
       </c>
       <c r="H316" s="11" t="inlineStr">
@@ -13029,7 +13029,7 @@
     <row r="341" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A341" s="11" t="inlineStr">
         <is>
-          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+          <t xml:space="preserve">power conversion system production, electrolysis, transformer and rectifier, 1 MW</t>
         </is>
       </c>
       <c r="B341" s="16">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="G341" s="11" t="inlineStr">
         <is>
-          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+          <t xml:space="preserve">power conversion system, electrolysis, transformer and rectifier, 1 MW</t>
         </is>
       </c>
       <c r="H341" s="27" t="inlineStr">
@@ -13501,7 +13501,7 @@
     <row r="358" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A358" s="11" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">motor drive assembly production, electrolysis, AEC</t>
         </is>
       </c>
       <c r="B358" s="16">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="G358" s="11" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">motor drive assembly, electrolysis, AEC</t>
         </is>
       </c>
       <c r="H358" s="10" t="inlineStr">
@@ -15336,7 +15336,7 @@
     <row r="421" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A421" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
+          <t xml:space="preserve">treatment of used power conversion system and motor drives, electrolysis, AEC</t>
         </is>
       </c>
       <c r="B421" s="16">
@@ -15359,7 +15359,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
+          <t xml:space="preserve">used power conversion system and motor drives, electrolysis, AEC</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -16962,7 +16962,7 @@
     <row r="474" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A474" s="11" t="inlineStr">
         <is>
-          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+          <t xml:space="preserve">ferritic steel production, electrolysis interconnect, Crofer 22 APU type</t>
         </is>
       </c>
       <c r="B474" s="12">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="G474" s="11" t="inlineStr">
         <is>
-          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+          <t xml:space="preserve">ferritic steel, electrolysis interconnect, Crofer 22 APU type</t>
         </is>
       </c>
       <c r="H474" s="11" t="inlineStr">
@@ -17218,7 +17218,7 @@
     <row r="481" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A481" s="11" t="inlineStr">
         <is>
-          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+          <t xml:space="preserve">contact ceramic production, lanthanum strontium manganite, La0.8Sr0.2MnO3</t>
         </is>
       </c>
       <c r="B481" s="12">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="G481" s="11" t="inlineStr">
         <is>
-          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+          <t xml:space="preserve">contact ceramic, lanthanum strontium manganite, La0.8Sr0.2MnO3</t>
         </is>
       </c>
       <c r="H481" s="11" t="inlineStr">
@@ -17277,7 +17277,7 @@
     <row r="483" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A483" s="11" t="inlineStr">
         <is>
-          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+          <t xml:space="preserve">glass seal production, SOEC, barium alumino-borosilicate</t>
         </is>
       </c>
       <c r="B483" s="12">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="G483" s="11" t="inlineStr">
         <is>
-          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+          <t xml:space="preserve">glass seal, SOEC, barium alumino-borosilicate</t>
         </is>
       </c>
       <c r="H483" s="11" t="inlineStr">
@@ -17947,7 +17947,7 @@
     <row r="512" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A512" s="16" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">motor drive assembly production, electrolysis, SOEC</t>
         </is>
       </c>
       <c r="B512" s="16">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="G512" s="16" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">motor drive assembly, electrolysis, SOEC</t>
         </is>
       </c>
       <c r="H512" s="10" t="inlineStr">
@@ -18393,7 +18393,7 @@
     <row r="527" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A527" s="16" t="inlineStr">
         <is>
-          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+          <t xml:space="preserve">power conversion system production, electrolysis, transformer and rectifier, 1 MW</t>
         </is>
       </c>
       <c r="B527" s="16">
@@ -18414,7 +18414,7 @@
       </c>
       <c r="G527" s="16" t="inlineStr">
         <is>
-          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+          <t xml:space="preserve">power conversion system, electrolysis, transformer and rectifier, 1 MW</t>
         </is>
       </c>
       <c r="H527" s="10" t="inlineStr">
@@ -20302,7 +20302,7 @@
     <row r="595" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A595" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
+          <t xml:space="preserve">treatment of used power conversion system and motor drives, electrolysis, SOEC</t>
         </is>
       </c>
       <c r="B595" s="16">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
+          <t xml:space="preserve">used power conversion system and motor drives, electrolysis, SOEC</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -21267,7 +21267,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+          <t xml:space="preserve">PFSA membrane production, electrolysis, EW1100</t>
         </is>
       </c>
     </row>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+          <t xml:space="preserve">PFSA membrane, electrolysis, EW1100</t>
         </is>
       </c>
     </row>
@@ -21337,7 +21337,8 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>APPROVED FINISHED PFSA MEMBRANE REFERENCE, issue90, 2026-10-18. Weber et al.2018 DOI10.1021/acs.est.8b02073 SISec1.2.1/TableS2 describesTFE+SO3-&gt;FDA,HFPoxidationwithNaOCl-&gt;HFPO,FDA+2HFPOadduct,Na2CO3pyrolysistoPSEPVE,polymerization90%yieldand39.31MJ/kgformingheat. Harzer2021PhD https://mediatum.ub.tum.de/doc/1634530/1634530.pdf synthesisfigurecorroboratesPSEPVE/alkalihydrolysis/acidconversion. ElectrolyzermembraneEW1100reference:Mechanical Characterization of Electrolyzer Membranes and Components Under Compression,2024 DOI10.1149/1945-7111/ad7a26. Theseareseparatechemistry/referenceproperties,not a measuredcompleteNafionfactory. Replace16kgTFEmonomerby16kgfinishedunreinforceddryacid-formPFSAperexisting1MWePEMstack. PreserveapprovedPt/Ir/coatingreferencesandlifetimepurchases. UseexplicitbalancednetengineeringchemistrywithEW1100g/molSO3H;n=6.557783744855004TFEbackboneunitsperC7F13O5SHacid-sidechainunit. FDA=C2F4O3SfromTFE+SO3;HFPO=C3F6OfromHFP+NaOCl,HFPfromTFEat1:1mass(rearrangementreference). FDA+2HFPO+Na2CO3-&gt;PSEPVE(C7F14O4S)+2NaF+2CO2;PSEPVE+backboneTFE+2NaOH+HCl-&gt;acidPFSA+NaF+NaCl+H2O. ThisNaOH/HClworkupis anexplicitbalancedengineeringvariant,not a claim ofHarzerKOH/HNO3industrialreagentchoice. Allupstreamintermediateconversionsassumed100%,overallfinishedpolymerretention90%asWeberreference. No2nd90%factoronprecursorinputs. Knownnetingredientsperkgfinished={'TFE': 1.0666093025141414, 'SO3': 0.08086565656565657, 'NaOCl': 0.15038135208080808, 'Na2CO3': 0.10705811975757576, 'NaOH': 0.0808015541010101, 'HCl': 0.03682626262626263};byproducts/reject={'NaCl': 0.17709020993939395, 'NaF': 0.1272368861909091, 'water': 0.018196969696969698, 'CO2': 0.08890707070707071, 'reject_PFSA': 0.11111111111111116}. BuyactualTFE,SO3,NaOCl,Na2CO3,NaOH,HCl,directlyatnetchainfeed;doNOTalsoaddcompleteWebermembranes orunsupportedHFP-&gt;hexafluoroethaneproxy. SaltoutputsNaCl/NaFandstoichiometricwatergotooneaqueouseffluentwith10kgprocesswater/kgfinished (explicitengineeringdilution,1-100kgsensitivity),1000kg/m3densityproxy. Fluoride-specificabatement/isolationanddissolvedsaltfateareunresolved;genericwastewaterisNOTvalidatedNaFdisposal. Polymerrejectgoestoexistingplasticincinerationwithoutcredit;stoichiometricCO2emittedonce.39.31MJ/kgWeberheat isoneaggregateon-sitechemicalsynthesis/filmformingallowance,notaddedagainateachmodeledintermediate;1kWh/kgsiteelectricityassumed. Existingnativeupstreamfeedproductionburdensremainseparate. TestEW1000-1200,finishedretention80-100%,heat20-80MJ/kg,andnonidealintermediateyields;thebalancednetrecipeis a stoichiometricengineeringreferencewithyield,NOTmeasuredindustrialgrosschemicalconsumption. Actualco-monomerpurification,catalysts,solventcirculation,intermediatescrap,PFASemissions,membranewatercontent,reinforcementandlong-termperformancearecoveragegaps. Finished16kgmasskept,notinferredfromfilmthicknessorcellarea. No native/runtime/YAMLorprimary-secondarysharechanges.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: PFSA membrane, EW1100, balanced chemistry engineering reference. Former reference product: PFSA membrane, EW1100, balanced chemistry engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FINISHED PFSA MEMBRANE REFERENCE, issue90, 2026-10-18. Weber et al.2018 DOI10.1021/acs.est.8b02073 SISec1.2.1/TableS2 describesTFE+SO3-&gt;FDA,HFPoxidationwithNaOCl-&gt;HFPO,FDA+2HFPOadduct,Na2CO3pyrolysistoPSEPVE,polymerization90%yieldand39.31MJ/kgformingheat. Harzer2021PhD https://mediatum.ub.tum.de/doc/1634530/1634530.pdf synthesisfigurecorroboratesPSEPVE/alkalihydrolysis/acidconversion. ElectrolyzermembraneEW1100reference:Mechanical Characterization of Electrolyzer Membranes and Components Under Compression,2024 DOI10.1149/1945-7111/ad7a26. Theseareseparatechemistry/referenceproperties,not a measuredcompleteNafionfactory. Replace16kgTFEmonomerby16kgfinishedunreinforceddryacid-formPFSAperexisting1MWePEMstack. PreserveapprovedPt/Ir/coatingreferencesandlifetimepurchases. UseexplicitbalancednetengineeringchemistrywithEW1100g/molSO3H;n=6.557783744855004TFEbackboneunitsperC7F13O5SHacid-sidechainunit. FDA=C2F4O3SfromTFE+SO3;HFPO=C3F6OfromHFP+NaOCl,HFPfromTFEat1:1mass(rearrangementreference). FDA+2HFPO+Na2CO3-&gt;PSEPVE(C7F14O4S)+2NaF+2CO2;PSEPVE+backboneTFE+2NaOH+HCl-&gt;acidPFSA+NaF+NaCl+H2O. ThisNaOH/HClworkupis anexplicitbalancedengineeringvariant,not a claim ofHarzerKOH/HNO3industrialreagentchoice. Allupstreamintermediateconversionsassumed100%,overallfinishedpolymerretention90%asWeberreference. No2nd90%factoronprecursorinputs. Knownnetingredientsperkgfinished={'TFE': 1.0666093025141414, 'SO3': 0.08086565656565657, 'NaOCl': 0.15038135208080808, 'Na2CO3': 0.10705811975757576, 'NaOH': 0.0808015541010101, 'HCl': 0.03682626262626263};byproducts/reject={'NaCl': 0.17709020993939395, 'NaF': 0.1272368861909091, 'water': 0.018196969696969698, 'CO2': 0.08890707070707071, 'reject_PFSA': 0.11111111111111116}. BuyactualTFE,SO3,NaOCl,Na2CO3,NaOH,HCl,directlyatnetchainfeed;doNOTalsoaddcompleteWebermembranes orunsupportedHFP-&gt;hexafluoroethaneproxy. SaltoutputsNaCl/NaFandstoichiometricwatergotooneaqueouseffluentwith10kgprocesswater/kgfinished (explicitengineeringdilution,1-100kgsensitivity),1000kg/m3densityproxy. Fluoride-specificabatement/isolationanddissolvedsaltfateareunresolved;genericwastewaterisNOTvalidatedNaFdisposal. Polymerrejectgoestoexistingplasticincinerationwithoutcredit;stoichiometricCO2emittedonce.39.31MJ/kgWeberheat isoneaggregateon-sitechemicalsynthesis/filmformingallowance,notaddedagainateachmodeledintermediate;1kWh/kgsiteelectricityassumed. Existingnativeupstreamfeedproductionburdensremainseparate. TestEW1000-1200,finishedretention80-100%,heat20-80MJ/kg,andnonidealintermediateyields;thebalancednetrecipeis a stoichiometricengineeringreferencewithyield,NOTmeasuredindustrialgrosschemicalconsumption. Actualco-monomerpurification,catalysts,solventcirculation,intermediatescrap,PFASemissions,membranewatercontent,reinforcementandlong-termperformancearecoveragegaps. Finished16kgmasskept,notinferredfromfilmthicknessorcellarea. No native/runtime/YAMLorprimary-secondarysharechanges.</t>
         </is>
       </c>
     </row>
@@ -21398,7 +21399,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+          <t xml:space="preserve">PFSA membrane production, electrolysis, EW1100</t>
         </is>
       </c>
       <c r="B645">
@@ -21421,12 +21422,12 @@
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+          <t xml:space="preserve">PFSA membrane, electrolysis, EW1100</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>PFSA membrane, EW1100, balanced chemistry engineering reference</t>
+          <t xml:space="preserve">PFSA membrane, electrolysis, EW1100</t>
         </is>
       </c>
     </row>
@@ -21853,7 +21854,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+          <t xml:space="preserve">glass seal production, SOEC, barium alumino-borosilicate</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21888,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+          <t xml:space="preserve">glass seal, SOEC, barium alumino-borosilicate</t>
         </is>
       </c>
     </row>
@@ -21923,7 +21924,8 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>APPROVED SOEC INORGANIC GLASS-SEAL REFERENCE, issue91, 2026-10-18. Sun,Xiao,Guo,Hong2010,CeramicsInternational36:821-826,DOI10.1016/j.ceramint.2009.09.045,experimentalBaO-Al2O3-B2O3-SiO2glassfamily:base40BaO/20B2O3/40SiO2mol%,Al2O3replacesB2O3/SiO2atconstant2:1Si/Boxide-moleratio;5mol%Alvariantidentifiedasstable,melting1400-1500Cfor1hour. https://www.sciencedirect.com/science/article/pii/S0272884209003812 . ExistingGerloff2021sealantmass4*6.4kg retained. SiliconepolymerisnotSiO2glassformer. Replacefour6.4kgingredients(Al2O3,B2O3,BaO,silicone)by25.6kgofonefinishedglassreference. Select/reconstruct5mol%Al2O3member:40BaO,5Al2O3,18.333333B2O3,36.666667SiO2mol%;theseareoxideMOLfractions,notweightfractions. Correspondingretainedweightfractions={'BaO': 0.6059001794302946, 'Al2O3': 0.05036460625483175, 'B2O3': 0.12609040016734147, 'SiO2': 0.21764481414753226}. Total25.6kgfinishedsealisinheritedengineeringmass,notmeasuredfromthispublishedglassdesign;sourceTable1fullcompositionwasnotindependentlyrecovered,recipeisexplicitreconstructionfrompublishedseriesdescription. UsingSOFCsealingglassasSOECanalogue doesnotdemonstrateactualstacksealgeometry,thermalcycling,dual-atmospherecompatibilityorleaktightness. PurchaseactualBaO,Al2O3,B2O3,SiO2equivalentsscaledby1/0.95forselected95%melting/formingretention,withmatchedsolidglassreject1/.95-1kg/kgtoexistingmixedhazardoustreatmentproxy;volatilizedB/alkalicomponentsandactualwasteclassificationunresolved.6MJ/kgthermaland1kWh/kgmilling/formingareexplicitengineeringutilityallowancesfor1450Cmelting/quenching,notmeasuredsourceutilities;test3-12MJ/kg,0.2-2kWh/kgand90-100%retention. SilicasandisbulkSiO2purityproxy,nonmetallurgicalaluminaisspecialtyoxideproxy;semiconductorgradepurificationnotclaimed. ExistingapprovedYSZ/YDCchemistryandfutureY/Ce/Zrco-scaling,Ni/La/Sr/Prpurchases,steel,stackreplacementandhydrogenoutputallocationunchanged. Do notreduceentirestackorapplyfuturedensitylearningtosealwithoutsource. No newnative/runtime/YAMLchangesorprimary-secondarycredit.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: SOEC glass seal, barium alumino-borosilicate engineering reference. Former reference product: SOEC glass seal, barium alumino-borosilicate engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED SOEC INORGANIC GLASS-SEAL REFERENCE, issue91, 2026-10-18. Sun,Xiao,Guo,Hong2010,CeramicsInternational36:821-826,DOI10.1016/j.ceramint.2009.09.045,experimentalBaO-Al2O3-B2O3-SiO2glassfamily:base40BaO/20B2O3/40SiO2mol%,Al2O3replacesB2O3/SiO2atconstant2:1Si/Boxide-moleratio;5mol%Alvariantidentifiedasstable,melting1400-1500Cfor1hour. https://www.sciencedirect.com/science/article/pii/S0272884209003812 . ExistingGerloff2021sealantmass4*6.4kg retained. SiliconepolymerisnotSiO2glassformer. Replacefour6.4kgingredients(Al2O3,B2O3,BaO,silicone)by25.6kgofonefinishedglassreference. Select/reconstruct5mol%Al2O3member:40BaO,5Al2O3,18.333333B2O3,36.666667SiO2mol%;theseareoxideMOLfractions,notweightfractions. Correspondingretainedweightfractions={'BaO': 0.6059001794302946, 'Al2O3': 0.05036460625483175, 'B2O3': 0.12609040016734147, 'SiO2': 0.21764481414753226}. Total25.6kgfinishedsealisinheritedengineeringmass,notmeasuredfromthispublishedglassdesign;sourceTable1fullcompositionwasnotindependentlyrecovered,recipeisexplicitreconstructionfrompublishedseriesdescription. UsingSOFCsealingglassasSOECanalogue doesnotdemonstrateactualstacksealgeometry,thermalcycling,dual-atmospherecompatibilityorleaktightness. PurchaseactualBaO,Al2O3,B2O3,SiO2equivalentsscaledby1/0.95forselected95%melting/formingretention,withmatchedsolidglassreject1/.95-1kg/kgtoexistingmixedhazardoustreatmentproxy;volatilizedB/alkalicomponentsandactualwasteclassificationunresolved.6MJ/kgthermaland1kWh/kgmilling/formingareexplicitengineeringutilityallowancesfor1450Cmelting/quenching,notmeasuredsourceutilities;test3-12MJ/kg,0.2-2kWh/kgand90-100%retention. SilicasandisbulkSiO2purityproxy,nonmetallurgicalaluminaisspecialtyoxideproxy;semiconductorgradepurificationnotclaimed. ExistingapprovedYSZ/YDCchemistryandfutureY/Ce/Zrco-scaling,Ni/La/Sr/Prpurchases,steel,stackreplacementandhydrogenoutputallocationunchanged. Do notreduceentirestackorapplyfuturedensitylearningtosealwithoutsource. No newnative/runtime/YAMLchangesorprimary-secondarycredit.</t>
         </is>
       </c>
     </row>
@@ -21984,7 +21986,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+          <t xml:space="preserve">glass seal production, SOEC, barium alumino-borosilicate</t>
         </is>
       </c>
       <c r="B669">
@@ -22007,12 +22009,12 @@
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+          <t xml:space="preserve">glass seal, SOEC, barium alumino-borosilicate</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>SOEC glass seal, barium alumino-borosilicate engineering reference</t>
+          <t xml:space="preserve">glass seal, SOEC, barium alumino-borosilicate</t>
         </is>
       </c>
     </row>
@@ -22269,7 +22271,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>silicon nitride, power-module ceramic engineering reference</t>
+          <t xml:space="preserve">silicon nitride production, for power modules</t>
         </is>
       </c>
     </row>
@@ -22303,7 +22305,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>silicon nitride, power-module ceramic engineering reference</t>
+          <t xml:space="preserve">silicon nitride, for power modules</t>
         </is>
       </c>
     </row>
@@ -22339,7 +22341,8 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: silicon nitride, power-module ceramic engineering reference. Former reference product: silicon nitride, power-module ceramic engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22403,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>silicon nitride, power-module ceramic engineering reference</t>
+          <t xml:space="preserve">silicon nitride production, for power modules</t>
         </is>
       </c>
       <c r="B688">
@@ -22423,12 +22426,12 @@
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>silicon nitride, power-module ceramic engineering reference</t>
+          <t xml:space="preserve">silicon nitride, for power modules</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>silicon nitride, power-module ceramic engineering reference</t>
+          <t xml:space="preserve">silicon nitride, for power modules</t>
         </is>
       </c>
     </row>
@@ -22580,7 +22583,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>lead oxide, power-module trace engineering reference</t>
+          <t xml:space="preserve">lead oxide production, for power modules</t>
         </is>
       </c>
     </row>
@@ -22614,7 +22617,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>lead oxide, power-module trace engineering reference</t>
+          <t xml:space="preserve">lead oxide, for power modules</t>
         </is>
       </c>
     </row>
@@ -22650,7 +22653,8 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: lead oxide, power-module trace engineering reference. Former reference product: lead oxide, power-module trace engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
         </is>
       </c>
     </row>
@@ -22711,7 +22715,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>lead oxide, power-module trace engineering reference</t>
+          <t xml:space="preserve">lead oxide production, for power modules</t>
         </is>
       </c>
       <c r="B704">
@@ -22734,12 +22738,12 @@
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>lead oxide, power-module trace engineering reference</t>
+          <t xml:space="preserve">lead oxide, for power modules</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>lead oxide, power-module trace engineering reference</t>
+          <t xml:space="preserve">lead oxide, for power modules</t>
         </is>
       </c>
     </row>
@@ -22856,7 +22860,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>SiC half-bridge module, declared material engineering reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module production</t>
         </is>
       </c>
     </row>
@@ -22890,7 +22894,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>SiC half-bridge module, declared material engineering reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module</t>
         </is>
       </c>
     </row>
@@ -22926,7 +22930,8 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: SiC half-bridge module, declared material engineering reference. Former reference product: SiC half-bridge module, declared material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
         </is>
       </c>
     </row>
@@ -22987,7 +22992,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>SiC half-bridge module, declared material engineering reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module production</t>
         </is>
       </c>
       <c r="B719">
@@ -23010,12 +23015,12 @@
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>SiC half-bridge module, declared material engineering reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>SiC half-bridge module, declared material engineering reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module</t>
         </is>
       </c>
     </row>
@@ -23127,7 +23132,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>silicon nitride, power-module ceramic engineering reference</t>
+          <t xml:space="preserve">silicon nitride production, for power modules</t>
         </is>
       </c>
       <c r="B723">
@@ -23150,12 +23155,12 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>silicon nitride, power-module ceramic engineering reference</t>
+          <t xml:space="preserve">silicon nitride, for power modules</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>silicon nitride, power-module ceramic engineering reference</t>
+          <t xml:space="preserve">silicon nitride, for power modules</t>
         </is>
       </c>
     </row>
@@ -23477,7 +23482,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>lead oxide, power-module trace engineering reference</t>
+          <t xml:space="preserve">lead oxide production, for power modules</t>
         </is>
       </c>
       <c r="B733">
@@ -23500,12 +23505,12 @@
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>lead oxide, power-module trace engineering reference</t>
+          <t xml:space="preserve">lead oxide, for power modules</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>lead oxide, power-module trace engineering reference</t>
+          <t xml:space="preserve">lead oxide, for power modules</t>
         </is>
       </c>
     </row>
@@ -23517,7 +23522,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+          <t xml:space="preserve">converter production, industrial, AC-DC, 1 MW</t>
         </is>
       </c>
     </row>
@@ -23551,7 +23556,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+          <t xml:space="preserve">converter, industrial, AC-DC, 1 MW</t>
         </is>
       </c>
     </row>
@@ -23587,7 +23592,8 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: industrial AC-DC converter, 1MW, component engineering reference. Former reference product: industrial AC-DC converter, 1MW, component engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
         </is>
       </c>
     </row>
@@ -23648,7 +23654,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+          <t xml:space="preserve">converter production, industrial, AC-DC, 1 MW</t>
         </is>
       </c>
       <c r="B745">
@@ -23671,12 +23677,12 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+          <t xml:space="preserve">converter, industrial, AC-DC, 1 MW</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+          <t xml:space="preserve">converter, industrial, AC-DC, 1 MW</t>
         </is>
       </c>
     </row>
@@ -23893,7 +23899,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>SiC half-bridge module, declared material engineering reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module production</t>
         </is>
       </c>
       <c r="B752">
@@ -23916,12 +23922,12 @@
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>SiC half-bridge module, declared material engineering reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>SiC half-bridge module, declared material engineering reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module</t>
         </is>
       </c>
     </row>
@@ -24143,7 +24149,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+          <t xml:space="preserve">transformer production, electrolysis, 1.1 MVA</t>
         </is>
       </c>
     </row>
@@ -24177,7 +24183,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+          <t xml:space="preserve">transformer, electrolysis, 1.1 MVA</t>
         </is>
       </c>
     </row>
@@ -24213,7 +24219,8 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: electrolyzer dedicated transformer, 1.1MVA, engineering reference. Former reference product: electrolyzer dedicated transformer, 1.1MVA, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
         </is>
       </c>
     </row>
@@ -24274,7 +24281,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+          <t xml:space="preserve">transformer production, electrolysis, 1.1 MVA</t>
         </is>
       </c>
       <c r="B770">
@@ -24297,12 +24304,12 @@
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+          <t xml:space="preserve">transformer, electrolysis, 1.1 MVA</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
         <is>
-          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+          <t xml:space="preserve">transformer, electrolysis, 1.1 MVA</t>
         </is>
       </c>
     </row>
@@ -24944,7 +24951,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+          <t xml:space="preserve">power conversion system production, electrolysis, transformer and rectifier, 1 MW</t>
         </is>
       </c>
     </row>
@@ -24978,7 +24985,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+          <t xml:space="preserve">power conversion system, electrolysis, transformer and rectifier, 1 MW</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25021,8 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: electrolyzer power conversion, 1MW, transformer and rectifier engineering reference. Former reference product: electrolyzer power conversion, 1MW, transformer and rectifier engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
         </is>
       </c>
     </row>
@@ -25075,7 +25083,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+          <t xml:space="preserve">power conversion system production, electrolysis, transformer and rectifier, 1 MW</t>
         </is>
       </c>
       <c r="B800">
@@ -25098,19 +25106,19 @@
       </c>
       <c r="G800" t="inlineStr">
         <is>
-          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+          <t xml:space="preserve">power conversion system, electrolysis, transformer and rectifier, 1 MW</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>electrolyzer power conversion, 1MW, transformer and rectifier engineering reference</t>
+          <t xml:space="preserve">power conversion system, electrolysis, transformer and rectifier, 1 MW</t>
         </is>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+          <t xml:space="preserve">converter production, industrial, AC-DC, 1 MW</t>
         </is>
       </c>
       <c r="B801">
@@ -25133,19 +25141,19 @@
       </c>
       <c r="G801" t="inlineStr">
         <is>
-          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+          <t xml:space="preserve">converter, industrial, AC-DC, 1 MW</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
         <is>
-          <t>industrial AC-DC converter, 1MW, component engineering reference</t>
+          <t xml:space="preserve">converter, industrial, AC-DC, 1 MW</t>
         </is>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+          <t xml:space="preserve">transformer production, electrolysis, 1.1 MVA</t>
         </is>
       </c>
       <c r="B802">
@@ -25168,12 +25176,12 @@
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+          <t xml:space="preserve">transformer, electrolysis, 1.1 MVA</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
         <is>
-          <t>electrolyzer dedicated transformer, 1.1MVA, engineering reference</t>
+          <t xml:space="preserve">transformer, electrolysis, 1.1 MVA</t>
         </is>
       </c>
     </row>
@@ -25185,7 +25193,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">treatment of used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
     </row>
@@ -25219,7 +25227,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
     </row>
@@ -25255,7 +25263,8 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: treatment of electrolyzer power conversion, 1MW, engineering reference. Former reference product: treatment of electrolyzer power conversion, 1MW, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
         </is>
       </c>
     </row>
@@ -25316,7 +25325,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">treatment of used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
       <c r="B814">
@@ -25339,12 +25348,12 @@
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
     </row>
@@ -25706,7 +25715,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+          <t xml:space="preserve">contact ceramic production, lanthanum strontium manganite, La0.8Sr0.2MnO3</t>
         </is>
       </c>
     </row>
@@ -25740,7 +25749,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+          <t xml:space="preserve">contact ceramic, lanthanum strontium manganite, La0.8Sr0.2MnO3</t>
         </is>
       </c>
     </row>
@@ -25776,7 +25785,8 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>APPROVED COMPLETE SOEC LSM REFERENCE, issue94, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis. Replace uncertain21kgLa2O3+21kgSrCO3 placeholders (both formerly to-check) by2.1kgfinishedLa0.8Sr0.2MnO3 perexistingMWstack. This is an explicit published-reference adoption, NOT recovered manufacturer BOM or proof that originalGerloff21kg meant2.1kg. Source-dose sensitivity2.1-21kgfinishedLSM required; old42kgrawsalts is not a chemically defined alternative. La0.8Sr0.2MnO3 is selected nominal oxygen-stoichiometric LSM; actual Sr doping/oxygen nonstoichiometry/contact-layer loading remain gaps. Net reaction0.4La2O3+0.2SrCO3+MnO2 -&gt;La0.8Sr0.2MnO3+0.2CO2+0.2O2. Use95% finished-solid retention,100% conversion before5%handlingreject; yields90-100%sensitivity. Perkgfinished feeds={'La2O3': 0.5923666319735489, 'SrCO3': 0.13420468074687047, 'MnO2': 0.3951562044603966};CO2=0.040007409129630044kg,O2=0.02908852910381745kg,reject=0.05263157894736836kg.6MJ/kgheat+1kWh/kgmilling/sintering is an engineering allowance,not measured industrial calcination (3-12MJ and0.5-2kWhsensitivity). All stoichiometric C/La/Sr/Mn/O and mass close. No nitric-acid/chloroacetic-acid/ammonia route or unsupported metal-free binder is silently copied. Keep totalfinished2.1kg distinct from grossprecursorfeed. Newsolidwaste andfinishedceramic EOL use genericinertdisposal,not validated heavy-metal-specific treatment/recovery. Existing Pr/Ni air-electrode,YSZ/YDCfutureco-scaling,glassseal,steelmass,lifetimes andoperatingH2energy unchanged. No primary/secondary-share or runtime changes.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference. Former reference product: LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED COMPLETE SOEC LSM REFERENCE, issue94, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.3, Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1 identifies LSM coating on interconnects, not electrolyte. Wei et al.2024 DOI10.1039/D3EE03875K indexed SI TableS17 reports2.1kg finishedLSM perMW; full SI retrieval currently404. Original Gerloff PtM SI DOI10.1021/acssuschemeng.1c02002 pS16 defers La/Sr quantities to a separate material-generation sheet. Stoichiometry below is independently balanced, not copied from the deficient indexed S18 synthesis. Replace uncertain21kgLa2O3+21kgSrCO3 placeholders (both formerly to-check) by2.1kgfinishedLa0.8Sr0.2MnO3 perexistingMWstack. This is an explicit published-reference adoption, NOT recovered manufacturer BOM or proof that originalGerloff21kg meant2.1kg. Source-dose sensitivity2.1-21kgfinishedLSM required; old42kgrawsalts is not a chemically defined alternative. La0.8Sr0.2MnO3 is selected nominal oxygen-stoichiometric LSM; actual Sr doping/oxygen nonstoichiometry/contact-layer loading remain gaps. Net reaction0.4La2O3+0.2SrCO3+MnO2 -&gt;La0.8Sr0.2MnO3+0.2CO2+0.2O2. Use95% finished-solid retention,100% conversion before5%handlingreject; yields90-100%sensitivity. Perkgfinished feeds={'La2O3': 0.5923666319735489, 'SrCO3': 0.13420468074687047, 'MnO2': 0.3951562044603966};CO2=0.040007409129630044kg,O2=0.02908852910381745kg,reject=0.05263157894736836kg.6MJ/kgheat+1kWh/kgmilling/sintering is an engineering allowance,not measured industrial calcination (3-12MJ and0.5-2kWhsensitivity). All stoichiometric C/La/Sr/Mn/O and mass close. No nitric-acid/chloroacetic-acid/ammonia route or unsupported metal-free binder is silently copied. Keep totalfinished2.1kg distinct from grossprecursorfeed. Newsolidwaste andfinishedceramic EOL use genericinertdisposal,not validated heavy-metal-specific treatment/recovery. Existing Pr/Ni air-electrode,YSZ/YDCfutureco-scaling,glassseal,steelmass,lifetimes andoperatingH2energy unchanged. No primary/secondary-share or runtime changes.</t>
         </is>
       </c>
     </row>
@@ -25837,7 +25847,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+          <t xml:space="preserve">contact ceramic production, lanthanum strontium manganite, La0.8Sr0.2MnO3</t>
         </is>
       </c>
       <c r="B836">
@@ -25860,12 +25870,12 @@
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+          <t xml:space="preserve">contact ceramic, lanthanum strontium manganite, La0.8Sr0.2MnO3</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
         <is>
-          <t>LSM contact ceramic, La0.8Sr0.2MnO3, balanced reference</t>
+          <t xml:space="preserve">contact ceramic, lanthanum strontium manganite, La0.8Sr0.2MnO3</t>
         </is>
       </c>
     </row>
@@ -26147,7 +26157,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+          <t xml:space="preserve">lanthanum metal production, oxide electrolysis</t>
         </is>
       </c>
     </row>
@@ -26181,7 +26191,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+          <t xml:space="preserve">lanthanum metal, oxide electrolysis</t>
         </is>
       </c>
     </row>
@@ -26217,7 +26227,8 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>APPROVED SOEC FERRITIC INTERCONNECT REFERENCE, issue95, 2026-10-18. Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1:chromiumsteelplate-&gt;deepdrawing+LSMcoating-&gt;interconnect; main stackdescription2outer3kg and4inner145g plates. Gerloff2021 PtM SI pS16 retains8976.1kg18/8steel but labels air-electrode. VDM Crofer22APU datasheet4146rev01 March2022 Table2 andApplications p5 explicitly SOEC interconnects/bipolarplates:Cr20-24wt%,Mn0.30-0.80,Ti0.03-0.20,La0.04-0.20,Fe balance. https://www.vdm-metals.com/fileadmin/user_upload/Downloads/Data_Sheets/Data_Sheet_VDM_Crofer_22_APU.pdf . Sourceflow8976.1kg is treated as the interconnectplate package based on originalmanufacturingdiagram,not9tair-electrodecatalyst. AdoptCrofer22APU-type reference for THIS stackinput only; do not replace ordinaryBoP18/8heat exchangers. Preserve8976.1kgfinishedsteel and8976.1kgexistingrollingservice; mass derives labstackscaleup and is NOT independently validated industrialMWgeometry. Preserve priorLSM,PrNi,ceramics,stackreplacement andlearning. Reference alloy massfractions={'Cr': 0.22, 'Mn': 0.005, 'Ti': 0.001, 'La': 0.001, 'Si': 0.001, 'Al': 0.0005, 'Cu': 0.0005, 'C': 0.0001, 'P': 5e-05, 'S': 5e-05, 'Fe': 0.7708}. Midrange/lowresidual choices are explicit assumptions within publishedranges,not measured heat assay. No intentionalNi addition; unknownresidualNi/othertraceimpurities are NOT provenzero. ActualoldNi8% cannot be claimed quantitatively without suppliercomposition; compareold18/8 as sensitivity. Cr20-24,Mn0.3-0.8,La0.04-0.20wt% sensitivities. Fe usesunalloyedsteel as feed-gradeproxy,withitsownminoralloys unresolved; completecomponentmetaluse is not identical toelementalpureFe. Addalloyingmaterialsonce and0.5kWh+2MJ/kgremeltingreference (0.25-1kWh/1-4MJsensitivity),not a completeCrsteel production dataset on top. Matchfinishedsteelmass1kgwith100%finalalloyretention; alloyingyield/slag andtracepickup remain gaps. La metal unavailable: explicit netoxide/carbon electrolyticreference La2O3+1.5C-&gt;2La+1.5CO2,95%metalretention,10kWh/kg+3MJ/kgassumed; fluoridebathmakeup,PFCemissions,purification andcalcium-route alternatives unresolved. Thisisstoichiometricnetelectrolysis,NOTthermal carbothermic reduction orvalidatedvendorLa process. Metalrejectgenericinertdisposal; La/C/O/massclose. FinishedinterconnectEOLexistingsteelcollection amount retained; genericsteelroute doesnotvalidatealloy-specificrecycling orrecoverycredits. Native/YAML/runtime/primary-secondaryshares untouched.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: lanthanum alloying metal, oxide-electrolysis net reference. Former reference product: lanthanum alloying metal, oxide-electrolysis net reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED SOEC FERRITIC INTERCONNECT REFERENCE, issue95, 2026-10-18. Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1:chromiumsteelplate-&gt;deepdrawing+LSMcoating-&gt;interconnect; main stackdescription2outer3kg and4inner145g plates. Gerloff2021 PtM SI pS16 retains8976.1kg18/8steel but labels air-electrode. VDM Crofer22APU datasheet4146rev01 March2022 Table2 andApplications p5 explicitly SOEC interconnects/bipolarplates:Cr20-24wt%,Mn0.30-0.80,Ti0.03-0.20,La0.04-0.20,Fe balance. https://www.vdm-metals.com/fileadmin/user_upload/Downloads/Data_Sheets/Data_Sheet_VDM_Crofer_22_APU.pdf . Sourceflow8976.1kg is treated as the interconnectplate package based on originalmanufacturingdiagram,not9tair-electrodecatalyst. AdoptCrofer22APU-type reference for THIS stackinput only; do not replace ordinaryBoP18/8heat exchangers. Preserve8976.1kgfinishedsteel and8976.1kgexistingrollingservice; mass derives labstackscaleup and is NOT independently validated industrialMWgeometry. Preserve priorLSM,PrNi,ceramics,stackreplacement andlearning. Reference alloy massfractions={'Cr': 0.22, 'Mn': 0.005, 'Ti': 0.001, 'La': 0.001, 'Si': 0.001, 'Al': 0.0005, 'Cu': 0.0005, 'C': 0.0001, 'P': 5e-05, 'S': 5e-05, 'Fe': 0.7708}. Midrange/lowresidual choices are explicit assumptions within publishedranges,not measured heat assay. No intentionalNi addition; unknownresidualNi/othertraceimpurities are NOT provenzero. ActualoldNi8% cannot be claimed quantitatively without suppliercomposition; compareold18/8 as sensitivity. Cr20-24,Mn0.3-0.8,La0.04-0.20wt% sensitivities. Fe usesunalloyedsteel as feed-gradeproxy,withitsownminoralloys unresolved; completecomponentmetaluse is not identical toelementalpureFe. Addalloyingmaterialsonce and0.5kWh+2MJ/kgremeltingreference (0.25-1kWh/1-4MJsensitivity),not a completeCrsteel production dataset on top. Matchfinishedsteelmass1kgwith100%finalalloyretention; alloyingyield/slag andtracepickup remain gaps. La metal unavailable: explicit netoxide/carbon electrolyticreference La2O3+1.5C-&gt;2La+1.5CO2,95%metalretention,10kWh/kg+3MJ/kgassumed; fluoridebathmakeup,PFCemissions,purification andcalcium-route alternatives unresolved. Thisisstoichiometricnetelectrolysis,NOTthermal carbothermic reduction orvalidatedvendorLa process. Metalrejectgenericinertdisposal; La/C/O/massclose. FinishedinterconnectEOLexistingsteelcollection amount retained; genericsteelroute doesnotvalidatealloy-specificrecycling orrecoverycredits. Native/YAML/runtime/primary-secondaryshares untouched.</t>
         </is>
       </c>
     </row>
@@ -26278,7 +26289,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+          <t xml:space="preserve">lanthanum metal production, oxide electrolysis</t>
         </is>
       </c>
       <c r="B856">
@@ -26301,12 +26312,12 @@
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+          <t xml:space="preserve">lanthanum metal, oxide electrolysis</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
         <is>
-          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+          <t xml:space="preserve">lanthanum metal, oxide electrolysis</t>
         </is>
       </c>
     </row>
@@ -26523,7 +26534,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+          <t xml:space="preserve">ferritic steel production, electrolysis interconnect, Crofer 22 APU type</t>
         </is>
       </c>
     </row>
@@ -26557,7 +26568,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+          <t xml:space="preserve">ferritic steel, electrolysis interconnect, Crofer 22 APU type</t>
         </is>
       </c>
     </row>
@@ -26593,7 +26604,8 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>APPROVED SOEC FERRITIC INTERCONNECT REFERENCE, issue95, 2026-10-18. Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1:chromiumsteelplate-&gt;deepdrawing+LSMcoating-&gt;interconnect; main stackdescription2outer3kg and4inner145g plates. Gerloff2021 PtM SI pS16 retains8976.1kg18/8steel but labels air-electrode. VDM Crofer22APU datasheet4146rev01 March2022 Table2 andApplications p5 explicitly SOEC interconnects/bipolarplates:Cr20-24wt%,Mn0.30-0.80,Ti0.03-0.20,La0.04-0.20,Fe balance. https://www.vdm-metals.com/fileadmin/user_upload/Downloads/Data_Sheets/Data_Sheet_VDM_Crofer_22_APU.pdf . Sourceflow8976.1kg is treated as the interconnectplate package based on originalmanufacturingdiagram,not9tair-electrodecatalyst. AdoptCrofer22APU-type reference for THIS stackinput only; do not replace ordinaryBoP18/8heat exchangers. Preserve8976.1kgfinishedsteel and8976.1kgexistingrollingservice; mass derives labstackscaleup and is NOT independently validated industrialMWgeometry. Preserve priorLSM,PrNi,ceramics,stackreplacement andlearning. Reference alloy massfractions={'Cr': 0.22, 'Mn': 0.005, 'Ti': 0.001, 'La': 0.001, 'Si': 0.001, 'Al': 0.0005, 'Cu': 0.0005, 'C': 0.0001, 'P': 5e-05, 'S': 5e-05, 'Fe': 0.7708}. Midrange/lowresidual choices are explicit assumptions within publishedranges,not measured heat assay. No intentionalNi addition; unknownresidualNi/othertraceimpurities are NOT provenzero. ActualoldNi8% cannot be claimed quantitatively without suppliercomposition; compareold18/8 as sensitivity. Cr20-24,Mn0.3-0.8,La0.04-0.20wt% sensitivities. Fe usesunalloyedsteel as feed-gradeproxy,withitsownminoralloys unresolved; completecomponentmetaluse is not identical toelementalpureFe. Addalloyingmaterialsonce and0.5kWh+2MJ/kgremeltingreference (0.25-1kWh/1-4MJsensitivity),not a completeCrsteel production dataset on top. Matchfinishedsteelmass1kgwith100%finalalloyretention; alloyingyield/slag andtracepickup remain gaps. La metal unavailable: explicit netoxide/carbon electrolyticreference La2O3+1.5C-&gt;2La+1.5CO2,95%metalretention,10kWh/kg+3MJ/kgassumed; fluoridebathmakeup,PFCemissions,purification andcalcium-route alternatives unresolved. Thisisstoichiometricnetelectrolysis,NOTthermal carbothermic reduction orvalidatedvendorLa process. Metalrejectgenericinertdisposal; La/C/O/massclose. FinishedinterconnectEOLexistingsteelcollection amount retained; genericsteelroute doesnotvalidatealloy-specificrecycling orrecoverycredits. Native/YAML/runtime/primary-secondaryshares untouched.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: ferritic interconnect steel, Crofer22APU-type engineering reference. Former reference product: ferritic interconnect steel, Crofer22APU-type engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED SOEC FERRITIC INTERCONNECT REFERENCE, issue95, 2026-10-18. Hafele2016 DOI10.1016/j.ijhydene.2016.05.069 SI FigS1:chromiumsteelplate-&gt;deepdrawing+LSMcoating-&gt;interconnect; main stackdescription2outer3kg and4inner145g plates. Gerloff2021 PtM SI pS16 retains8976.1kg18/8steel but labels air-electrode. VDM Crofer22APU datasheet4146rev01 March2022 Table2 andApplications p5 explicitly SOEC interconnects/bipolarplates:Cr20-24wt%,Mn0.30-0.80,Ti0.03-0.20,La0.04-0.20,Fe balance. https://www.vdm-metals.com/fileadmin/user_upload/Downloads/Data_Sheets/Data_Sheet_VDM_Crofer_22_APU.pdf . Sourceflow8976.1kg is treated as the interconnectplate package based on originalmanufacturingdiagram,not9tair-electrodecatalyst. AdoptCrofer22APU-type reference for THIS stackinput only; do not replace ordinaryBoP18/8heat exchangers. Preserve8976.1kgfinishedsteel and8976.1kgexistingrollingservice; mass derives labstackscaleup and is NOT independently validated industrialMWgeometry. Preserve priorLSM,PrNi,ceramics,stackreplacement andlearning. Reference alloy massfractions={'Cr': 0.22, 'Mn': 0.005, 'Ti': 0.001, 'La': 0.001, 'Si': 0.001, 'Al': 0.0005, 'Cu': 0.0005, 'C': 0.0001, 'P': 5e-05, 'S': 5e-05, 'Fe': 0.7708}. Midrange/lowresidual choices are explicit assumptions within publishedranges,not measured heat assay. No intentionalNi addition; unknownresidualNi/othertraceimpurities are NOT provenzero. ActualoldNi8% cannot be claimed quantitatively without suppliercomposition; compareold18/8 as sensitivity. Cr20-24,Mn0.3-0.8,La0.04-0.20wt% sensitivities. Fe usesunalloyedsteel as feed-gradeproxy,withitsownminoralloys unresolved; completecomponentmetaluse is not identical toelementalpureFe. Addalloyingmaterialsonce and0.5kWh+2MJ/kgremeltingreference (0.25-1kWh/1-4MJsensitivity),not a completeCrsteel production dataset on top. Matchfinishedsteelmass1kgwith100%finalalloyretention; alloyingyield/slag andtracepickup remain gaps. La metal unavailable: explicit netoxide/carbon electrolyticreference La2O3+1.5C-&gt;2La+1.5CO2,95%metalretention,10kWh/kg+3MJ/kgassumed; fluoridebathmakeup,PFCemissions,purification andcalcium-route alternatives unresolved. Thisisstoichiometricnetelectrolysis,NOTthermal carbothermic reduction orvalidatedvendorLa process. Metalrejectgenericinertdisposal; La/C/O/massclose. FinishedinterconnectEOLexistingsteelcollection amount retained; genericsteelroute doesnotvalidatealloy-specificrecycling orrecoverycredits. Native/YAML/runtime/primary-secondaryshares untouched.</t>
         </is>
       </c>
     </row>
@@ -26654,7 +26666,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+          <t xml:space="preserve">ferritic steel production, electrolysis interconnect, Crofer 22 APU type</t>
         </is>
       </c>
       <c r="B874">
@@ -26677,12 +26689,12 @@
       </c>
       <c r="G874" t="inlineStr">
         <is>
-          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+          <t xml:space="preserve">ferritic steel, electrolysis interconnect, Crofer 22 APU type</t>
         </is>
       </c>
       <c r="I874" t="inlineStr">
         <is>
-          <t>ferritic interconnect steel, Crofer22APU-type engineering reference</t>
+          <t xml:space="preserve">ferritic steel, electrolysis interconnect, Crofer 22 APU type</t>
         </is>
       </c>
     </row>
@@ -26794,7 +26806,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+          <t xml:space="preserve">lanthanum metal production, oxide electrolysis</t>
         </is>
       </c>
       <c r="B878">
@@ -26817,12 +26829,12 @@
       </c>
       <c r="G878" t="inlineStr">
         <is>
-          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+          <t xml:space="preserve">lanthanum metal, oxide electrolysis</t>
         </is>
       </c>
       <c r="I878" t="inlineStr">
         <is>
-          <t>lanthanum alloying metal, oxide-electrolysis net reference</t>
+          <t xml:space="preserve">lanthanum metal, oxide electrolysis</t>
         </is>
       </c>
     </row>
@@ -27149,7 +27161,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+          <t xml:space="preserve">diaphragm production, alkaline electrolysis, zirconia-polysulfone with PPS mesh</t>
         </is>
       </c>
     </row>
@@ -27183,7 +27195,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+          <t xml:space="preserve">diaphragm, alkaline electrolysis, zirconia-polysulfone with PPS mesh</t>
         </is>
       </c>
     </row>
@@ -27219,7 +27231,8 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference. Former reference product: AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED REINFORCED AEC DIAPHRAGM REFERENCE, issue96, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 Sec2.2.1 explicitly assumed40%PSU/60%ZrO2 fromAgfa;not a transcriptionerror. Rodriguez et al.2019 DOI10.3390/membranes9100129 reports85wt%ZrO2/15wt%PSU and500+/-50umthickness,1+/-0.2g/cm3weightdensity; microscopy showsmesh. Lee2020 DOI10.1016/j.memsci.2020.118541 uses purchasedPPSmesh; patent KR20190135273A describes200ummesh. Geometry below is engineering,not manufacturerclothspecification. Replace48.8kgPSU+73kgZrO2 with121.8kgfinisheddryZirfon-typeengineeringmembrane,notcertifiedAgfaUTP500recipe. Preserveoldtotaldrymass asreferenceassumption;actualoldwet/drybasisunknown. Selected500umfinishedthickness,0.5kg/m2dryarealmass implies243.6m2/MW at121.8kg. SupportwovenPPS100umfilaments/200umpitch/twodirections/1.05crimp,rho1350kg/m3 gives0.11133018966158831kgPPS/m2 and0.22266037932317662fractionofdrymembrane. Theseclothgeometryvaluesareexplicitassumptions,notmeasuredPVFmesh. Remainingcoating0.7773396206768234massfractionuses85/15ZrO2/PSU. Finishedfractions={'PPS': 0.22266037932317662, 'ZrO2': 0.6607386775752998, 'PSU': 0.1166009431015235};usingZrO2rho5680,PSU1240andPPS1350,computedporosity=0.6247061350887926consistentwith45-65%referenceinterval. Do notmistake85/15coatingforwholemembrane. Sensitivitysupport10-30wt%,coatingZr75-85wt%,arealmass0.4-0.6kg/m2,thickness450-550um;notallcombinationsarephysicallycompatible. Coating95%retention,mesh100%,1kWh/kgforming/dryingallowance;freshNMP0.2kg/kgretainedcoating assumes4kgcirculationand95%recovery,solventmakeupalltosolventwaste.10kgprocesswater/kgfinishedandgenericWWT;salinity,coagulationkinetics,soluteemissions,membranegasbarrieranddurabilityqualificationgaps remain. Sourcegross121.8kgisnotindependentlyverifiedfor2026plant. MatchedfinishedEOLroutesneworganicPPS/PSUfractiontogenericplasticincinerationandZrO2togenericinertdisposal;old193kgmixedplasticwasteincluded144.2gasket+48.8PSU,replaceonly48.8PSUshare,leavegasketuntilissue100. No phantommetalrecoverycredit;otherstackmetals,lifetime,energy unchanged.</t>
         </is>
       </c>
     </row>
@@ -27280,7 +27293,7 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+          <t xml:space="preserve">diaphragm production, alkaline electrolysis, zirconia-polysulfone with PPS mesh</t>
         </is>
       </c>
       <c r="B899">
@@ -27303,12 +27316,12 @@
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+          <t xml:space="preserve">diaphragm, alkaline electrolysis, zirconia-polysulfone with PPS mesh</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
         <is>
-          <t>AEC reinforced diaphragm, zirconia-PSU with PPS mesh reference</t>
+          <t xml:space="preserve">diaphragm, alkaline electrolysis, zirconia-polysulfone with PPS mesh</t>
         </is>
       </c>
     </row>
@@ -27635,7 +27648,7 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch production, electrolysis motor drive, 1200 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -27669,7 +27682,7 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 1200 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -27705,7 +27718,8 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference. Former reference product: Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
         </is>
       </c>
     </row>
@@ -27766,7 +27780,7 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch production, electrolysis motor drive, 1200 V, TO-247</t>
         </is>
       </c>
       <c r="B920">
@@ -27789,12 +27803,12 @@
       </c>
       <c r="G920" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 1200 V, TO-247</t>
         </is>
       </c>
       <c r="I920" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 1200 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -28261,7 +28275,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch production, electrolysis motor drive, 650 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -28295,7 +28309,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 650 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -28331,7 +28345,8 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference. Former reference product: Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
         </is>
       </c>
     </row>
@@ -28392,7 +28407,7 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch production, electrolysis motor drive, 650 V, TO-247</t>
         </is>
       </c>
       <c r="B945">
@@ -28415,12 +28430,12 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 650 V, TO-247</t>
         </is>
       </c>
       <c r="I945" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 650 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -28887,7 +28902,7 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module production, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
     </row>
@@ -28921,7 +28936,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
     </row>
@@ -28957,7 +28972,8 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference. Former reference product: Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
         </is>
       </c>
     </row>
@@ -29018,7 +29034,7 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module production, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
       <c r="B970">
@@ -29041,12 +29057,12 @@
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
       <c r="I970" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
     </row>
@@ -29373,7 +29389,7 @@
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>industrial motor drive, 75kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive production, industrial, 75 kW</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29423,7 @@
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>industrial motor drive, 75kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 75 kW</t>
         </is>
       </c>
     </row>
@@ -29443,7 +29459,8 @@
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients. Thisframe:installedmass=41.2016kg;EPDbulkledger={'steel': 21.069, 'Al': 6.74208, 'Cu': 3.37104, 'PC': 2.4814599999999998, 'ABS': 1.73234, 'electronics': 3.60514};unresolvedotherelectronics=0.11513999999999995kg;unresolvedtotaloutsidepackage=2.3156800000000035kg,pluscomponentmoduleunknownwhereapplicable. Packagingpaperusescorrugated-boxproxy,EPPusesPPresinwithoutverifiedfoamprocessing,SEBSusesgeneric syntheticrubberproxywithunvalidatedhydrogenation/grade,PCusesRoWproductionproxytoavoidunsupportedpre3.10regionalmarket.1kWh/driveon-siteassemblyallowanceassumed,notEPDmeasuredenergy.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: industrial motor drive, 75kW auxiliary reference. Former reference product: industrial motor drive, 75kW auxiliary reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients. Thisframe:installedmass=41.2016kg;EPDbulkledger={'steel': 21.069, 'Al': 6.74208, 'Cu': 3.37104, 'PC': 2.4814599999999998, 'ABS': 1.73234, 'electronics': 3.60514};unresolvedotherelectronics=0.11513999999999995kg;unresolvedtotaloutsidepackage=2.3156800000000035kg,pluscomponentmoduleunknownwhereapplicable. Packagingpaperusescorrugated-boxproxy,EPPusesPPresinwithoutverifiedfoamprocessing,SEBSusesgeneric syntheticrubberproxywithunvalidatedhydrogenation/grade,PCusesRoWproductionproxytoavoidunsupportedpre3.10regionalmarket.1kWh/driveon-siteassemblyallowanceassumed,notEPDmeasuredenergy.</t>
         </is>
       </c>
     </row>
@@ -29504,7 +29521,7 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>industrial motor drive, 75kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive production, industrial, 75 kW</t>
         </is>
       </c>
       <c r="B991">
@@ -29527,12 +29544,12 @@
       </c>
       <c r="G991" t="inlineStr">
         <is>
-          <t>industrial motor drive, 75kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 75 kW</t>
         </is>
       </c>
       <c r="I991" t="inlineStr">
         <is>
-          <t>industrial motor drive, 75kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 75 kW</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29731,7 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module production, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
       <c r="B997">
@@ -29737,12 +29754,12 @@
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
       <c r="I997" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference</t>
+          <t xml:space="preserve">silicon carbide half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30051,7 @@
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>industrial motor drive, 15kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive production, industrial, 15 kW</t>
         </is>
       </c>
     </row>
@@ -30068,7 +30085,7 @@
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>industrial motor drive, 15kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 15 kW</t>
         </is>
       </c>
     </row>
@@ -30104,7 +30121,8 @@
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients. Thisframe:installedmass=10.3292kg;EPDbulkledger={'steel': 2.3205, 'Al': 2.6299, 'PC': 2.2491, 'ABS': 0.6069, 'SEBS': 0.1071, 'electronics': 1.8683};unresolvedotherelectronics=0.14572770800000007kg;unresolvedtotaloutsidepackage=0.6931277079999998kg,pluscomponentmoduleunknownwhereapplicable. Packagingpaperusescorrugated-boxproxy,EPPusesPPresinwithoutverifiedfoamprocessing,SEBSusesgeneric syntheticrubberproxywithunvalidatedhydrogenation/grade,PCusesRoWproductionproxytoavoidunsupportedpre3.10regionalmarket.1kWh/driveon-siteassemblyallowanceassumed,notEPDmeasuredenergy.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: industrial motor drive, 15kW auxiliary reference. Former reference product: industrial motor drive, 15kW auxiliary reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients. Thisframe:installedmass=10.3292kg;EPDbulkledger={'steel': 2.3205, 'Al': 2.6299, 'PC': 2.2491, 'ABS': 0.6069, 'SEBS': 0.1071, 'electronics': 1.8683};unresolvedotherelectronics=0.14572770800000007kg;unresolvedtotaloutsidepackage=0.6931277079999998kg,pluscomponentmoduleunknownwhereapplicable. Packagingpaperusescorrugated-boxproxy,EPPusesPPresinwithoutverifiedfoamprocessing,SEBSusesgeneric syntheticrubberproxywithunvalidatedhydrogenation/grade,PCusesRoWproductionproxytoavoidunsupportedpre3.10regionalmarket.1kWh/driveon-siteassemblyallowanceassumed,notEPDmeasuredenergy.</t>
         </is>
       </c>
     </row>
@@ -30165,7 +30183,7 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>industrial motor drive, 15kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive production, industrial, 15 kW</t>
         </is>
       </c>
       <c r="B1017">
@@ -30188,12 +30206,12 @@
       </c>
       <c r="G1017" t="inlineStr">
         <is>
-          <t>industrial motor drive, 15kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 15 kW</t>
         </is>
       </c>
       <c r="I1017" t="inlineStr">
         <is>
-          <t>industrial motor drive, 15kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 15 kW</t>
         </is>
       </c>
     </row>
@@ -30375,7 +30393,7 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch production, electrolysis motor drive, 1200 V, TO-247</t>
         </is>
       </c>
       <c r="B1023">
@@ -30398,12 +30416,12 @@
       </c>
       <c r="G1023" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 1200 V, TO-247</t>
         </is>
       </c>
       <c r="I1023" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 1200 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -30695,7 +30713,7 @@
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive production, industrial, 1.1 kW</t>
         </is>
       </c>
     </row>
@@ -30729,7 +30747,7 @@
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 1.1 kW</t>
         </is>
       </c>
     </row>
@@ -30765,7 +30783,8 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients. Thisframe:installedmass=7.586410000000001kg;EPDbulkledger={'steel': 1.4545700000000001, 'Al': 1.4284400000000002, 'Cu': 0.29614000000000007, 'PC': 1.9162000000000001, 'ABS': 0.7403500000000002, 'electronics': 1.3413400000000002};unresolvedotherelectronics=0.20877296400000028kg;unresolvedtotaloutsidepackage=0.6181429639999994kg,pluscomponentmoduleunknownwhereapplicable. Packagingpaperusescorrugated-boxproxy,EPPusesPPresinwithoutverifiedfoamprocessing,SEBSusesgeneric syntheticrubberproxywithunvalidatedhydrogenation/grade,PCusesRoWproductionproxytoavoidunsupportedpre3.10regionalmarket.1kWh/driveon-siteassemblyallowanceassumed,notEPDmeasuredenergy.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: industrial motor drive, 1.1kW auxiliary reference. Former reference product: industrial motor drive, 1.1kW auxiliary reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients. Thisframe:installedmass=7.586410000000001kg;EPDbulkledger={'steel': 1.4545700000000001, 'Al': 1.4284400000000002, 'Cu': 0.29614000000000007, 'PC': 1.9162000000000001, 'ABS': 0.7403500000000002, 'electronics': 1.3413400000000002};unresolvedotherelectronics=0.20877296400000028kg;unresolvedtotaloutsidepackage=0.6181429639999994kg,pluscomponentmoduleunknownwhereapplicable. Packagingpaperusescorrugated-boxproxy,EPPusesPPresinwithoutverifiedfoamprocessing,SEBSusesgeneric syntheticrubberproxywithunvalidatedhydrogenation/grade,PCusesRoWproductionproxytoavoidunsupportedpre3.10regionalmarket.1kWh/driveon-siteassemblyallowanceassumed,notEPDmeasuredenergy.</t>
         </is>
       </c>
     </row>
@@ -30826,7 +30845,7 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive production, industrial, 1.1 kW</t>
         </is>
       </c>
       <c r="B1043">
@@ -30849,12 +30868,12 @@
       </c>
       <c r="G1043" t="inlineStr">
         <is>
-          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 1.1 kW</t>
         </is>
       </c>
       <c r="I1043" t="inlineStr">
         <is>
-          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 1.1 kW</t>
         </is>
       </c>
     </row>
@@ -31036,7 +31055,7 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch production, electrolysis motor drive, 650 V, TO-247</t>
         </is>
       </c>
       <c r="B1049">
@@ -31059,12 +31078,12 @@
       </c>
       <c r="G1049" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 650 V, TO-247</t>
         </is>
       </c>
       <c r="I1049" t="inlineStr">
         <is>
-          <t>Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference</t>
+          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 650 V, TO-247</t>
         </is>
       </c>
     </row>
@@ -31356,7 +31375,7 @@
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">motor drive assembly production, electrolysis, PEM</t>
         </is>
       </c>
     </row>
@@ -31390,7 +31409,7 @@
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">motor drive assembly, electrolysis, PEM</t>
         </is>
       </c>
     </row>
@@ -31426,7 +31445,8 @@
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: electrolyzer auxiliary drive lifetime kit, PEM, reference. Former reference product: electrolyzer auxiliary drive lifetime kit, PEM, reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
     </row>
@@ -31487,7 +31507,7 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">motor drive assembly production, electrolysis, PEM</t>
         </is>
       </c>
       <c r="B1069">
@@ -31510,19 +31530,19 @@
       </c>
       <c r="G1069" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">motor drive assembly, electrolysis, PEM</t>
         </is>
       </c>
       <c r="I1069" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">motor drive assembly, electrolysis, PEM</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>industrial motor drive, 75kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive production, industrial, 75 kW</t>
         </is>
       </c>
       <c r="B1070">
@@ -31545,12 +31565,12 @@
       </c>
       <c r="G1070" t="inlineStr">
         <is>
-          <t>industrial motor drive, 75kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 75 kW</t>
         </is>
       </c>
       <c r="I1070" t="inlineStr">
         <is>
-          <t>industrial motor drive, 75kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 75 kW</t>
         </is>
       </c>
     </row>
@@ -31562,7 +31582,7 @@
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">treatment of used motor drive assembly, electrolysis, PEM</t>
         </is>
       </c>
     </row>
@@ -31596,7 +31616,7 @@
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, PEM</t>
         </is>
       </c>
     </row>
@@ -31632,7 +31652,8 @@
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference. Former reference product: treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
     </row>
@@ -31693,7 +31714,7 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">treatment of used motor drive assembly, electrolysis, PEM</t>
         </is>
       </c>
       <c r="B1082">
@@ -31716,12 +31737,12 @@
       </c>
       <c r="G1082" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, PEM</t>
         </is>
       </c>
       <c r="I1082" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, PEM</t>
         </is>
       </c>
     </row>
@@ -31768,7 +31789,7 @@
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
+          <t xml:space="preserve">treatment of used power conversion system and motor drives, electrolysis, PEM</t>
         </is>
       </c>
     </row>
@@ -31802,7 +31823,7 @@
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
+          <t xml:space="preserve">used power conversion system and motor drives, electrolysis, PEM</t>
         </is>
       </c>
     </row>
@@ -31838,7 +31859,8 @@
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: treatment of electrolyzer power conversion and auxiliary drives, PEM, reference. Former reference product: treatment of electrolyzer power conversion and auxiliary drives, PEM, reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31921,7 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
+          <t xml:space="preserve">treatment of used power conversion system and motor drives, electrolysis, PEM</t>
         </is>
       </c>
       <c r="B1095">
@@ -31922,19 +31944,19 @@
       </c>
       <c r="G1095" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
+          <t xml:space="preserve">used power conversion system and motor drives, electrolysis, PEM</t>
         </is>
       </c>
       <c r="I1095" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, PEM, reference</t>
+          <t xml:space="preserve">used power conversion system and motor drives, electrolysis, PEM</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">treatment of used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
       <c r="B1096">
@@ -31957,19 +31979,19 @@
       </c>
       <c r="G1096" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
       <c r="I1096" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">treatment of used motor drive assembly, electrolysis, PEM</t>
         </is>
       </c>
       <c r="B1097">
@@ -31992,12 +32014,12 @@
       </c>
       <c r="G1097" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, PEM</t>
         </is>
       </c>
       <c r="I1097" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, PEM, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, PEM</t>
         </is>
       </c>
     </row>
@@ -32009,7 +32031,7 @@
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">motor drive assembly production, electrolysis, AEC</t>
         </is>
       </c>
     </row>
@@ -32043,7 +32065,7 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">motor drive assembly, electrolysis, AEC</t>
         </is>
       </c>
     </row>
@@ -32079,7 +32101,8 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: electrolyzer auxiliary drive lifetime kit, AEC, reference. Former reference product: electrolyzer auxiliary drive lifetime kit, AEC, reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
     </row>
@@ -32140,7 +32163,7 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">motor drive assembly production, electrolysis, AEC</t>
         </is>
       </c>
       <c r="B1109">
@@ -32163,19 +32186,19 @@
       </c>
       <c r="G1109" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">motor drive assembly, electrolysis, AEC</t>
         </is>
       </c>
       <c r="I1109" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">motor drive assembly, electrolysis, AEC</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>industrial motor drive, 75kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive production, industrial, 75 kW</t>
         </is>
       </c>
       <c r="B1110">
@@ -32198,12 +32221,12 @@
       </c>
       <c r="G1110" t="inlineStr">
         <is>
-          <t>industrial motor drive, 75kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 75 kW</t>
         </is>
       </c>
       <c r="I1110" t="inlineStr">
         <is>
-          <t>industrial motor drive, 75kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 75 kW</t>
         </is>
       </c>
     </row>
@@ -32215,7 +32238,7 @@
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">treatment of used motor drive assembly, electrolysis, AEC</t>
         </is>
       </c>
     </row>
@@ -32249,7 +32272,7 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, AEC</t>
         </is>
       </c>
     </row>
@@ -32285,7 +32308,8 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference. Former reference product: treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
     </row>
@@ -32346,7 +32370,7 @@
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">treatment of used motor drive assembly, electrolysis, AEC</t>
         </is>
       </c>
       <c r="B1122">
@@ -32369,12 +32393,12 @@
       </c>
       <c r="G1122" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, AEC</t>
         </is>
       </c>
       <c r="I1122" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, AEC</t>
         </is>
       </c>
     </row>
@@ -32421,7 +32445,7 @@
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
+          <t xml:space="preserve">treatment of used power conversion system and motor drives, electrolysis, AEC</t>
         </is>
       </c>
     </row>
@@ -32455,7 +32479,7 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
+          <t xml:space="preserve">used power conversion system and motor drives, electrolysis, AEC</t>
         </is>
       </c>
     </row>
@@ -32491,7 +32515,8 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: treatment of electrolyzer power conversion and auxiliary drives, AEC, reference. Former reference product: treatment of electrolyzer power conversion and auxiliary drives, AEC, reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
     </row>
@@ -32552,7 +32577,7 @@
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
+          <t xml:space="preserve">treatment of used power conversion system and motor drives, electrolysis, AEC</t>
         </is>
       </c>
       <c r="B1135">
@@ -32575,19 +32600,19 @@
       </c>
       <c r="G1135" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
+          <t xml:space="preserve">used power conversion system and motor drives, electrolysis, AEC</t>
         </is>
       </c>
       <c r="I1135" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, AEC, reference</t>
+          <t xml:space="preserve">used power conversion system and motor drives, electrolysis, AEC</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">treatment of used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
       <c r="B1136">
@@ -32610,19 +32635,19 @@
       </c>
       <c r="G1136" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
       <c r="I1136" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">treatment of used motor drive assembly, electrolysis, AEC</t>
         </is>
       </c>
       <c r="B1137">
@@ -32645,12 +32670,12 @@
       </c>
       <c r="G1137" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, AEC</t>
         </is>
       </c>
       <c r="I1137" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, AEC, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, AEC</t>
         </is>
       </c>
     </row>
@@ -32662,7 +32687,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">motor drive assembly production, electrolysis, SOEC</t>
         </is>
       </c>
     </row>
@@ -32696,7 +32721,7 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">motor drive assembly, electrolysis, SOEC</t>
         </is>
       </c>
     </row>
@@ -32732,7 +32757,8 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: electrolyzer auxiliary drive lifetime kit, SOEC, reference. Former reference product: electrolyzer auxiliary drive lifetime kit, SOEC, reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
     </row>
@@ -32793,7 +32819,7 @@
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">motor drive assembly production, electrolysis, SOEC</t>
         </is>
       </c>
       <c r="B1149">
@@ -32816,19 +32842,19 @@
       </c>
       <c r="G1149" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">motor drive assembly, electrolysis, SOEC</t>
         </is>
       </c>
       <c r="I1149" t="inlineStr">
         <is>
-          <t>electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">motor drive assembly, electrolysis, SOEC</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>industrial motor drive, 15kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive production, industrial, 15 kW</t>
         </is>
       </c>
       <c r="B1150">
@@ -32851,19 +32877,19 @@
       </c>
       <c r="G1150" t="inlineStr">
         <is>
-          <t>industrial motor drive, 15kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 15 kW</t>
         </is>
       </c>
       <c r="I1150" t="inlineStr">
         <is>
-          <t>industrial motor drive, 15kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 15 kW</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive production, industrial, 1.1 kW</t>
         </is>
       </c>
       <c r="B1151">
@@ -32886,12 +32912,12 @@
       </c>
       <c r="G1151" t="inlineStr">
         <is>
-          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 1.1 kW</t>
         </is>
       </c>
       <c r="I1151" t="inlineStr">
         <is>
-          <t>industrial motor drive, 1.1kW auxiliary reference</t>
+          <t xml:space="preserve">motor drive, industrial, 1.1 kW</t>
         </is>
       </c>
     </row>
@@ -32903,7 +32929,7 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">treatment of used motor drive assembly, electrolysis, SOEC</t>
         </is>
       </c>
     </row>
@@ -32937,7 +32963,7 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, SOEC</t>
         </is>
       </c>
     </row>
@@ -32973,7 +32999,8 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference. Former reference product: treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
     </row>
@@ -33034,7 +33061,7 @@
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">treatment of used motor drive assembly, electrolysis, SOEC</t>
         </is>
       </c>
       <c r="B1163">
@@ -33057,12 +33084,12 @@
       </c>
       <c r="G1163" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, SOEC</t>
         </is>
       </c>
       <c r="I1163" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, SOEC</t>
         </is>
       </c>
     </row>
@@ -33109,7 +33136,7 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
+          <t xml:space="preserve">treatment of used power conversion system and motor drives, electrolysis, SOEC</t>
         </is>
       </c>
     </row>
@@ -33143,7 +33170,7 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
+          <t xml:space="preserve">used power conversion system and motor drives, electrolysis, SOEC</t>
         </is>
       </c>
     </row>
@@ -33179,7 +33206,8 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference. Former reference product: treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
         </is>
       </c>
     </row>
@@ -33240,7 +33268,7 @@
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
+          <t xml:space="preserve">treatment of used power conversion system and motor drives, electrolysis, SOEC</t>
         </is>
       </c>
       <c r="B1176">
@@ -33263,19 +33291,19 @@
       </c>
       <c r="G1176" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
+          <t xml:space="preserve">used power conversion system and motor drives, electrolysis, SOEC</t>
         </is>
       </c>
       <c r="I1176" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion and auxiliary drives, SOEC, reference</t>
+          <t xml:space="preserve">used power conversion system and motor drives, electrolysis, SOEC</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">treatment of used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
       <c r="B1177">
@@ -33298,19 +33326,19 @@
       </c>
       <c r="G1177" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
       <c r="I1177" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer power conversion, 1MW, engineering reference</t>
+          <t xml:space="preserve">used power conversion system, electrolysis, 1 MW</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">treatment of used motor drive assembly, electrolysis, SOEC</t>
         </is>
       </c>
       <c r="B1178">
@@ -33333,12 +33361,12 @@
       </c>
       <c r="G1178" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, SOEC</t>
         </is>
       </c>
       <c r="I1178" t="inlineStr">
         <is>
-          <t>treatment of electrolyzer auxiliary drive lifetime kit, SOEC, reference</t>
+          <t xml:space="preserve">used motor drive assembly, electrolysis, SOEC</t>
         </is>
       </c>
     </row>
@@ -33350,7 +33378,7 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>PTFE gasket, polymerization and forming engineering reference</t>
+          <t xml:space="preserve">PTFE gasket production, polymerization and forming</t>
         </is>
       </c>
     </row>
@@ -33384,7 +33412,7 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>PTFE gasket, polymerization and forming engineering reference</t>
+          <t xml:space="preserve">PTFE gasket, polymerization and forming</t>
         </is>
       </c>
     </row>
@@ -33420,7 +33448,8 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>APPROVED FINISHED AEC PTFE GASKETS, issue100, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 andPtM DOI10.1021/acssuschemeng.1c02002 SI pS12 identify144.2kgTFEinputasgasket. FinishedPTFEproperties/polymerization:Hintzer et al.2014 Ullmann Fluoropolymers DOI10.1002/14356007.a11_393.pub2;ecoinvent3.12hasPTFEemulsionpolymerizationbut3.8-3.11lackafinishedprovider. Engineeringallowancesbelowuse3.12polymerizationenergy7.5MJ+0.5kWh/kgplus3MJ+0.2kWhforming,notacopyofwholebackgroundinventory. Replace144.2kgvolatileTFEmonomerby144.2kgfinishedPTFEgasketreference,maintainingallversionbehaviorwithoneworkbookprovider. nC2F4-&gt;(C2F4)n;100%chemicalconversionthen95%finishedsolidretention(includingforming/machiningreject). Perkgfinished1/0.95=1.0526315789473684kgTFE,solidPTFEreject=0.05263157894736836kg. Thisyieldisassumed,90-100%sensitivity;notmeasuredindustrialpolymerizationyield. Aggregatemanufacture10.5MJheat+0.7kWh/kgfinishedincludespolymerizationandformingonce(5-20MJ,.35-1.4kWhsensitivity). ExistingTFEsupplyupstreamburdensretainedonce. Initiator,emulsionwater/surfactant,polymerdrying,highpressureequipment,purification,PFAS/TFEfugitiveemissionsandactualgasketshapesareunresolved;solid-rejectreferenceisnotclaimofzeroindustrialairloss. No nativePTFEpurchaseontopofmonomer,nomassivegasgasketinterpretation. FinishedAECgasketEOL144.2kgoldplasticroutepreserved;fluoropolymer-specificHFabatementnotvalidatedbygenericroute. Stacklifetimesandmetalinputsunchanged.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: PTFE gasket, polymerization and forming engineering reference. Former reference product: PTFE gasket, polymerization and forming engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FINISHED AEC PTFE GASKETS, issue100, 2026-10-18. Gerloff2021 DOI10.1016/j.est.2021.102759 andPtM DOI10.1021/acssuschemeng.1c02002 SI pS12 identify144.2kgTFEinputasgasket. FinishedPTFEproperties/polymerization:Hintzer et al.2014 Ullmann Fluoropolymers DOI10.1002/14356007.a11_393.pub2;ecoinvent3.12hasPTFEemulsionpolymerizationbut3.8-3.11lackafinishedprovider. Engineeringallowancesbelowuse3.12polymerizationenergy7.5MJ+0.5kWh/kgplus3MJ+0.2kWhforming,notacopyofwholebackgroundinventory. Replace144.2kgvolatileTFEmonomerby144.2kgfinishedPTFEgasketreference,maintainingallversionbehaviorwithoneworkbookprovider. nC2F4-&gt;(C2F4)n;100%chemicalconversionthen95%finishedsolidretention(includingforming/machiningreject). Perkgfinished1/0.95=1.0526315789473684kgTFE,solidPTFEreject=0.05263157894736836kg. Thisyieldisassumed,90-100%sensitivity;notmeasuredindustrialpolymerizationyield. Aggregatemanufacture10.5MJheat+0.7kWh/kgfinishedincludespolymerizationandformingonce(5-20MJ,.35-1.4kWhsensitivity). ExistingTFEsupplyupstreamburdensretainedonce. Initiator,emulsionwater/surfactant,polymerdrying,highpressureequipment,purification,PFAS/TFEfugitiveemissionsandactualgasketshapesareunresolved;solid-rejectreferenceisnotclaimofzeroindustrialairloss. No nativePTFEpurchaseontopofmonomer,nomassivegasgasketinterpretation. FinishedAECgasketEOL144.2kgoldplasticroutepreserved;fluoropolymer-specificHFabatementnotvalidatedbygenericroute. Stacklifetimesandmetalinputsunchanged.</t>
         </is>
       </c>
     </row>
@@ -33481,7 +33510,7 @@
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>PTFE gasket, polymerization and forming engineering reference</t>
+          <t xml:space="preserve">PTFE gasket production, polymerization and forming</t>
         </is>
       </c>
       <c r="B1190">
@@ -33504,12 +33533,12 @@
       </c>
       <c r="G1190" t="inlineStr">
         <is>
-          <t>PTFE gasket, polymerization and forming engineering reference</t>
+          <t xml:space="preserve">PTFE gasket, polymerization and forming</t>
         </is>
       </c>
       <c r="I1190" t="inlineStr">
         <is>
-          <t>PTFE gasket, polymerization and forming engineering reference</t>
+          <t xml:space="preserve">PTFE gasket, polymerization and forming</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -28902,7 +28902,7 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module production, electrolysis motor drive, 1200 V, 300 A</t>
+          <t>IGBT half-bridge module production, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
     </row>
@@ -28936,7 +28936,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
+          <t>IGBT half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
     </row>
@@ -28972,7 +28972,9 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference. Former reference product: Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>SILICON IGBT MODULE IDENTITY CORRECTION, 2026-10-19. The selected FF300R12KT4 reference is an Infineon TRENCHSTOP IGBT4 silicon half-bridge with emitter-controlled antiparallel diodes, not a SiC MOSFET module. Manufacturer: https://www.infineon.com/part/FF300R12KT4 ; datasheet https://www.infineon.com/assets/row/public/documents/non-assigned/49/infineon-ff300r12kt4-datasheet-en.pdf . Correct the activity, reference product, production exchange and all purchases in this workbook to IGBT half-bridge module. Preserve the same selected part, 1200 V/300 A ratings, 340 g declared piece, every material and process quantity, purchase count, lifetime and end-of-life allocation. This repairs a misleading label introduced by the earlier nomenclature revision; it does not change the physical design or turn the silicon feed into a fabricated die. The separate die-fabrication, geometry, unknown-composition and industrial-duty limitations remain open. Real SiC TO-247 switches and the separate SiC module reference are unchanged. No native, runtime or YAML edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference. Former reference product: Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
         </is>
       </c>
@@ -29034,7 +29036,7 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module production, electrolysis motor drive, 1200 V, 300 A</t>
+          <t>IGBT half-bridge module production, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
       <c r="B970">
@@ -29057,12 +29059,12 @@
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
+          <t>IGBT half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
       <c r="I970" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
+          <t>IGBT half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
     </row>
@@ -29731,7 +29733,7 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module production, electrolysis motor drive, 1200 V, 300 A</t>
+          <t>IGBT half-bridge module production, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
       <c r="B997">
@@ -29754,12 +29756,12 @@
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
+          <t>IGBT half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
       <c r="I997" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
+          <t>IGBT half-bridge module, electrolysis motor drive, 1200 V, 300 A</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -28972,7 +28972,9 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>SILICON IGBT MODULE IDENTITY CORRECTION, 2026-10-19. The selected FF300R12KT4 reference is an Infineon TRENCHSTOP IGBT4 silicon half-bridge with emitter-controlled antiparallel diodes, not a SiC MOSFET module. Manufacturer: https://www.infineon.com/part/FF300R12KT4 ; datasheet https://www.infineon.com/assets/row/public/documents/non-assigned/49/infineon-ff300r12kt4-datasheet-en.pdf . Correct the activity, reference product, production exchange and all purchases in this workbook to IGBT half-bridge module. Preserve the same selected part, 1200 V/300 A ratings, 340 g declared piece, every material and process quantity, purchase count, lifetime and end-of-life allocation. This repairs a misleading label introduced by the earlier nomenclature revision; it does not change the physical design or turn the silicon feed into a fabricated die. The separate die-fabrication, geometry, unknown-composition and industrial-duty limitations remain open. Real SiC TO-247 switches and the separate SiC module reference are unchanged. No native, runtime or YAML edits.
+          <t>SILICON IGBT DIE FABRICATION BOUNDARY, 2026-10-19. The selected FF300R12KT4 silicon IGBT module previously bought 1 g raw electronic-grade silicon without wafer fabrication. Replace only that die feed with the native GLO market for wafer, fabricated, for integrated circuit at 0.001/(2330*270e-6) = 0.00158957240502 square meter per module. This purchases FEOL/BEOL chemistry, process gases, lithography, doping, cleanroom utilities, upstream raw wafer and native fabrication yields once. No second complete module or packaged IC is purchased. Preserve every other module input, the 340 g unit, all consumer quantities, bulk ownership, lifetimes and EOL. The 1 g die mass is the EXISTING geometry assumption, not a newly recovered manufacturer BOM; 270 micrometres matches the native electronic wafer thickness, not a claim about this thinned IGBT4 die. A historical generic silicon IC fab is a process proxy for a power IGBT, not an exact qualified IGBT recipe. Illustrative 100/270/400 um thickness sensitivity is reported; it is not a measured distribution. The published PELCA IGBT model (https://doi.org/10.3390/su18052663) confirms why raw-wafer, device-processing and cleanroom boundaries are needed; its different 750 V ultrathin design is not silently copied as this 1200 V IGBT4. Manufacturer identity: https://www.infineon.com/part/FF300R12KT4 . Unknown module composition, actual die dimensions and power-device fabrication remain design sensitivities; this corrects an omitted manufacturing boundary without inventing new metal fractions. Actual SiC devices remain separate. Existing supplemental workbook only; no runtime, native, mapping or primary/secondary-share changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+SILICON IGBT MODULE IDENTITY CORRECTION, 2026-10-19. The selected FF300R12KT4 reference is an Infineon TRENCHSTOP IGBT4 silicon half-bridge with emitter-controlled antiparallel diodes, not a SiC MOSFET module. Manufacturer: https://www.infineon.com/part/FF300R12KT4 ; datasheet https://www.infineon.com/assets/row/public/documents/non-assigned/49/infineon-ff300r12kt4-datasheet-en.pdf . Correct the activity, reference product, production exchange and all purchases in this workbook to IGBT half-bridge module. Preserve the same selected part, 1200 V/300 A ratings, 340 g declared piece, every material and process quantity, purchase count, lifetime and end-of-life allocation. This repairs a misleading label introduced by the earlier nomenclature revision; it does not change the physical design or turn the silicon feed into a fabricated die. The separate die-fabrication, geometry, unknown-composition and industrial-duty limitations remain open. Real SiC TO-247 switches and the separate SiC module reference are unchanged. No native, runtime or YAML edits.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Nomenclature revision, 2026-10-19. Former activity name: Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference. Former reference product: Electrolyzer auxiliary drive 1200V300A half-bridge, module geometry reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
@@ -29211,11 +29213,11 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>market for silicon, electronics grade</t>
+          <t>market for wafer, fabricated, for integrated circuit</t>
         </is>
       </c>
       <c r="B975">
-        <v>0.001</v>
+        <v>0.0015895724050230488</v>
       </c>
       <c r="C975" t="inlineStr">
         <is>
@@ -29224,7 +29226,7 @@
       </c>
       <c r="D975" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>square meter</t>
         </is>
       </c>
       <c r="F975" t="inlineStr">
@@ -29234,12 +29236,17 @@
       </c>
       <c r="G975" t="inlineStr">
         <is>
-          <t>silicon, electronics grade</t>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>SILICON IGBT DIE FABRICATION BOUNDARY, 2026-10-19. The selected FF300R12KT4 silicon IGBT module previously bought 1 g raw electronic-grade silicon without wafer fabrication. Replace only that die feed with the native GLO market for wafer, fabricated, for integrated circuit at 0.001/(2330*270e-6) = 0.00158957240502 square meter per module. This purchases FEOL/BEOL chemistry, process gases, lithography, doping, cleanroom utilities, upstream raw wafer and native fabrication yields once. No second complete module or packaged IC is purchased. Preserve every other module input, the 340 g unit, all consumer quantities, bulk ownership, lifetimes and EOL. The 1 g die mass is the EXISTING geometry assumption, not a newly recovered manufacturer BOM; 270 micrometres matches the native electronic wafer thickness, not a claim about this thinned IGBT4 die. A historical generic silicon IC fab is a process proxy for a power IGBT, not an exact qualified IGBT recipe. Illustrative 100/270/400 um thickness sensitivity is reported; it is not a measured distribution. The published PELCA IGBT model (https://doi.org/10.3390/su18052663) confirms why raw-wafer, device-processing and cleanroom boundaries are needed; its different 750 V ultrathin design is not silently copied as this 1200 V IGBT4. Manufacturer identity: https://www.infineon.com/part/FF300R12KT4 . Unknown module composition, actual die dimensions and power-device fabrication remain design sensitivities; this corrects an omitted manufacturing boundary without inventing new metal fractions. Actual SiC devices remain separate. Existing supplemental workbook only; no runtime, native, mapping or primary/secondary-share changes.</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
         <is>
-          <t>silicon, electronics grade</t>
+          <t>wafer, fabricated, for integrated circuit</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1194"/>
+  <dimension ref="A1:U1209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -22930,7 +22930,9 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: SiC half-bridge module, declared material engineering reference. Former reference product: SiC half-bridge module, declared material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: SiC half-bridge module, declared material engineering reference. Former reference product: SiC half-bridge module, declared material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
         </is>
       </c>
@@ -23097,7 +23099,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>market for silicon carbide</t>
+          <t>silicon carbide wafer production, physical vapour transport</t>
         </is>
       </c>
       <c r="B722">
@@ -23120,12 +23122,17 @@
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>silicon carbide</t>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>silicon carbide</t>
+          <t>silicon carbide wafer</t>
         </is>
       </c>
     </row>
@@ -27718,7 +27725,9 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference. Former reference product: Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference. Former reference product: Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
         </is>
       </c>
@@ -27815,7 +27824,7 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>market for silicon carbide</t>
+          <t>silicon carbide wafer production, physical vapour transport</t>
         </is>
       </c>
       <c r="B921">
@@ -27838,12 +27847,17 @@
       </c>
       <c r="G921" t="inlineStr">
         <is>
-          <t>silicon carbide</t>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
         </is>
       </c>
       <c r="I921" t="inlineStr">
         <is>
-          <t>silicon carbide</t>
+          <t>silicon carbide wafer</t>
         </is>
       </c>
     </row>
@@ -28345,7 +28359,9 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference. Former reference product: Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Nomenclature revision, 2026-10-19. Former activity name: Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference. Former reference product: Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
         </is>
       </c>
@@ -28442,7 +28458,7 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>market for silicon carbide</t>
+          <t>silicon carbide wafer production, physical vapour transport</t>
         </is>
       </c>
       <c r="B946">
@@ -28465,12 +28481,17 @@
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>silicon carbide</t>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
         </is>
       </c>
       <c r="I946" t="inlineStr">
         <is>
-          <t>silicon carbide</t>
+          <t>silicon carbide wafer</t>
         </is>
       </c>
     </row>
@@ -33688,6 +33709,272 @@
       <c r="I1194" t="inlineStr">
         <is>
           <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer production, physical vapour transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Arvidsson and Molander 2017, DOI10.1111/jiec.12526; Warren et al.2015, DOI10.1021/acs.est.5b01627. Published PVT substrate reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer production, physical vapour transport</t>
+        </is>
+      </c>
+      <c r="B1206">
+        <v>1</v>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>market for silicon carbide</t>
+        </is>
+      </c>
+      <c r="B1207">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>silicon carbide</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>Net feed includes crystal, slicing and polishing losses once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1208">
+        <v>35603.02625723187</v>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>4 kWh/cm2 at 350 um and 3210 kg/m3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B1209">
+        <v>-1.8571428571428572</v>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>Generic discarded-crystal/kerf fate; no recycling credit.</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1209"/>
+  <dimension ref="A1:U1291"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -22855,669 +22855,698 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t/>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module production</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>location</t>
+          <t/>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B712">
-        <v>1</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t/>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>source</t>
+          <t/>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016).</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t/>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.
-PREVIOUS NOTES (retained as history; the correction above takes precedence):
-Nomenclature revision, 2026-10-19. Former activity name: SiC half-bridge module, declared material engineering reference. Former reference product: SiC half-bridge module, declared material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
-APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>name</t>
+          <t/>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t/>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>location</t>
+          <t/>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t/>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>type</t>
+          <t/>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t/>
         </is>
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t/>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>product</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module production</t>
-        </is>
-      </c>
-      <c r="B719">
-        <v>1</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>production</t>
+          <t/>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module</t>
+          <t/>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide half-bridge module</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
-        </is>
-      </c>
-      <c r="B720">
-        <v>0.68</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t/>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>market for tin</t>
-        </is>
-      </c>
-      <c r="B721">
-        <v>0.016</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>tin</t>
+          <t/>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>tin</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>silicon carbide wafer production, physical vapour transport</t>
-        </is>
-      </c>
-      <c r="B722">
-        <v>0.001</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>silicon carbide wafer</t>
+          <t/>
         </is>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
+          <t/>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>silicon carbide wafer</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon nitride production, for power modules</t>
-        </is>
-      </c>
-      <c r="B723">
-        <v>0.009</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon nitride, for power modules</t>
+          <t/>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon nitride, for power modules</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>market for nickel, class 1</t>
-        </is>
-      </c>
-      <c r="B724">
-        <v>0.001</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>nickel, class 1</t>
+          <t/>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>nickel, class 1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>market for antimony</t>
-        </is>
-      </c>
-      <c r="B725">
-        <v>0.001</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>antimony</t>
+          <t/>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>antimony</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>market for silver</t>
-        </is>
-      </c>
-      <c r="B726">
-        <v>0.001</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t/>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>market for silicone product</t>
-        </is>
-      </c>
-      <c r="B727">
-        <v>0.084</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t/>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>silicone product</t>
+          <t/>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>silicone product</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>market for nylon 6</t>
-        </is>
-      </c>
-      <c r="B728">
-        <v>0.089</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t/>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>nylon 6</t>
+          <t/>
         </is>
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>nylon 6</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>market for glass fibre</t>
-        </is>
-      </c>
-      <c r="B729">
-        <v>0.046</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>glass fibre</t>
+          <t/>
         </is>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>glass fibre</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>market for organophosphorus-compound, unspecified</t>
-        </is>
-      </c>
-      <c r="B730">
-        <v>0.015</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>organophosphorus-compound, unspecified</t>
+          <t/>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>organophosphorus-compound, unspecified</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="B731">
-        <v>0.05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t/>
         </is>
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>market for carbon black</t>
-        </is>
-      </c>
-      <c r="B732">
-        <v>0.001</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>carbon black</t>
+          <t/>
         </is>
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>carbon black</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead oxide production, for power modules</t>
-        </is>
-      </c>
-      <c r="B733">
-        <v>1.8e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead oxide, for power modules</t>
+          <t/>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead oxide, for power modules</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -27650,1268 +27679,1322 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t/>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch production, electrolysis motor drive, 1200 V, TO-247</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>location</t>
+          <t/>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B913">
-        <v>1</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t/>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 1200 V, TO-247</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>source</t>
+          <t/>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t/>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.
-PREVIOUS NOTES (retained as history; the correction above takes precedence):
-Nomenclature revision, 2026-10-19. Former activity name: Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference. Former reference product: Electrolyzer auxiliary drive 1200V SiC switch, TO247 MCD material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
-APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>name</t>
+          <t/>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t/>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>location</t>
+          <t/>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t/>
         </is>
       </c>
       <c r="F919" t="inlineStr">
         <is>
-          <t>type</t>
+          <t/>
         </is>
       </c>
       <c r="G919" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t/>
         </is>
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t/>
         </is>
       </c>
       <c r="I919" t="inlineStr">
         <is>
-          <t>product</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch production, electrolysis motor drive, 1200 V, TO-247</t>
-        </is>
-      </c>
-      <c r="B920">
-        <v>1</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="F920" t="inlineStr">
         <is>
-          <t>production</t>
+          <t/>
         </is>
       </c>
       <c r="G920" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 1200 V, TO-247</t>
+          <t/>
         </is>
       </c>
       <c r="I920" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 1200 V, TO-247</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>silicon carbide wafer production, physical vapour transport</t>
-        </is>
-      </c>
-      <c r="B921">
-        <v>4.941e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F921" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G921" t="inlineStr">
         <is>
-          <t>silicon carbide wafer</t>
+          <t/>
         </is>
       </c>
       <c r="H921" t="inlineStr">
         <is>
-          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
+          <t/>
         </is>
       </c>
       <c r="I921" t="inlineStr">
         <is>
-          <t>silicon carbide wafer</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>market for phosphorus, white, liquid</t>
-        </is>
-      </c>
-      <c r="B922">
-        <v>1.192e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F922" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G922" t="inlineStr">
         <is>
-          <t>phosphorus, white, liquid</t>
+          <t/>
         </is>
       </c>
       <c r="I922" t="inlineStr">
         <is>
-          <t>phosphorus, white, liquid</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="B923">
-        <v>3.972e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F923" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G923" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t/>
         </is>
       </c>
       <c r="I923" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
-        </is>
-      </c>
-      <c r="B924">
-        <v>0.003967074</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F924" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G924" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t/>
         </is>
       </c>
       <c r="I924" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>market for aluminium, primary, ingot</t>
-        </is>
-      </c>
-      <c r="B925">
-        <v>4.257e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t/>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F925" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G925" t="inlineStr">
         <is>
-          <t>aluminium, primary, ingot</t>
+          <t/>
         </is>
       </c>
       <c r="I925" t="inlineStr">
         <is>
-          <t>aluminium, primary, ingot</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>market for carbon black</t>
-        </is>
-      </c>
-      <c r="B926">
-        <v>2.0032e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F926" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>carbon black</t>
+          <t/>
         </is>
       </c>
       <c r="I926" t="inlineStr">
         <is>
-          <t>carbon black</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>market for epoxy resin, liquid</t>
-        </is>
-      </c>
-      <c r="B927">
-        <v>0.000380613</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t/>
         </is>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t/>
         </is>
       </c>
       <c r="I927" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>market for silica sand</t>
-        </is>
-      </c>
-      <c r="B928">
-        <v>0.00160258</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F928" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>silica sand</t>
+          <t/>
         </is>
       </c>
       <c r="I928" t="inlineStr">
         <is>
-          <t>silica sand</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>market for tin</t>
-        </is>
-      </c>
-      <c r="B929">
-        <v>3.3233e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F929" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G929" t="inlineStr">
         <is>
-          <t>tin</t>
+          <t/>
         </is>
       </c>
       <c r="I929" t="inlineStr">
         <is>
-          <t>tin</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>market for nickel, class 1</t>
-        </is>
-      </c>
-      <c r="B930">
-        <v>2.9065e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F930" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>nickel, class 1</t>
+          <t/>
         </is>
       </c>
       <c r="I930" t="inlineStr">
         <is>
-          <t>nickel, class 1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>market for antimony</t>
-        </is>
-      </c>
-      <c r="B931">
-        <v>2.0899999999999998e-07</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F931" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G931" t="inlineStr">
         <is>
-          <t>antimony</t>
+          <t/>
         </is>
       </c>
       <c r="I931" t="inlineStr">
         <is>
-          <t>antimony</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>market for silver</t>
-        </is>
-      </c>
-      <c r="B932">
-        <v>5.23e-07</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F932" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t/>
         </is>
       </c>
       <c r="I932" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B933">
-        <v>0.006047690999999999</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t/>
         </is>
       </c>
       <c r="F933" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t/>
         </is>
       </c>
       <c r="I933" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t/>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch production, electrolysis motor drive, 650 V, TO-247</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>location</t>
+          <t/>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B938">
-        <v>1</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t/>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 650 V, TO-247</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>source</t>
+          <t/>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t/>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.
-PREVIOUS NOTES (retained as history; the correction above takes precedence):
-Nomenclature revision, 2026-10-19. Former activity name: Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference. Former reference product: Electrolyzer auxiliary drive 650V SiC switch, TO247 MCD material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
-APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory. Componentreference:InfineonIMW120R045M1 MCDMA00164188205April2021 andIMW65R048M1H MCDMA00540015111Dec2019,PG-TO247-3-41,6047.69/6047.25mg. Fullmgconstituentledgers={'1200V': {'SiC': 4.941, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 4.257, 'carbon': 20.032, 'epoxy': 380.613, 'silica': 1602.58, 'Sn': 33.233, 'Ni': 29.065, 'Sb': 0.209, 'Ag': 0.523}, '650V': {'SiC': 2.646, 'P': 1.192, 'steel': 3.972, 'Cu': 3967.074, 'Al': 5.601, 'carbon': 20.046, 'epoxy': 380.868, 'silica': 1603.657, 'Sn': 32.692, 'Ni': 29.065, 'Sb': 0.126, 'Ag': 0.314}}. Ledgerrounding0.001/0.003mgnotarbitrarilyrenormalized. Source https://www.infineon.com/assets/row/public/documents/60/71/infineon-ma001641882-materialcontentsheet-en.pdf and https://www.infineon.com/assets/row/public/documents/24/71/infineon-ma005400151-materialcontentsheet-en.pdf . These3pinpackagesarematerialanalogues,notpin-compatibleclaimforTI4pinWolfspeedBOM. SiCpowderfeedisnotqualifiedepitaxy/waferfabrication;processyield/energy/purity remain gaps.1kWh/kgpackageassemblyreferenceadded,notfullICTchipproxy. FF300R12KT4 datasheet340g,1200V300Ahalfbridge,Cu baseplate,Al2O3isolation; https://www.infineon.com/assets/row/public/documents/60/49/infineon-ff300r12kt4-ds-en.pdf . ManufacturerfullMCDnotrecovered. ModulematerialinventoryisGEOMETRYENGINEERINGESTIMATE,notmanufacturerdeclaration. Assumedgrossbaseplate106.4x61.4x2.5mm,DBC35cm2with0.6mmCuand0.63mmAl2O3,25gCu terminals,45cm3PAhousing,25cm3siliconegel,1gSi,0.5gAlwire,4gSACsolder,10gsteel;geometry={'baseplate_length_m': 0.1064, 'baseplate_width_m': 0.0614, 'baseplate_thickness_m': 0.0025, 'DBC_area_m2': 0.0035, 'DBC_Cu_total_thickness_m': 0.0006, 'ceramic_thickness_m': 0.00063, 'Cu_density_kg_m3': 8960, 'alumina_density_kg_m3': 3900};knownmodulekg={'Cu': 0.190154304, 'alumina': 0.0085995, 'PA': 0.051300000000000005, 'silicone': 0.02425, 'Si': 0.001, 'Al': 0.0005, 'solder': 0.004, 'steel': 0.01};unresolvedmodulemass=0.050196196000000026kg. Exteriorfootprintusedasbaseplatearea isproxy;holes/recessesandrealplate thicknessunknown.Sensitivitybaseplate2-3mm,terminalCu15-35g,unresolvedcompositionnotzeroAu/Ni/Ag. FeedgradeSi/Al2O3/siliconesareproxies;diearea/doping/waferyieldunverified. Noextracompletemoduleinventoryon topofingredients.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>name</t>
+          <t/>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t/>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>location</t>
+          <t/>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t/>
         </is>
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t>type</t>
+          <t/>
         </is>
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t/>
         </is>
       </c>
       <c r="H944" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t/>
         </is>
       </c>
       <c r="I944" t="inlineStr">
         <is>
-          <t>product</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch production, electrolysis motor drive, 650 V, TO-247</t>
-        </is>
-      </c>
-      <c r="B945">
-        <v>1</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t/>
         </is>
       </c>
       <c r="F945" t="inlineStr">
         <is>
-          <t>production</t>
+          <t/>
         </is>
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 650 V, TO-247</t>
+          <t/>
         </is>
       </c>
       <c r="I945" t="inlineStr">
         <is>
-          <t xml:space="preserve">silicon carbide switch, electrolysis motor drive, 650 V, TO-247</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>silicon carbide wafer production, physical vapour transport</t>
-        </is>
-      </c>
-      <c r="B946">
-        <v>2.6459999999999997e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F946" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>silicon carbide wafer</t>
+          <t/>
         </is>
       </c>
       <c r="H946" t="inlineStr">
         <is>
-          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
+          <t/>
         </is>
       </c>
       <c r="I946" t="inlineStr">
         <is>
-          <t>silicon carbide wafer</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>market for phosphorus, white, liquid</t>
-        </is>
-      </c>
-      <c r="B947">
-        <v>1.192e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F947" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G947" t="inlineStr">
         <is>
-          <t>phosphorus, white, liquid</t>
+          <t/>
         </is>
       </c>
       <c r="I947" t="inlineStr">
         <is>
-          <t>phosphorus, white, liquid</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="B948">
-        <v>3.972e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F948" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G948" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t/>
         </is>
       </c>
       <c r="I948" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
-        </is>
-      </c>
-      <c r="B949">
-        <v>0.003967074</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t/>
         </is>
       </c>
       <c r="I949" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>market for aluminium, primary, ingot</t>
-        </is>
-      </c>
-      <c r="B950">
-        <v>5.601e-06</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t/>
         </is>
       </c>
       <c r="D950" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F950" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G950" t="inlineStr">
         <is>
-          <t>aluminium, primary, ingot</t>
+          <t/>
         </is>
       </c>
       <c r="I950" t="inlineStr">
         <is>
-          <t>aluminium, primary, ingot</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>market for carbon black</t>
-        </is>
-      </c>
-      <c r="B951">
-        <v>2.0046e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D951" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G951" t="inlineStr">
         <is>
-          <t>carbon black</t>
+          <t/>
         </is>
       </c>
       <c r="I951" t="inlineStr">
         <is>
-          <t>carbon black</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>market for epoxy resin, liquid</t>
-        </is>
-      </c>
-      <c r="B952">
-        <v>0.00038086799999999997</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t/>
         </is>
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G952" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t/>
         </is>
       </c>
       <c r="I952" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>market for silica sand</t>
-        </is>
-      </c>
-      <c r="B953">
-        <v>0.0016036569999999999</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G953" t="inlineStr">
         <is>
-          <t>silica sand</t>
+          <t/>
         </is>
       </c>
       <c r="I953" t="inlineStr">
         <is>
-          <t>silica sand</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>market for tin</t>
-        </is>
-      </c>
-      <c r="B954">
-        <v>3.2692e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D954" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G954" t="inlineStr">
         <is>
-          <t>tin</t>
+          <t/>
         </is>
       </c>
       <c r="I954" t="inlineStr">
         <is>
-          <t>tin</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>market for nickel, class 1</t>
-        </is>
-      </c>
-      <c r="B955">
-        <v>2.9065e-05</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D955" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F955" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G955" t="inlineStr">
         <is>
-          <t>nickel, class 1</t>
+          <t/>
         </is>
       </c>
       <c r="I955" t="inlineStr">
         <is>
-          <t>nickel, class 1</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>market for antimony</t>
-        </is>
-      </c>
-      <c r="B956">
-        <v>1.26e-07</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D956" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F956" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G956" t="inlineStr">
         <is>
-          <t>antimony</t>
+          <t/>
         </is>
       </c>
       <c r="I956" t="inlineStr">
         <is>
-          <t>antimony</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>market for silver</t>
-        </is>
-      </c>
-      <c r="B957">
-        <v>3.14e-07</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D957" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t/>
         </is>
       </c>
       <c r="F957" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t/>
         </is>
       </c>
       <c r="I957" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B958">
-        <v>0.006047253</v>
+          <t/>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t/>
         </is>
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t/>
         </is>
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t/>
         </is>
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t/>
         </is>
       </c>
       <c r="I958" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -33790,7 +33873,9 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
+          <t>CONSISTENT SiC WAFER/FABRICATION BASIS, 2026-10-20. This supersedes the earlier4kWh/cm2-physical-wafer and35%yield interpretation. Warren2015 https://doi.org/10.1021/acs.est.5b01627 primary manuscript section4.1 https://www.osti.gov/servlets/purl/1855705 defines4.04kWh/cm2 of FUNCTIONAL DIE, including perimeter/nonfunctional die losses. Its100mm reference has81.07cm2/wafer,1314gooddies*3.42mm2=44.9388cm2goodarea; thus2.239456667kWh/cm2physical usable wafer. Its6.6cm boule yields47good350um wafers after kerf/polishing and bad wafers; retained wafer/boule mass=47*.035/6.6=0.2492424242. This is a published reference design, not current measured factory yield. Net consumed Acheson SiC powder is represented as the boule mass,100%net conversion; actual PVT-grade purification/charge losses remain unrepresented. Unused circulating charge is not repeatedly purchased. The wafer provider output remains1kg PHYSICAL350um wafer, not1kg of good chips. Supply its net discarded crystal/kerf once to the existing mineral waste proxy. No argon amount or direct-growth emissions is established. Spejo2023 https://doi.org/10.1016/j.pedc.2023.100050 Table1/section3 models150mm SiC MOSFET processing with520potential25mm2dies and442gooddies (85%electrical yield). These are future-maturity estimates and a3.3kV source analogue, not measured650/1200/2300V part production. Selected scenario3 front-end electricity4.99kWh/cm2GOODDIE already includes wafer utilization/yield; do NOT divide it again by0.85. Test its four published scenarios 2.50,3.01,4.99,6.02kWh/cm2. Source good-area fraction=442*.25/(pi*7.5^2)=0.62530; physical wafer input/good-die area=1/that fraction. Finished SiC mass is held fixed. Infer delivered die area from3210kg/m3 and350um unthinned-die reference, not a measured thickness; test175/100um. Thinning and cutting reject mass=physical wafer input minus retained SiC, treated once separately from upstream crystal/kerf. Failed dies are assumed bare SiC in this nominal ledger; discarded metallization and process chemicals remain unquantified. The electrical good-die yield is separate from geometry and wafer-growth losses. Linear wafer-area transfer from Warren substrate to Spejo geometry is explicit: total substrate electricity is recalculated on physical wafer area, not copied from already-yield-adjusted4.04 a second time. Add front-end electricity to any EXISTING package-assembly allowance; do not add substrate electricity again in device helpers or charge a second packaged transistor. Global electricity remains a geography proxy. No operating electricity, device counts, retained package metals/masses, voltage identities, final equipment EOL or lifetime coefficients change. This closes known electricity and nominal reject boundaries only: SiC epitaxy/etch/deposition/doping chemicals, process gas utilization/abatement, direct emissions, actual chip geometry, module packaging and industrial qualification remain open. An energy range is not evidence for toxicity completeness. No fabricated gas capture or extra silicon/DRAM chemical recipe. All parameters are static references, not a newly inferred time-learning curve. Only existing supplemental workbooks change; no runtime/YAML/native edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
         </is>
       </c>
     </row>
@@ -33880,7 +33965,7 @@
         </is>
       </c>
       <c r="B1207">
-        <v>2.857142857142857</v>
+        <v>4.012158054711246</v>
       </c>
       <c r="C1207" t="inlineStr">
         <is>
@@ -33915,7 +34000,7 @@
         </is>
       </c>
       <c r="B1208">
-        <v>35603.02625723187</v>
+        <v>19932.858629976276</v>
       </c>
       <c r="C1208" t="inlineStr">
         <is>
@@ -33950,7 +34035,7 @@
         </is>
       </c>
       <c r="B1209">
-        <v>-1.8571428571428572</v>
+        <v>-3.0121580547112456</v>
       </c>
       <c r="C1209" t="inlineStr">
         <is>
@@ -33975,6 +34060,2074 @@
       <c r="H1209" t="inlineStr">
         <is>
           <t>Generic discarded-crystal/kerf fate; no recycling credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>silicon carbide half-bridge module production</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>silicon carbide half-bridge module</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>CONSISTENT SiC WAFER/FABRICATION BASIS, 2026-10-20. This supersedes the earlier4kWh/cm2-physical-wafer and35%yield interpretation. Warren2015 https://doi.org/10.1021/acs.est.5b01627 primary manuscript section4.1 https://www.osti.gov/servlets/purl/1855705 defines4.04kWh/cm2 of FUNCTIONAL DIE, including perimeter/nonfunctional die losses. Its100mm reference has81.07cm2/wafer,1314gooddies*3.42mm2=44.9388cm2goodarea; thus2.239456667kWh/cm2physical usable wafer. Its6.6cm boule yields47good350um wafers after kerf/polishing and bad wafers; retained wafer/boule mass=47*.035/6.6=0.2492424242. This is a published reference design, not current measured factory yield. Net consumed Acheson SiC powder is represented as the boule mass,100%net conversion; actual PVT-grade purification/charge losses remain unrepresented. Unused circulating charge is not repeatedly purchased. The wafer provider output remains1kg PHYSICAL350um wafer, not1kg of good chips. Supply its net discarded crystal/kerf once to the existing mineral waste proxy. No argon amount or direct-growth emissions is established. Spejo2023 https://doi.org/10.1016/j.pedc.2023.100050 Table1/section3 models150mm SiC MOSFET processing with520potential25mm2dies and442gooddies (85%electrical yield). These are future-maturity estimates and a3.3kV source analogue, not measured650/1200/2300V part production. Selected scenario3 front-end electricity4.99kWh/cm2GOODDIE already includes wafer utilization/yield; do NOT divide it again by0.85. Test its four published scenarios 2.50,3.01,4.99,6.02kWh/cm2. Source good-area fraction=442*.25/(pi*7.5^2)=0.62530; physical wafer input/good-die area=1/that fraction. Finished SiC mass is held fixed. Infer delivered die area from3210kg/m3 and350um unthinned-die reference, not a measured thickness; test175/100um. Thinning and cutting reject mass=physical wafer input minus retained SiC, treated once separately from upstream crystal/kerf. Failed dies are assumed bare SiC in this nominal ledger; discarded metallization and process chemicals remain unquantified. The electrical good-die yield is separate from geometry and wafer-growth losses. Linear wafer-area transfer from Warren substrate to Spejo geometry is explicit: total substrate electricity is recalculated on physical wafer area, not copied from already-yield-adjusted4.04 a second time. Add front-end electricity to any EXISTING package-assembly allowance; do not add substrate electricity again in device helpers or charge a second packaged transistor. Global electricity remains a geography proxy. No operating electricity, device counts, retained package metals/masses, voltage identities, final equipment EOL or lifetime coefficients change. This closes known electricity and nominal reject boundaries only: SiC epitaxy/etch/deposition/doping chemicals, process gas utilization/abatement, direct emissions, actual chip geometry, module packaging and industrial qualification remain open. An energy range is not evidence for toxicity completeness. No fabricated gas capture or extra silicon/DRAM chemical recipe. All parameters are static references, not a newly inferred time-learning curve. Only existing supplemental workbooks change; no runtime/YAML/native edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>silicon carbide half-bridge module production</t>
+        </is>
+      </c>
+      <c r="B1221">
+        <v>1</v>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>silicon carbide half-bridge module</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>silicon carbide half-bridge module</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1222">
+        <v>0.68</v>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1223">
+        <v>0.016</v>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer production, physical vapour transport</t>
+        </is>
+      </c>
+      <c r="B1224">
+        <v>0.0015992270295423158</v>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>silicon nitride production, for power modules</t>
+        </is>
+      </c>
+      <c r="B1225">
+        <v>0.009</v>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>silicon nitride, for power modules</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>silicon nitride, for power modules</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1226">
+        <v>0.001</v>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>market for antimony</t>
+        </is>
+      </c>
+      <c r="B1227">
+        <v>0.001</v>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1228">
+        <v>0.001</v>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>market for silicone product</t>
+        </is>
+      </c>
+      <c r="B1229">
+        <v>0.084</v>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>market for nylon 6</t>
+        </is>
+      </c>
+      <c r="B1230">
+        <v>0.089</v>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>market for glass fibre</t>
+        </is>
+      </c>
+      <c r="B1231">
+        <v>0.046</v>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>market for organophosphorus-compound, unspecified</t>
+        </is>
+      </c>
+      <c r="B1232">
+        <v>0.015</v>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>organophosphorus-compound, unspecified</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>organophosphorus-compound, unspecified</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1233">
+        <v>0.05</v>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1234">
+        <v>0.001</v>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>lead oxide production, for power modules</t>
+        </is>
+      </c>
+      <c r="B1235">
+        <v>1.8e-05</v>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>lead oxide, for power modules</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>lead oxide, for power modules</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1236">
+        <v>44.41477525589676</v>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B1237">
+        <v>-0.0005992270295423158</v>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>silicon carbide switch production, electrolysis motor drive, 1200 V, TO-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>silicon carbide switch, electrolysis motor drive, 1200 V, TO-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>CONSISTENT SiC WAFER/FABRICATION BASIS, 2026-10-20. This supersedes the earlier4kWh/cm2-physical-wafer and35%yield interpretation. Warren2015 https://doi.org/10.1021/acs.est.5b01627 primary manuscript section4.1 https://www.osti.gov/servlets/purl/1855705 defines4.04kWh/cm2 of FUNCTIONAL DIE, including perimeter/nonfunctional die losses. Its100mm reference has81.07cm2/wafer,1314gooddies*3.42mm2=44.9388cm2goodarea; thus2.239456667kWh/cm2physical usable wafer. Its6.6cm boule yields47good350um wafers after kerf/polishing and bad wafers; retained wafer/boule mass=47*.035/6.6=0.2492424242. This is a published reference design, not current measured factory yield. Net consumed Acheson SiC powder is represented as the boule mass,100%net conversion; actual PVT-grade purification/charge losses remain unrepresented. Unused circulating charge is not repeatedly purchased. The wafer provider output remains1kg PHYSICAL350um wafer, not1kg of good chips. Supply its net discarded crystal/kerf once to the existing mineral waste proxy. No argon amount or direct-growth emissions is established. Spejo2023 https://doi.org/10.1016/j.pedc.2023.100050 Table1/section3 models150mm SiC MOSFET processing with520potential25mm2dies and442gooddies (85%electrical yield). These are future-maturity estimates and a3.3kV source analogue, not measured650/1200/2300V part production. Selected scenario3 front-end electricity4.99kWh/cm2GOODDIE already includes wafer utilization/yield; do NOT divide it again by0.85. Test its four published scenarios 2.50,3.01,4.99,6.02kWh/cm2. Source good-area fraction=442*.25/(pi*7.5^2)=0.62530; physical wafer input/good-die area=1/that fraction. Finished SiC mass is held fixed. Infer delivered die area from3210kg/m3 and350um unthinned-die reference, not a measured thickness; test175/100um. Thinning and cutting reject mass=physical wafer input minus retained SiC, treated once separately from upstream crystal/kerf. Failed dies are assumed bare SiC in this nominal ledger; discarded metallization and process chemicals remain unquantified. The electrical good-die yield is separate from geometry and wafer-growth losses. Linear wafer-area transfer from Warren substrate to Spejo geometry is explicit: total substrate electricity is recalculated on physical wafer area, not copied from already-yield-adjusted4.04 a second time. Add front-end electricity to any EXISTING package-assembly allowance; do not add substrate electricity again in device helpers or charge a second packaged transistor. Global electricity remains a geography proxy. No operating electricity, device counts, retained package metals/masses, voltage identities, final equipment EOL or lifetime coefficients change. This closes known electricity and nominal reject boundaries only: SiC epitaxy/etch/deposition/doping chemicals, process gas utilization/abatement, direct emissions, actual chip geometry, module packaging and industrial qualification remain open. An energy range is not evidence for toxicity completeness. No fabricated gas capture or extra silicon/DRAM chemical recipe. All parameters are static references, not a newly inferred time-learning curve. Only existing supplemental workbooks change; no runtime/YAML/native edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>silicon carbide switch production, electrolysis motor drive, 1200 V, TO-247</t>
+        </is>
+      </c>
+      <c r="B1250">
+        <v>1</v>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>silicon carbide switch, electrolysis motor drive, 1200 V, TO-247</t>
+        </is>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>silicon carbide switch, electrolysis motor drive, 1200 V, TO-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer production, physical vapour transport</t>
+        </is>
+      </c>
+      <c r="B1251">
+        <v>7.901780752968583e-06</v>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
+        </is>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1252">
+        <v>1.192e-06</v>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1253">
+        <v>3.972e-06</v>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1254">
+        <v>0.003967074</v>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B1255">
+        <v>4.257e-06</v>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1256">
+        <v>2.0032e-05</v>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1257">
+        <v>0.000380613</v>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1258">
+        <v>0.00160258</v>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1259">
+        <v>3.3233e-05</v>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1260">
+        <v>2.9065e-05</v>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>market for antimony</t>
+        </is>
+      </c>
+      <c r="B1261">
+        <v>2.0899999999999998e-07</v>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1262">
+        <v>5.23e-07</v>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1263">
+        <v>0.2255010955393859</v>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B1264">
+        <v>-2.960780752968583e-06</v>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>silicon carbide switch production, electrolysis motor drive, 650 V, TO-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>silicon carbide switch, electrolysis motor drive, 650 V, TO-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>CONSISTENT SiC WAFER/FABRICATION BASIS, 2026-10-20. This supersedes the earlier4kWh/cm2-physical-wafer and35%yield interpretation. Warren2015 https://doi.org/10.1021/acs.est.5b01627 primary manuscript section4.1 https://www.osti.gov/servlets/purl/1855705 defines4.04kWh/cm2 of FUNCTIONAL DIE, including perimeter/nonfunctional die losses. Its100mm reference has81.07cm2/wafer,1314gooddies*3.42mm2=44.9388cm2goodarea; thus2.239456667kWh/cm2physical usable wafer. Its6.6cm boule yields47good350um wafers after kerf/polishing and bad wafers; retained wafer/boule mass=47*.035/6.6=0.2492424242. This is a published reference design, not current measured factory yield. Net consumed Acheson SiC powder is represented as the boule mass,100%net conversion; actual PVT-grade purification/charge losses remain unrepresented. Unused circulating charge is not repeatedly purchased. The wafer provider output remains1kg PHYSICAL350um wafer, not1kg of good chips. Supply its net discarded crystal/kerf once to the existing mineral waste proxy. No argon amount or direct-growth emissions is established. Spejo2023 https://doi.org/10.1016/j.pedc.2023.100050 Table1/section3 models150mm SiC MOSFET processing with520potential25mm2dies and442gooddies (85%electrical yield). These are future-maturity estimates and a3.3kV source analogue, not measured650/1200/2300V part production. Selected scenario3 front-end electricity4.99kWh/cm2GOODDIE already includes wafer utilization/yield; do NOT divide it again by0.85. Test its four published scenarios 2.50,3.01,4.99,6.02kWh/cm2. Source good-area fraction=442*.25/(pi*7.5^2)=0.62530; physical wafer input/good-die area=1/that fraction. Finished SiC mass is held fixed. Infer delivered die area from3210kg/m3 and350um unthinned-die reference, not a measured thickness; test175/100um. Thinning and cutting reject mass=physical wafer input minus retained SiC, treated once separately from upstream crystal/kerf. Failed dies are assumed bare SiC in this nominal ledger; discarded metallization and process chemicals remain unquantified. The electrical good-die yield is separate from geometry and wafer-growth losses. Linear wafer-area transfer from Warren substrate to Spejo geometry is explicit: total substrate electricity is recalculated on physical wafer area, not copied from already-yield-adjusted4.04 a second time. Add front-end electricity to any EXISTING package-assembly allowance; do not add substrate electricity again in device helpers or charge a second packaged transistor. Global electricity remains a geography proxy. No operating electricity, device counts, retained package metals/masses, voltage identities, final equipment EOL or lifetime coefficients change. This closes known electricity and nominal reject boundaries only: SiC epitaxy/etch/deposition/doping chemicals, process gas utilization/abatement, direct emissions, actual chip geometry, module packaging and industrial qualification remain open. An energy range is not evidence for toxicity completeness. No fabricated gas capture or extra silicon/DRAM chemical recipe. All parameters are static references, not a newly inferred time-learning curve. Only existing supplemental workbooks change; no runtime/YAML/native edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>silicon carbide switch production, electrolysis motor drive, 650 V, TO-247</t>
+        </is>
+      </c>
+      <c r="B1277">
+        <v>1</v>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>silicon carbide switch, electrolysis motor drive, 650 V, TO-247</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>silicon carbide switch, electrolysis motor drive, 650 V, TO-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer production, physical vapour transport</t>
+        </is>
+      </c>
+      <c r="B1278">
+        <v>4.231554720168967e-06</v>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>SiC SUBSTRATE MANUFACTURE, 2026-10-19. Arvidsson and Molander (2017), DOI 10.1111/jiec.12526, section Silicon Carbide Wafer Production / Physical Vapor Transport, citing Warren et al. (2015), DOI 10.1021/acs.est.5b01627: PVT substrate electricity 4.0 kWh/cm2 for a 350 micrometre wafer, density 3210 kg/m3, net wafer-material yield 0.35 including poor crystal regions, slicing and polishing. Thus per kg finished wafer: electricity 35603.0262572 kWh and Acheson SiC powder 1/0.35 = 2.85714285714 kg. Source linearly scales growth electricity with thickness; this mass-normalized reference uses its 350 micrometre basis. Unused charge recirculates internally and is not purchased again; the net discarded 1/0.35-1 kg SiC goes once to generic inert-waste disposal, with no recovery credit. This waste fate is an explicit proxy for discarded crystal/kerf. The source omits measured argon and direct growth emissions; those are unresolved, not demonstrated zero. Global electricity is a geographic proxy. This restores SUBSTRATE production instead of buying industrial SiC powder as a finished semiconductor. It does NOT include device epitaxy, lithography, implantation, metallization, die yields or package assembly. Those remain separate open boundaries; do not interpret this as a complete SiC transistor LCI or a current vendor-specific process. Retain declared finished SiC die mass, package metals/resins, part counts, service life, operating losses and EOL. Do not purchase a complete packaged power device on top. Published reference is historical: test electricity 2/4/6 kWh/cm2 and wafer yield 0.35/0.50/0.70 as illustrative process sensitivities, not measured statistics. Source https://link.springer.com/article/10.1111/jiec.12526 (CC BY 4.0); full text https://publications.lib.chalmers.se/records/fulltext/253433/local_253433.pdf . Only existing supplemental workbooks change; no runtime, native, mapping or primary/secondary-share edits.</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>silicon carbide wafer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1279">
+        <v>1.192e-06</v>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1280">
+        <v>3.972e-06</v>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1281">
+        <v>0.003967074</v>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B1282">
+        <v>5.601e-06</v>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1283">
+        <v>2.0046e-05</v>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1284">
+        <v>0.00038086799999999997</v>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1285">
+        <v>0.0016036569999999999</v>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1286">
+        <v>3.2692e-05</v>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1287">
+        <v>2.9065e-05</v>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>market for antimony</t>
+        </is>
+      </c>
+      <c r="B1288">
+        <v>1.26e-07</v>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>antimony</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1289">
+        <v>3.14e-07</v>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1290">
+        <v>0.12356874832710282</v>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B1291">
+        <v>-1.5855547201689676e-06</v>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1291"/>
+  <dimension ref="A1:U1321"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -36128,6 +36128,677 @@
       <c r="I1291" t="inlineStr">
         <is>
           <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>neodymium production, molten salt electrolysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>neodymium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1298">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/adem.201901206 ; https://www.osti.gov/servlets/purl/1509117</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>NEODYMIUM OXIDE-TO-METAL MANUFACTURING REFERENCE, 2026-10-20. One kg nominal Nd metal at the factory gate, with integrated fluoride preparation and explicit mass/element ledgers. This is a reconstructed engineering reference, not measured factory data. Schreiber etal2020, Table1 and sections3.2.2-3.2.4, https://doi.org/10.1002/adem.201901206, supplies modern 8.5kWh/kgNd electrolysis,0.000576kgNdF3/0.000653kgLiF makeup, 14mgCF4/1.4mgC2F6,0.09kgrefractory,0.03kggraphitepot and estimated 2.7gWcathode/kgNd. Its best/middle1.13kgNd2O3 doses underfeed elemental Nd for their stated1kgmetal output; do NOT copy that imbalance. NETL2014 Rare Earth Oxide Electrolysis, https://www.osti.gov/servlets/purl/1509117, pp.4-7, describes a Lynas didymium pilot design and distinguishes assumed transfer to other REEs. This Nd-only reference does not adopt that blanket heavy-REE transfer. Select94%Nd collection as a rounded engineering reference consistent with the NETL~1.24kgNd2O3/kgNd dose, not measured industrial recovery; test90/94/98/100%. Uncollected Nd remains as oxide in solid waste. Magnet95%material retention is a separate downstream fabrication stage, not this refinery yield applied twice. Buy total oxide including precursor losses once. Preserve the source CO2:CO mass ratio0.055:0.211 but calculate absolute gas and reactive carbon quantities from oxygen liberated by the oxide actually reduced. Graphite includes reacted carbon plus0.03kgspentpot. PFC values are grams converted to kilograms. Their fluorine is explicitly supplied by NdF3 decomposition; the corresponding Nd enters metal, reducing oxide required for that fraction. LiF is not treated as a source of metallic Li. HigherPFC cases buy extra NdF3 to avoid inventing fluorine while retaining ordinary bath losses. Prepare NdF3 inline via Nd2O3+6HF-&gt;2NdF3+3H2O. Adopt95%oxide conversion as an explicit reference matching the approximately0.880kg oxide/0.044kgoxide-waste relation in the literature, but close the stoichiometry with unrounded molecular weights. The0.528kWh/kgNdF3 utility is the published direct-fluorination reference; this integrated recipe is not a wholesale copy of either inconsistent published fluorination ledger. No unexplained ammonia input/output. Prepare LiF inline from Li2CO3+2HF-&gt;2LiF+CO2+H2O at nominal complete conversion;1kWh/kgLiF utility is an explicit small-process allowance, not measured manufacture. No nonexistent finished-fluoride market or duplicate fluoride manufacture is bought. Source8.5kWh already uses kgmetal output; do not divide it by collection yield again. Fluorination feeds10%excessHF. Select dry salt-dust collection followed by99%capture of unreacted HF in a wet lime scrubber; capture and sequence are engineering choices, not demonstrated plant performance. CaO+2HF-&gt;CaF2+H2O;10%excessCaO becomes Ca(OH)2. No sulfur input exists, so no invented CaSO4 output is transferred from NETL. Retain source6.27e-5kg/kgNd dust with homogeneous NdF3/LiF loss composition; native fine-PM is a characterization proxy because the source does not establish the size/speciation distribution or individual RE-compound toxicity. Test zero/upscaled dust and capture. Source0.175kgprocess water plus reaction water goes to one negative wastewater treatment input at1000kg/m3. Captured salts,unconverted oxide,lime residues and spentcathode have one matched underground disposal reference; graphitepot and refractory have matched mineral disposal. These are treatment-class proxies, not measured leaching or hazard classification. No recovery/recycling/substitution credit. Lynas allows Mo/Wcathodes. Use an explicit same-volume Mo transfer of source2.7gW/kgNd with nominal densities10.28/19.25: 0.00144187012987kgMo/kgNd. Actual geometry and service life remain uncertain; test tenfold lower/higher consumption. Basic refractory is an unspecified refractory-class proxy. The elemental Nd/C/F/Li/Ca/H/O/Mo and aggregate material ledgers close, with unchanged refractory mass carried separately. Equipment construction, actual yields/assays,thermal integration,emissions speciation and process qualification remain uncertain. This supplies Nd reduction only; Pr/Tb/Dy/Ho and other precursor reduction and magnet alloy/powder/coating gaps are not silently declared solved. Keep existing magnet15kWh/kg for its downstream fabrication reference, separate from this reduction process. All measured magnet fractions, finished magnet dose,motor/vehicle/per-MJ quantities and finalEOL are unchanged. Existing supplemental workbook only; no runtime,YAML or active metal-indicator edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>neodymium production, molten salt electrolysis</t>
+        </is>
+      </c>
+      <c r="B1303">
+        <v>1.0</v>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>neodymium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>market for neodymium oxide</t>
+        </is>
+      </c>
+      <c r="B1304">
+        <v>1.2412915220936207</v>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>neodymium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>market for lithium carbonate</t>
+        </is>
+      </c>
+      <c r="B1305">
+        <v>0.0009300661975372661</v>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>lithium carbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>market for hydrogen fluoride</t>
+        </is>
+      </c>
+      <c r="B1306">
+        <v>0.0007429997805387021</v>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>hydrogen fluoride</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>market for graphite</t>
+        </is>
+      </c>
+      <c r="B1307">
+        <v>0.13934385918953662</v>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>market for quicklime, milled, loose</t>
+        </is>
+      </c>
+      <c r="B1308">
+        <v>0.00010308836218651622</v>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>quicklime, milled, loose</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1309">
+        <v>0.175</v>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>market for molybdenum</t>
+        </is>
+      </c>
+      <c r="B1310">
+        <v>0.0014418701298701299</v>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>molybdenum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>market for refractory, basic, packed</t>
+        </is>
+      </c>
+      <c r="B1311">
+        <v>0.09</v>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>refractory, basic, packed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1312">
+        <v>8.500957128</v>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B1313">
+        <v>-0.12</v>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="B1314">
+        <v>-0.07717668742596276</v>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B1315">
+        <v>-0.00017533120662317387</v>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, fossil</t>
+        </is>
+      </c>
+      <c r="B1316">
+        <v>0.05756224388258545</v>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>Carbon monoxide, fossil</t>
+        </is>
+      </c>
+      <c r="B1317">
+        <v>0.21870449236722184</v>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>Methane, tetrafluoro-, R-14</t>
+        </is>
+      </c>
+      <c r="B1318">
+        <v>1.4e-05</v>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>Ethane, hexafluoro-, HFC-116</t>
+        </is>
+      </c>
+      <c r="B1319">
+        <v>1.4e-06</v>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>Hydrogen fluoride</t>
+        </is>
+      </c>
+      <c r="B1320">
+        <v>6.754543459442758e-07</v>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>Particulate Matter, &lt; 2.5 um</t>
+        </is>
+      </c>
+      <c r="B1321">
+        <v>6.27e-05</v>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>biosphere</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1321"/>
+  <dimension ref="A1:U1352"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -36797,6 +36797,707 @@
         </is>
       </c>
       <c r="F1321" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>praseodymium production, molten salt electrolysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>praseodymium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1328">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jelechem.2024.118724 ; https://doi.org/10.3390/ma18010184 ; https://doi.org/10.1016/0022-5088(85)90092-X ; https://doi.org/10.1002/adem.201901206 ; https://www.osti.gov/servlets/purl/1509117</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>PRASEODYMIUM REDUCTION REFERENCE, 2026-10-20. One kg nominal Pr metal, from a Pr6O11 oxide convention consistent with the existing magnet recipe and Pr indicator. Local native metadata does not establish oxide oxidation state. This is a balanced engineering reference, NOT a measured commercial pure-Pr plant. Chen etal2024 DOI10.1016/j.jelechem.2024.118724 demonstrates Pr3+ reduction on W in LiF-PrF3-Pr6O11 and flags yield limitations. Cvetkovic etal2025 DOI10.3390/ma18010184 measures gases in Nd/Pr oxide-fluoride melts and supports higher-valence oxide/carbon chemistry, CO/CO2 and PFCs; do NOT turn its ppm peaks into unmeasured kg-per-kg industrial factors. Pr6O11 contains11oxygen/6Pr, not3oxygen/2Pr. Calculate the complete liberated oxygen and carbon-gas balance using the selected oxide; uncollected Pr is an oxide-equivalent residue, not a measured slag assay. Keep94%net metal collection as an explicit transfer of the existing light-REE engineering reference, not an observed Pr yield; test70-100%. Schreiber etal2020 DOI10.1002/adem.201901206 supports the light-REE MSE process class but quantifies Nd. Transfer its8.5kWh/kgNd toPr by144.242/140.90766 for equal trivalent-cation charge perkg; this is NOT measured Pr electricity. The higher-valence oxygen is included in the overall oxide/carbon gas balance. Test direct8.5kWh,12kWh and an11/9valence multiplier instead of asserting that same current efficiency or pre-reduction energetics is established. Transfer the Nd0.055:0.211CO2:CO mass ratio but recalculate gases from Pr-oxide oxygen. Scale Nd fluoride/LiF makeup and14mgCF4/1.4mgC2F6 by the same metal-mole ratio. Retain a fixed non-PFC bath loss and buy matched extra PrF3 for high-PFC cases. Fluorine comes fromPrF3 decomposition and its Pr joins the metal; no metallicLi is invented. These are explicit emission/bath transfers,not Pr factory data. Prepare PrF3 inline: Pr6O11+2H2-&gt;3Pr2O3+2H2O, thenPr2O3+6HF-&gt;2PrF3+3H2O. Hydrogen pre-reduction is a chosen preparation route supported by the1985oxide reduction study DOI10.1016/0022-5088(85)90092-X; it is not added to the bulk electrolysis feed. Reduce ALL fluoride-precursor oxide before95%fluorination: unconverted solids arePr2O3 and the associatedH2/reactionwater are counted. No unavailable finishedPrF3 supplier or duplicate oxide manufacture is purchased. Source3.9hydrogen,liquid,RER is the official legacy name migrating to gaseous medium-pressure merchantH2,RER in3.10+; it is a supply proxy,not extra liquefaction. Transfer0.528kWh/kgfluoride and1kWh/kgLiF utilities; add an explicit1kWh/kg fluoride-precursor-oxide pre-reduction allowance,not measured factory heating. HF feed has10%excess with96%capture reference; lime scrubbing closesCa/F/H/O. Select0.175kgprocesswater,0.03kggraphitepot,0.09kgrefractory and same-volume Mo cathode transfer of2.7gW at10.28/19.25density ratio from the existingNd architecture. Their Pr throughput/lifetimes are assumptions. Transfer6.27e-5kg salt dust withPrF3/LiF composition; generic finePM is a size/speciation proxy. Match oxide/salt/lime/cathode solids to underground disposal; graphitepot and refractory to inert disposal; process plus reactionwater to wastewater at 1000kg/m3. Disposal classes and leaching are unqualified. No recovery credit. ElementalPr/C/F/Li/Ca/H/O/Mo and aggregate mass close. Actual commercial yield,bath assay,energy,emissions,abatement,plant equipment and service life remain evidence gaps. Preserve B3 retained7.4%Pr,95%magnet fabrication retention, all other constituents,15kWh/kg downstream fabrication,finished magnet/motor/vehicle doses and finalEOL. A1 has noPr and is unchanged. Heavy-REE/Ca reduction and magnet alloy/powder/coating are separate gaps. Existing supplemental workbooks only; no active indicator definitions or primary/secondary shares changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>praseodymium production, molten salt electrolysis</t>
+        </is>
+      </c>
+      <c r="B1333">
+        <v>1.0</v>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>praseodymium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>market for praseodymium oxide</t>
+        </is>
+      </c>
+      <c r="B1334">
+        <v>1.2857597883644067</v>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>praseodymium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>market for lithium carbonate</t>
+        </is>
+      </c>
+      <c r="B1335">
+        <v>0.0009520746314655309</v>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>lithium carbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>market for hydrogen fluoride</t>
+        </is>
+      </c>
+      <c r="B1336">
+        <v>0.0007605816060281143</v>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>hydrogen fluoride</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>market for hydrogen, liquid</t>
+        </is>
+      </c>
+      <c r="B1337">
+        <v>2.072607175903332e-06</v>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>hydrogen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>market for graphite</t>
+        </is>
+      </c>
+      <c r="B1338">
+        <v>0.1668044266985518</v>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>market for quicklime, milled, loose</t>
+        </is>
+      </c>
+      <c r="B1339">
+        <v>0.0001023299615597901</v>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>quicklime, milled, loose</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1340">
+        <v>0.175</v>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>market for molybdenum</t>
+        </is>
+      </c>
+      <c r="B1341">
+        <v>0.0014418701298701299</v>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>molybdenum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>market for refractory, basic, packed</t>
+        </is>
+      </c>
+      <c r="B1342">
+        <v>0.09</v>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>refractory, basic, packed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1343">
+        <v>8.702637712370528</v>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B1344">
+        <v>-0.12</v>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="B1345">
+        <v>-0.07986172744986104</v>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B1346">
+        <v>-0.00017535672437878042</v>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, fossil</t>
+        </is>
+      </c>
+      <c r="B1347">
+        <v>0.0718926417538634</v>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>Carbon monoxide, fossil</t>
+        </is>
+      </c>
+      <c r="B1348">
+        <v>0.2736308202504637</v>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>Methane, tetrafluoro-, R-14</t>
+        </is>
+      </c>
+      <c r="B1349">
+        <v>1.433128617706092e-05</v>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>Ethane, hexafluoro-, HFC-116</t>
+        </is>
+      </c>
+      <c r="B1350">
+        <v>1.433128617706092e-06</v>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>Hydrogen fluoride</t>
+        </is>
+      </c>
+      <c r="B1351">
+        <v>2.7657512946476926e-06</v>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>Particulate Matter, &lt; 2.5 um</t>
+        </is>
+      </c>
+      <c r="B1352">
+        <v>6.27e-05</v>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
         <is>
           <t>biosphere</t>
         </is>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1352"/>
+  <dimension ref="A1:U1394"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -37498,6 +37498,863 @@
         </is>
       </c>
       <c r="F1352" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>calcium production, aluminothermic reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1359">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>https://bureau-industrial-transformation.jrc.ec.europa.eu/sites/default/files/2020-03/superseded_nfm_bref_1201.pdf ; https://eprints.nmlindia.org/id/eprint/4042/ ; https://patents.google.com/patent/US20230049604A1/en ; https://doi.org/10.1016/j.mtchem.2021.100608 ; https://behost.lib.iastate.edu/DR/Croat_TN798-C7x.pdf ; https://patents.google.com/patent/CN118854092B/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>CALCIUM REDUCTANT MANUFACTURE, 2026-10-20. One kg nominal elementalCa from aluminothermic lime reduction; NOT lime bought at a metal equivalent. EC2001NonferrousBREF sections10.1.4.1.2/10.2.1,pp589/596, documents electric-resistance vacuum retorts and20-25kWh/kgmetal directenergy, in addition to upstream lime/Al manufacture. Select22.5kWh/kg as an old European process-class reference transferred to genericGLO electricity; not a measured current world mix or technology-learning forecast. Jacob/Srikanth1990 establishes3CaO.Al2O3 as the practical aluminate endpoint: 6CaO+2Al-&gt;3Ca+Ca3Al2O6. Select approximate3kgreactiveCaO+0.5kgAl perkgCa consistent with the prior-art feed context inUS20230049604A1; derive the actual species ledger rather than copying rounded2.5kgslag. Unreacted lime remains; excessAl and any lostCa undergo selected dry passivation toAl2O3/CaO using ambientoxygen. No reactive metal is sent untreated to nominal mineral disposal. Buy quicklime at selected95%CaO and nominal elementalAl ingot,aligned with the database/indicator metal convention; actual commercial assays are unspecified. Test99.7%/95%Al alternatives. Unassayed impurities are carried as unchanged bulk solid, not invented trace elements. The existing native primary-ingot commodity is a specific reductant supply reference; no primary/secondary fraction or recyclingcredit is inferred. Use the source3.9European ingot market (IAI Area,EU27 &amp;EFTA),matching the reference process region; official migration selects the current Western/CentralEurope market. This is a procurement proxy,not a world mix. Nominal reactionmetal collection100% is bookkeeping for this output-based feed reference, not an observed plant recovery; loss alternatives scale feed and passivated solids explicitly. Do not divide output-based22.5kWh by a second assumed source yield. Add0.01kg/kg generic furnace refractory with equal spent mass. Slag/impurity/refractory mass goes once to negative inert-waste disposal, an unqualified treatment-class proxy. Upstream calcination CO2 is already in quicklime; no second direct calcination emission. Ambient oxygen remains an uncharacterized mass-ledger term. Grinding/pelletizing/vacuum/heating are assigned the combined utility reference; actual powder preparation,cooling,retort hardware,gas/dust losses,productpurity and industrial qualification remain gaps. Nominal Ca/Al/O and totalmass close. This supplies the new Ho reduction step; it does not replace the existing CaO constituent in magnets without evidence of its actual chemical form. Existing supplemental workbook only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>calcium production, aluminothermic reduction</t>
+        </is>
+      </c>
+      <c r="B1364">
+        <v>1.0</v>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>market for quicklime, milled, loose</t>
+        </is>
+      </c>
+      <c r="B1365">
+        <v>3.1578947368421053</v>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>quicklime, milled, loose</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B1366">
+        <v>0.5</v>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>IAI Area, EU27 &amp; EFTA</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1367">
+        <v>22.5</v>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1367" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>market for refractory, basic, packed</t>
+        </is>
+      </c>
+      <c r="B1368">
+        <v>0.01</v>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>refractory, basic, packed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B1369">
+        <v>-2.7134189187434643</v>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>holmium production, calcium reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>holmium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1376">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>https://bureau-industrial-transformation.jrc.ec.europa.eu/sites/default/files/2020-03/superseded_nfm_bref_1201.pdf ; https://eprints.nmlindia.org/id/eprint/4042/ ; https://patents.google.com/patent/US20230049604A1/en ; https://doi.org/10.1016/j.mtchem.2021.100608 ; https://behost.lib.iastate.edu/DR/Croat_TN798-C7x.pdf ; https://patents.google.com/patent/CN118854092B/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>HOLMIUM REDUCTION REFERENCE, 2026-10-20. One kg nominal Ho metal. Use a heavy-REE fluoride/calcium route, not the Nd/Pr electrolysis inventory. Published anhydrous-fluoride research and the Ames historical calcium-route account support Ho fluoride reduction withCa and subsequent vacuum refining. No assertion of a measured commercial Ho plant or high-purity5N product. Ho2O3+6HF-&gt;2HoF3+3H2O;2HoF3+3Ca-&gt;2Ho+3CaF2. Select98%fluorination and98%net metalcollection, testing losses separately. These are engineering references: the historical97-99%calcium-route yields are not current Ho factory qualification. CN118854092B supports HF/NH4HF2 fluorination and 10-20%excessCa process windows but describes extra5Npurification; do not silently claim itsKF/NaF additives,twostage1800-2000Cdistillation or yield as this reference. Choose HF and the conventional self-fluxingCaF2 route, 10%Caexcess,10%HFexcess and99%unreactedHFcapture in a lime scrubber. Buy metallicCa from the separate balanced aluminothermic provider, including its Al,energy and residue boundary. Do not purchase lime as if it were metallicCa or buy the same lime/Al manufacture twice. Nominal unrecoveredHo and unusedCa are separated and dry-passivated to oxides with ambientoxygen before disposal. Actual segregation, recovery,passivation utilities and residue speciation remain unqualified. No recovered-metal credit or unmeasured full internal recycle. Choose6kWh/kgHo combined reduction/vacuum-refining electricity plus 0.528kWh/kgHoF3 fluorination utility as explicit allowances/fluoride analogy,not measured Ho electricity; test broad heating alternatives. Use10normalLAr/kgHo at273.15K/101325Pa (39.948g/mol),purchased through native liquidargon as a delivery proxy. UncharacterizedAr release is in the massledger only. Choose an explicit1kgmetalbatch Ta vessel: 100mmID,150mminternalheight,2mmwall/base,16650kg/m3,1000batches; divide its shell/base mass by total lifetime output. Geometry/life are assumptions,not supplier measurements. Native capacitor-grade Ta powder is an elemental feed proxy,not a purchased capacitor or finished crucible. Add20kWh/kgTa forming/sintering allowance; actual Ta grade,crucible manufacture,purity and life require qualification. W vacuum hardware and other plant equipment are not represented by a fabricated carbide-as-metal proxy; their proper inventories remain gaps. Add0.01kg/kg generic refractory and0.5kgprocesswater, both explicit allowances. Match CaF2,oxide/scrubber/cathode residues to one underground waste input; refractory to inertdisposal; process+reactionwater to wastewater at1000kg/m3. Treatment/hazard/leaching assumptions are not certified. Ho/Ca/F/H/O/Ta and aggregate mass close, including ambientair andAr. No PFC factors from a different electrolysis route are inserted. Retain both magnetHo fractions,95%magnet fabrication retention,all other constituents,downstream energy,motor/vehicle/per-MJ doses and finalEOL. The existing CaO magnetconstituent stays unchanged pending speciation. Tb/Dy reduction,actual industrial qualification and magnet alloy/powder/ coating remain open. Active indicator definitions are unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1380" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1380" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>holmium production, calcium reduction</t>
+        </is>
+      </c>
+      <c r="B1381">
+        <v>1.0</v>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1381" t="inlineStr">
+        <is>
+          <t>holmium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>market for holmium oxide</t>
+        </is>
+      </c>
+      <c r="B1382">
+        <v>1.1927393728956757</v>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>holmium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>market for hydrogen fluoride</t>
+        </is>
+      </c>
+      <c r="B1383">
+        <v>0.408466413950889</v>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>hydrogen fluoride</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>calcium production, aluminothermic reduction</t>
+        </is>
+      </c>
+      <c r="B1384">
+        <v>0.4091319365341866</v>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1384" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>market for quicklime, milled, loose</t>
+        </is>
+      </c>
+      <c r="B1385">
+        <v>0.05667314409146499</v>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1385" t="inlineStr">
+        <is>
+          <t>quicklime, milled, loose</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1386">
+        <v>0.5</v>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1386" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>market for tantalum powder, capacitor-grade</t>
+        </is>
+      </c>
+      <c r="B1387">
+        <v>0.0018834890967031814</v>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>tantalum powder, capacitor-grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>market for argon, liquid</t>
+        </is>
+      </c>
+      <c r="B1388">
+        <v>0.01782281354481728</v>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>argon, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1389">
+        <v>6.762630714016732</v>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>market for refractory, basic, packed</t>
+        </is>
+      </c>
+      <c r="B1390">
+        <v>0.01</v>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>refractory, basic, packed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="B1391">
+        <v>-0.9042583346313534</v>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B1392">
+        <v>-0.01</v>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B1393">
+        <v>-0.0006820818594946691</v>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>Hydrogen fluoride</t>
+        </is>
+      </c>
+      <c r="B1394">
+        <v>0.0003713331035917181</v>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
         <is>
           <t>biosphere</t>
         </is>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1394"/>
+  <dimension ref="A1:U1420"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -38355,6 +38355,582 @@
         </is>
       </c>
       <c r="F1394" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>terbium production, calcium reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>terbium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1401">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.mtchem.2021.100608 ; https://doi.org/10.1039/J19690001256 ; https://behost.lib.iastate.edu/DR/Croat_TN798-C7x.pdf ; https://patents.google.com/patent/CN118854092B/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>TERBIUM REDUCTION REFERENCE, 2026-10-20. One kg nominal Tb metal; a balanced engineering reference, not a measured industrial plant or a certified product purity. Hung etal2021 DOI10.1016/j.mtchem.2021.100608 supports anhydrous fluoride preparation followed by calcium reduction for high-melting Tb. Its experiment uses NH4HF2; the paper also identifies HF-gas fluorination as an alternative. Do not copy its ammonium-reagent doses or assert that this workbook reproduces that experiment. Choose a separate H2/HF route: Tb4O7+H2-&gt;2Tb2O3+H2O; Tb2O3+6HF-&gt;2TbF3+3H2O;2TbF3+3Ca-&gt;2Tb+3CaF2. Gallagher/Jenkins1969 DOI10.1039/J19690001256 used H2 reduction to regenerate TbO1.5; it does not supply industrial utility or recovery factors. Tb4O7 is the existing recipe and contained-metal convention, not an independently established native market assay. Reduce ALL charged oxide before selected98%fluorination; include the extra mixed-valence oxygen in H2 and reactionwater. Select98%netmetal collection, 10%Ca excess,10%HF excess and99%unreactedHF capture with lime. These are explicit assumptions with recovery/capture/excess sensitivities, not measured Tb factory values. Purchase elementalCa from the existing separate aluminothermic provider, including its manufacture once; lime is only the scrubber reagent. Select controlled dry stabilization of unrecoveredTb and unfluorinatedTb2O3 to Tb4O7, and excessCa toCaO. Include the oxygen required to reoxidize the unfluorinated sesquioxide; no oxygen is silently created in the residue. Nominal netH2 is stoichiometric; excessH2 comparator cases use controlled oxidation to water with ambient oxygen and no heat credit. Actual purge, recirculation,segregation/passivation and emissions remain unqualified. Choose10kWh/kgTb combined reduction/refining electricity plus1kWh/kgcharged oxide for H2preparation and0.528kWh/kgTbF3 fluorination allowance. Tb is in a different high-boiling refining class fromHo;10kWh is an explicit allowance, not a measured Tb/Ho scale factor. Test broad separate heating alternatives. GLO medium-voltage electricity is a generic supply reference,not a regional production mix. Source3.9liquidH2,RER is the official legacy supplier name migrating to medium-pressure merchant gaseousH2,RER in3.10+; do not add duplicate liquefaction. Buy10normalLAr/kg at273.15K/101325Pa through native liquidAr as delivery proxy; its uncharacterized release remains in massledger. Choose100mmID,150mmheight,2mmwall/base Ta vessel,16650kg/m3,1000onekg batches; allocate shell/base feed over lifetime output and add20kWh/kgTa forming allowance. Native capacitor-gradeTa powder is elemental supply,not a finished crucible. Purity,geometry,manufacture and life remain assumptions; vacuum/retort hardware and cooling are gaps,not fabricated tungsten-carbide proxies. Add0.01kgrefractory and0.5kgprocesswater/kgTb. Match stabilizedTb/Ca,fluoride, scrubber andTa solids once to underground disposal; refractory to inert disposal; process+reactionwater to wastewater at1000kg/m3. Treatment classes and leaching are unqualified. No recovery credit or electrolysis-route PFCs. Tb/Ca/F/H/O/Ta and aggregate mass close,including ambient oxygen andAr. Preserve both magnetTb fractions,95%fabrication retention,all other constituents, downstream energy,motor/vehicle/per-MJ equipment doses and finalEOL. Existing magnetCaO constituent is unchanged pending speciation. Dy reduction,alloy/powder/ coating and actual commercial qualification remain gaps. Active indicators unchanged under workbook-only scope; no delivered-Tb system total certified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1405" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>terbium production, calcium reduction</t>
+        </is>
+      </c>
+      <c r="B1406">
+        <v>1.0</v>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>terbium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>market for terbium oxide</t>
+        </is>
+      </c>
+      <c r="B1407">
+        <v>1.2246692367750838</v>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>terbium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>market for hydrogen fluoride</t>
+        </is>
+      </c>
+      <c r="B1408">
+        <v>0.4239002805206138</v>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>hydrogen fluoride</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>market for hydrogen, liquid</t>
+        </is>
+      </c>
+      <c r="B1409">
+        <v>0.003302061886966879</v>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>hydrogen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>calcium production, aluminothermic reduction</t>
+        </is>
+      </c>
+      <c r="B1410">
+        <v>0.4245909498146297</v>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>market for quicklime, milled, loose</t>
+        </is>
+      </c>
+      <c r="B1411">
+        <v>0.058814533723807225</v>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>quicklime, milled, loose</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1412">
+        <v>0.5</v>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>market for tantalum powder, capacitor-grade</t>
+        </is>
+      </c>
+      <c r="B1413">
+        <v>0.0018834890967031814</v>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>tantalum powder, capacitor-grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>market for argon, liquid</t>
+        </is>
+      </c>
+      <c r="B1414">
+        <v>0.01782281354481728</v>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>argon, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1415">
+        <v>11.99433495014637</v>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>market for refractory, basic, packed</t>
+        </is>
+      </c>
+      <c r="B1416">
+        <v>0.01</v>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>refractory, basic, packed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="B1417">
+        <v>-0.9378342343413424</v>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B1418">
+        <v>-0.01</v>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B1419">
+        <v>-0.000718469070447265</v>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>Hydrogen fluoride</t>
+        </is>
+      </c>
+      <c r="B1420">
+        <v>0.0003853638913823768</v>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1420" t="inlineStr">
         <is>
           <t>biosphere</t>
         </is>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -2571,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1420"/>
+  <dimension ref="A1:U1445"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -38931,6 +38931,552 @@
         </is>
       </c>
       <c r="F1420" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>dysprosium production, calcium reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>dysprosium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1427">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.31276/VJSTE.2023.0012 ; https://doi.org/10.1016/j.mtchem.2021.100608 ; https://behost.lib.iastate.edu/DR/Croat_TN798-C7x.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>DYSPROSIUM REDUCTION REFERENCE, 2026-10-20. One kg nominal Dy metal for the existing A1 magnet sensitivity. No Dy is added to the default B3 grade. Use a balanced engineering route,not a measured commercial inventory. Hung/Thuy/Thuan2024 DOI10.31276/VJSTE.2023.0012 reports85.7%reduction response with Ca/DyF3molar ratio2.15 in a small-batch experiment at1450-1460C,50minutes. Its HCl/ICP-based response is not finished puremetal recovery. Select0.857 as one-pass conversion in this explicit ledger; nominal downstream collection1 adds no second undocumented yield penalty. Test extra collectionloss separately. Charge2.15molCa per mol INITIAL DyF3,not per mol Dyformed; preserve unreduced DyF3 and its fluorine in the solidresidue. This is a chosen material partition for an engineering reference,not a measured waste assay or factory purity claim. The source prepares fluoride with NH4HF2; this workbook instead chooses the HF alternative described in DOI10.1016/j.mtchem.2021.100608. Do not transplant the source ammoniumrecipe or its reported fluoride efficiency into the HF route. Dy2O3+6HF-&gt;2DyF3+3H2O;2DyF3+3Ca-&gt;2Dy+3CaF2. No mixed-valence H2 pre-reduction is needed for trivalent Dy2O3. Choose98%HF-route fluorination, 10%HFexcess and99%unreactedHFcapture with lime. Existing oxide convention and nominal elementalCa align with database/indicator accounting; actual market assay and source99%Ca procurement are not certified by this reference. Buy metallicCa from the existing separate aluminothermic provider,including its Al,energy and residue once. Do not buy the same manufacture again as lime. Selected unusedCa and any separate uncollectedDy are dry-passivated to oxides with ambientoxygen. UnfluorinatedDy2O3 and unreducedDyF3 remain distinct solids. No internalrecycle or recoveredmetal credit is assumed. Speciation,stabilization, segregation and actual collection require qualification. SourceHCl is analytical testing,not an industrial dissolution purchase or destruction of the deliveredmetal. Choose6kWh/kgDy reduction/vacuum-refining electricity plus0.528kWh/kgprepared DyF3 fluorination allowance and20kWh/kgTa forming allowance. These are output-based engineering utilities,not metered Dy values. Do not multiply the source15kW nameplate by holdtime and label it measured industrial consumption. Test heating and batchscale separately. Use genericGLO mediumvoltage supply. Choose10normalLAr/kg at273.15K/101325Pa through liquidAr deliveryproxy; the massledger includes its uncharacterized airrelease. Its use is not the source small-batch gas budget. Choose a1kgmetalbatch Ta vessel,100mmID, 150mmheight,2mmwall/base,16650kg/m3 and1000batches. Geometry/life are assumptions; native capacitor-gradeTa powder is elementalfeed,not finishedcrucible. Actual Ta purity,refining/cooling/vacuum/retort hardware and manufacture remain gaps. Do not use tungsten carbide as an unavailable tungstenmetal proxy. Add0.01kgrefractory and0.5kgprocesswater/kgDy as allowances. Match Dyoxide/ fluoride,CaF2/passivatedCa,scrubber andTa residues once to underground disposal; refractory to inertdisposal; process+reactionwater to wastewater at1000kg/m3. Treatment classes and leaching are unqualified. No PFC factors from a different electrolysis route. Dy/Ca/F/H/O/Ta and totalmass close,including ambientoxygen andAr. Preserve A1Dy0.5/100.1,95%magnetretention,otherinputs,downstream energy, equipment/per-MJ doses and finalEOL. B3 is unchanged. Existing magnetCaO constituent stays pending speciation. Actual alloy/powder/coating and commercial qualification remain open. Active indicators unchanged under workbook-only scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>dysprosium production, calcium reduction</t>
+        </is>
+      </c>
+      <c r="B1432">
+        <v>1.0</v>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>dysprosium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>market for dysprosium oxide</t>
+        </is>
+      </c>
+      <c r="B1433">
+        <v>1.3665171301444017</v>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>dysprosium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>market for hydrogen fluoride</t>
+        </is>
+      </c>
+      <c r="B1434">
+        <v>0.47407687236621493</v>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>hydrogen fluoride</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>calcium production, aluminothermic reduction</t>
+        </is>
+      </c>
+      <c r="B1435">
+        <v>0.6187430212727763</v>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>market for quicklime, milled, loose</t>
+        </is>
+      </c>
+      <c r="B1436">
+        <v>0.0657763428776592</v>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>quicklime, milled, loose</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1437">
+        <v>0.5</v>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1437" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>market for tantalum powder, capacitor-grade</t>
+        </is>
+      </c>
+      <c r="B1438">
+        <v>0.0018834890967031814</v>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1438" t="inlineStr">
+        <is>
+          <t>tantalum powder, capacitor-grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>market for argon, liquid</t>
+        </is>
+      </c>
+      <c r="B1439">
+        <v>0.01782281354481728</v>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1439" t="inlineStr">
+        <is>
+          <t>argon, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1440">
+        <v>6.86986416743046</v>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1440" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>market for refractory, basic, packed</t>
+        </is>
+      </c>
+      <c r="B1441">
+        <v>0.01</v>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1441" t="inlineStr">
+        <is>
+          <t>refractory, basic, packed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="B1442">
+        <v>-1.4145538904261759</v>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B1443">
+        <v>-0.01</v>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B1444">
+        <v>-0.0007113289991921731</v>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>Hydrogen fluoride</t>
+        </is>
+      </c>
+      <c r="B1445">
+        <v>0.00043097897487837805</v>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F1445" t="inlineStr">
         <is>
           <t>biosphere</t>
         </is>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -14846,7 +14846,9 @@
       </c>
       <c r="B403" s="14" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
+          <t>CONTROL-CABLE RETIREMENT MASS CORRECTION, 2026-10-20. Existing purchased control-unit assembly:100kg, nominal46%steel/32%industrial plastic/14%mounted boards/8%cables; native ecoinvent control-unit documentation, checked in3.12cutoff RER andRoW. Cable inputs expressed partly in metres are NOT summed as kg. These are retained source assembly fractions, not a newly measured control-panel BOM. Existing inventory sources Gerloff2021 DOI10.1016/j.est.2021.102759 and the separately documented replacement power-conversion/drive kits. For one AEC BoP the100kg control assembly contributes8kg nominal finished cables, not800kg. Correct only its aggregate used-cable treatment purchase from-800 to-8kg. PEM/SOEC already use-8kg. The371.7kg separate AEC copper feed already has its separate approximately372kg scrap-Cu route; it is not an extra800kg cable. Replacement converter and motor-drive disposal remains in its dedicated kit and is not added here. Preserve negative waste production and negative treatment purchase, so actual disposal activation stays positive. Manufacturing, metal purchases, operating energy, stack and equipment lifetimes are unchanged. This removes792kg unsupported waste per BoP; it does not qualify the real cable design or all other BoP waste fractions.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -15154,7 +15156,7 @@
         <v>219</v>
       </c>
       <c r="B415" s="11">
-        <v>-800</v>
+        <v>-8.0</v>
       </c>
       <c r="C415" s="11" t="s">
         <v>17</v>
@@ -15167,6 +15169,11 @@
       </c>
       <c r="G415" s="11" t="s">
         <v>220</v>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>CONTROL-CABLE RETIREMENT MASS CORRECTION, 2026-10-20. Existing purchased control-unit assembly:100kg, nominal46%steel/32%industrial plastic/14%mounted boards/8%cables; native ecoinvent control-unit documentation, checked in3.12cutoff RER andRoW. Cable inputs expressed partly in metres are NOT summed as kg. These are retained source assembly fractions, not a newly measured control-panel BOM. Existing inventory sources Gerloff2021 DOI10.1016/j.est.2021.102759 and the separately documented replacement power-conversion/drive kits. For one AEC BoP the100kg control assembly contributes8kg nominal finished cables, not800kg. Correct only its aggregate used-cable treatment purchase from-800 to-8kg. PEM/SOEC already use-8kg. The371.7kg separate AEC copper feed already has its separate approximately372kg scrap-Cu route; it is not an extra800kg cable. Replacement converter and motor-drive disposal remains in its dedicated kit and is not added here. Preserve negative waste production and negative treatment purchase, so actual disposal activation stays positive. Manufacturing, metal purchases, operating energy, stack and equipment lifetimes are unchanged. This removes792kg unsupported waste per BoP; it does not qualify the real cable design or all other BoP waste fractions.</t>
+        </is>
       </c>
       <c r="J415"/>
       <c r="K415" s="19"/>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -19819,7 +19819,9 @@
       </c>
       <c r="B577" s="14" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
+          <t>SOEC BoP STEEL RETIREMENT RECONCILIATION, 2026-10-20. Existing purchased control-unit assembly:100kg, nominal46%steel/32%industrial plastic/14%mounted boards/8%cables; native ecoinvent control-unit documentation, checked in3.12cutoff RER andRoW. Cable inputs expressed partly in metres are NOT summed as kg. These are retained source assembly fractions, not a newly measured control-panel BOM. Existing inventory sources Gerloff2021 DOI10.1016/j.est.2021.102759 and the separately documented replacement power-conversion/drive kits. Read retained material purchases, not the separate forming-service kg:ordinary/stainless steel16215.4+1503.6+2250=19969kg, plus46kg control housing gives20015kg to existing scrap-steel route. Reinforcing steel6500+5000+8.5+452.1+399+7+267=12633.6kg to its existing sorting route. Previous20421kg scrap steel and12227kg reinforcement misplaced approximately406kg between routes and retained0.6kg source rounding. Correct these two amounts only. Cast iron3000kg has its separate route. All new transformer, converter and replacement-drive metals remain handled by their separate treatment kit: do not add them to these totals again. Manufacturing, metal feeds, operating energy, lifetimes, waste signs and supplier identities are unchanged. This reconciles the existing nominal material ledger, not actual plant grades or recycling recovery fractions; no avoided-production credit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -19972,7 +19974,7 @@
         <v>204</v>
       </c>
       <c r="B584" s="11">
-        <v>-20421</v>
+        <v>-20015.0</v>
       </c>
       <c r="C584" s="11" t="s">
         <v>37</v>
@@ -19985,6 +19987,11 @@
       </c>
       <c r="G584" s="11" t="s">
         <v>205</v>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>SOEC BoP STEEL RETIREMENT RECONCILIATION, 2026-10-20. Existing purchased control-unit assembly:100kg, nominal46%steel/32%industrial plastic/14%mounted boards/8%cables; native ecoinvent control-unit documentation, checked in3.12cutoff RER andRoW. Cable inputs expressed partly in metres are NOT summed as kg. These are retained source assembly fractions, not a newly measured control-panel BOM. Existing inventory sources Gerloff2021 DOI10.1016/j.est.2021.102759 and the separately documented replacement power-conversion/drive kits. Read retained material purchases, not the separate forming-service kg:ordinary/stainless steel16215.4+1503.6+2250=19969kg, plus46kg control housing gives20015kg to existing scrap-steel route. Reinforcing steel6500+5000+8.5+452.1+399+7+267=12633.6kg to its existing sorting route. Previous20421kg scrap steel and12227kg reinforcement misplaced approximately406kg between routes and retained0.6kg source rounding. Correct these two amounts only. Cast iron3000kg has its separate route. All new transformer, converter and replacement-drive metals remain handled by their separate treatment kit: do not add them to these totals again. Manufacturing, metal feeds, operating energy, lifetimes, waste signs and supplier identities are unchanged. This reconciles the existing nominal material ledger, not actual plant grades or recycling recovery fractions; no avoided-production credit.</t>
+        </is>
       </c>
       <c r="J584"/>
       <c r="K584" s="19"/>
@@ -20001,7 +20008,7 @@
         <v>449</v>
       </c>
       <c r="B585" s="11">
-        <v>-12227</v>
+        <v>-12633.6</v>
       </c>
       <c r="C585" s="11" t="s">
         <v>217</v>
@@ -20017,7 +20024,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+          <t>SOEC BoP STEEL RETIREMENT RECONCILIATION, 2026-10-20. Existing purchased control-unit assembly:100kg, nominal46%steel/32%industrial plastic/14%mounted boards/8%cables; native ecoinvent control-unit documentation, checked in3.12cutoff RER andRoW. Cable inputs expressed partly in metres are NOT summed as kg. These are retained source assembly fractions, not a newly measured control-panel BOM. Existing inventory sources Gerloff2021 DOI10.1016/j.est.2021.102759 and the separately documented replacement power-conversion/drive kits. Read retained material purchases, not the separate forming-service kg:ordinary/stainless steel16215.4+1503.6+2250=19969kg, plus46kg control housing gives20015kg to existing scrap-steel route. Reinforcing steel6500+5000+8.5+452.1+399+7+267=12633.6kg to its existing sorting route. Previous20421kg scrap steel and12227kg reinforcement misplaced approximately406kg between routes and retained0.6kg source rounding. Correct these two amounts only. Cast iron3000kg has its separate route. All new transformer, converter and replacement-drive metals remain handled by their separate treatment kit: do not add them to these totals again. Manufacturing, metal feeds, operating energy, lifetimes, waste signs and supplier identities are unchanged. This reconciles the existing nominal material ledger, not actual plant grades or recycling recovery fractions; no avoided-production credit.</t>
         </is>
       </c>
       <c r="J585"/>

--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -10853,7 +10853,9 @@
       </c>
       <c r="B262" s="14" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
+          <t>DUPLICATE CONTROL-PLASTIC RETIREMENT CORRECTION, 2026-10-20. Existing purchased control-unit assembly:100kg, nominal46%steel/32%industrial plastic/14%mounted boards/8%cables; native ecoinvent control-unit documentation, checked in3.12cutoff RER andRoW. Cable inputs expressed partly in metres are NOT summed as kg. These are retained source assembly fractions, not a newly measured control-panel BOM. Existing inventory sources Gerloff2021 DOI10.1016/j.est.2021.102759 and the separately documented replacement power-conversion/drive kits. The100kg plant control-unit assembly already sends its32kg nominal housing plastic to the existing industrial-electronics plastic waste route. The additional32kg mixed-plastic entry in PEM, and32kg within the34.8kg SOEC mixed-plastic entry, duplicate that same finished housing. Remove only the duplicate32kg: PEM-32 becomes0kg; SOEC-34.8 becomes-2.8kg. Keep SOEC1.4kgABS control panel+1.4kg elastomer insulation once in the mixed route. Keep PEM764.6kg and SOEC534kg PE/PP retirement separately; these correspond to the direct finished polymer purchases. AEC mixed plastic remains unchanged: its93kg represents92.9kg separate elastomer insulation with original rounding, not another control housing. The source control-unit32.193kg gross polymer feed contains its own manufacturing loss and is not32.193kg finished housing. Dedicated converter/drive-kit and cable/PCB treatments remain unchanged. No extra manufacture, changed metal input, operating energy, lifetime or recycling credit. This reconciles the nominal retirement boundary, not polymer grade or actual fate.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED INDUSTRIAL RECTIFIER/TRANSFORMER HARDWARE REFERENCE, issue93, 2026-10-18. ABB2024DCS880PEP,ABBG-00601-V01.01-EN,pp4-10,industrialDCconverters9-5520kWincludingelectrolysis:reference120.63kgincluding6.8kgpackaging,materialcategoriesperTable;187kgH7familyusedasgrosscabinet-scaleanalogue. https://library.e.abb.com/public/41e28362ad194fb1b6172e296a83ee64/PEP_EPD_DCS880_H1_H8_3AXD10002336256_RevA_EN_20241003.pdf . InfineonFF1000UXTR23T2M1MCD18July2025,1017g,2300VSiChalfbridgemodule: https://www.infineon.com/assets/row/public/documents/60/75/infineon-ff1000uxtr23t2m1-materialcontentdatasheet-en.pdf . IEAPVPS2026DOI10.69766/WJTE1771X-transformer-utilityL,2500kVA20/0.4kVmanufacturer-based5681.2kgoiltransformerprofile(Boutros2026/Schneider2016). Theold1tonne(100Al+200Cu+600steel+100elastomer)power-electronicsblockhadnopart-levelrectifierrecipe. ReplaceonlythatblockinPEM/AEC/SOECBoPs,notcompressor/pumpfrequencyconvertersor100kgplantcontrols. Newone1MWreferencecomprises187kgconverterand1.1MVAtransformer,nominalgrossmass2686.728kg;old1000kgmasswasnotindependentlyvalidatedandisNOTpreservedasmeasuredtruth. Thisis an explicitREFERENCE-DESIGNCHANGErequiringoldbulk-versusnewreferenceandtransformer1.05-1.5MVAsensitivity,notproofthatallsitesneedthismass. Converteris a syntheticactivefront-endengineeringvariant,NOTa certifiedABB_DCS880(whichisthyristor-based). Transferonlyitsindustrialcabinetmaterialprofileand187kgfamilymass;use3documentedSiChalfbridgemodules(6switches)at3*1.017kg,a1MW1100VDC/690VACreference. At98%converterefficiencyand0.99powerfactor,ACcurrent=862.4402397079726A,DCcurrent909.09A;1.1MVAexceeds1MW/(.98*.99). Semiconductorvoltage2300Vhasheadroom;Transformerleakageisassumedtoprovideinputreactanceinthedeclaredreference;actualneedforadditionallinechokes/EMIfiltersis anunresolveddesigngap,notclaimedzeroequipment. Actualjunctiontemperature,ripple,DCstackvoltage,controlstabilityandcoolingMUSTbevalidatedforarealdesign. Module is anindustrial/renewablespowerpart,notanEVinverterinventory. Threepartsare a topologyassumption,notsourcedABBfittedcount. Factory2025/26designisananalogueforstaticinventoryyears,notmeasured2020installedtechnology. MCDknownretainedfractions={'Cu': 0.68, 'Sn': 0.016, 'SiC': 0.001, 'Si3N4': 0.009, 'Ni': 0.001, 'Sb': 0.001, 'Ag': 0.001, 'silicone': 0.084, 'PA': 0.089, 'glass': 0.046, 'orgP': 0.015, 'steel': 0.05, 'carbon': 0.001, 'PbO': 1.8e-05};sum=0.9940180000000001,remainder=0.005981999999999932unquantifiedtrace/rounding/otheradditives. Gold,Co,Y,Mg,Zn,CrtracesmarkedXareUNQUANTIFIED,notzero. Usefullknownmaterialfeedonce,100%finalassemblyreference;nativefeedproductionyieldremains. SiCpowderandstoichiometricSi3N4arefeed-gradeproxies;semiconductorwafer/epitaxy/dieyieldandpurificationenergyareunresolved,notrepresentedbyanextraall-siliconICTchip. Si3N4=3Si+2N2with3MJ/kgheat+1kWh/kgengineeringmanufacture;PbO=Pb+Owith3MJ/kgheat. Convertergrosscategoryledger={'ABS': 8.12501282614425, 'GFplastic': 7.530499692523939, 'PA': 1.3871973117807257, 'steel': 53.308010981287886, 'Al': 42.80494562066239, 'Cu': 39.832379952560835, 'electronics': 29.131143547395236, 'other': 2.5762235790213475}. EPDpercentagesandpackagingareincomplete/rounded:retainknownabsoluteamountson120.63kg/113.83kgproductbasis;doNOTrenormalizecategoriesorapplypackagingasinstalledproduct. Knownbulkmetals/plasticsplusmoduleingredientsaremodeled. Electronicscategorypartition:3.051kgcompletepowermodules,8kgmountedgate/protectionPCBs,14kgfilmDC-linkcapacitors,1kgcoolingblower,remaining3.080143547395238kgUNRESOLVED. ThesePCB/capacitor/fanmassallocationsareengineeringassumptionswith50-150%sensitivity,notmanufacturerBOM.14kgcapbankreference5mFat1100Vstores3.025kJ;actualESR/ripple/hold-up/temperaturequalificationunknown. Fanusesgenericperkgcoolingfanmaterialproxy,notverifiedindustrialairflow. KeepunknownEPDother/missingmass=4.880810067644745kgplusunknownmodulefractionexplicit;doNOTassigntoallPCB,gold-freepolymeroranyinventedmetal. GFthermoplasticuses70%PA/30%glassfibreengineeringcomposition;polymergrades/flameretardantsunknown. Transformeris .44 ofsource2500kVAprofileatfixedmaterialperVAasexplicitlinearcapacityassumption,notnonlinearsizinglaw. ExistingLVgridsupplyretained:dedicatedtransformerassumedon-site400/690Visolation/voltageadaptation;20/0.4kVsourcecoil/insulationgeometryisMATERIALSCALEPROXY,notexactturnsratiodesign. Nativepublic-griddistributionhardwareanddedicatedplanttransformerareseparatefunctions. NominalsourceGOES2153kgusesexplicit3wt%Si+97%unalloyedsteelreference;thermal/rollingprocessesretainedandscaled. Sourcepressboard36.96isMASSkg,not36.96m3;convertathardboard1000kg/m3reference(800-1300sensitivity). Listedsourceingredients5670kgversusdeclared5681.2kg:11.2kgremainunresolved,notfilledwithmetal. Thislocaltransformerreferencecorrectsunit/compositiononlywithinthisnewprovider;existingPVworkbookunchanged. ManufacturingONLYinnewhardwarehelpers;existingplantassemblyelectricityretained,noextraoperatinglossenergyorstandby. Lifetime20yearBoPallocationandstacklifeunchanged. UpdateexistingBoPEOLvectorsbyremovingoldpowerblock600kgsteel/100kgAl/200kgCu/100kgplastic,andaddonecompletepower-conversiontreatment. NewEOLroutesknowntransformermetals,cabinetbulkmetals,oil,cellulose,epoxy/rubber/paint,andremainingconvertermassonce;unresolvedtransformermassandmixedminor-metalfatesremaincoveragegaps. No EPDmoduleDcredits,providerrecyclingsharechanges,native/runtime/YAMLmutations.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -11283,7 +11285,7 @@
         <v>210</v>
       </c>
       <c r="B278" s="11">
-        <v>-32</v>
+        <v>0.0</v>
       </c>
       <c r="C278" s="11" t="s">
         <v>212</v>
@@ -11299,7 +11301,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+          <t>DUPLICATE CONTROL-PLASTIC RETIREMENT CORRECTION, 2026-10-20. Existing purchased control-unit assembly:100kg, nominal46%steel/32%industrial plastic/14%mounted boards/8%cables; native ecoinvent control-unit documentation, checked in3.12cutoff RER andRoW. Cable inputs expressed partly in metres are NOT summed as kg. These are retained source assembly fractions, not a newly measured control-panel BOM. Existing inventory sources Gerloff2021 DOI10.1016/j.est.2021.102759 and the separately documented replacement power-conversion/drive kits. The100kg plant control-unit assembly already sends its32kg nominal housing plastic to the existing industrial-electronics plastic waste route. The additional32kg mixed-plastic entry in PEM, and32kg within the34.8kg SOEC mixed-plastic entry, duplicate that same finished housing. Remove only the duplicate32kg: PEM-32 becomes0kg; SOEC-34.8 becomes-2.8kg. Keep SOEC1.4kgABS control panel+1.4kg elastomer insulation once in the mixed route. Keep PEM764.6kg and SOEC534kg PE/PP retirement separately; these correspond to the direct finished polymer purchases. AEC mixed plastic remains unchanged: its93kg represents92.9kg separate elastomer insulation with original rounding, not another control housing. The source control-unit32.193kg gross polymer feed contains its own manufacturing loss and is not32.193kg finished housing. Dedicated converter/drive-kit and cable/PCB treatments remain unchanged. No extra manufacture, changed metal input, operating energy, lifetime or recycling credit. This reconciles the nominal retirement boundary, not polymer grade or actual fate.</t>
         </is>
       </c>
       <c r="J278"/>
@@ -19819,7 +19821,9 @@
       </c>
       <c r="B577" s="14" t="inlineStr">
         <is>
-          <t>SOEC BoP STEEL RETIREMENT RECONCILIATION, 2026-10-20. Existing purchased control-unit assembly:100kg, nominal46%steel/32%industrial plastic/14%mounted boards/8%cables; native ecoinvent control-unit documentation, checked in3.12cutoff RER andRoW. Cable inputs expressed partly in metres are NOT summed as kg. These are retained source assembly fractions, not a newly measured control-panel BOM. Existing inventory sources Gerloff2021 DOI10.1016/j.est.2021.102759 and the separately documented replacement power-conversion/drive kits. Read retained material purchases, not the separate forming-service kg:ordinary/stainless steel16215.4+1503.6+2250=19969kg, plus46kg control housing gives20015kg to existing scrap-steel route. Reinforcing steel6500+5000+8.5+452.1+399+7+267=12633.6kg to its existing sorting route. Previous20421kg scrap steel and12227kg reinforcement misplaced approximately406kg between routes and retained0.6kg source rounding. Correct these two amounts only. Cast iron3000kg has its separate route. All new transformer, converter and replacement-drive metals remain handled by their separate treatment kit: do not add them to these totals again. Manufacturing, metal feeds, operating energy, lifetimes, waste signs and supplier identities are unchanged. This reconciles the existing nominal material ledger, not actual plant grades or recycling recovery fractions; no avoided-production credit.
+          <t>DUPLICATE CONTROL-PLASTIC RETIREMENT CORRECTION, 2026-10-20. Existing purchased control-unit assembly:100kg, nominal46%steel/32%industrial plastic/14%mounted boards/8%cables; native ecoinvent control-unit documentation, checked in3.12cutoff RER andRoW. Cable inputs expressed partly in metres are NOT summed as kg. These are retained source assembly fractions, not a newly measured control-panel BOM. Existing inventory sources Gerloff2021 DOI10.1016/j.est.2021.102759 and the separately documented replacement power-conversion/drive kits. The100kg plant control-unit assembly already sends its32kg nominal housing plastic to the existing industrial-electronics plastic waste route. The additional32kg mixed-plastic entry in PEM, and32kg within the34.8kg SOEC mixed-plastic entry, duplicate that same finished housing. Remove only the duplicate32kg: PEM-32 becomes0kg; SOEC-34.8 becomes-2.8kg. Keep SOEC1.4kgABS control panel+1.4kg elastomer insulation once in the mixed route. Keep PEM764.6kg and SOEC534kg PE/PP retirement separately; these correspond to the direct finished polymer purchases. AEC mixed plastic remains unchanged: its93kg represents92.9kg separate elastomer insulation with original rounding, not another control housing. The source control-unit32.193kg gross polymer feed contains its own manufacturing loss and is not32.193kg finished housing. Dedicated converter/drive-kit and cable/PCB treatments remain unchanged. No extra manufacture, changed metal input, operating energy, lifetime or recycling credit. This reconciles the nominal retirement boundary, not polymer grade or actual fate.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+SOEC BoP STEEL RETIREMENT RECONCILIATION, 2026-10-20. Existing purchased control-unit assembly:100kg, nominal46%steel/32%industrial plastic/14%mounted boards/8%cables; native ecoinvent control-unit documentation, checked in3.12cutoff RER andRoW. Cable inputs expressed partly in metres are NOT summed as kg. These are retained source assembly fractions, not a newly measured control-panel BOM. Existing inventory sources Gerloff2021 DOI10.1016/j.est.2021.102759 and the separately documented replacement power-conversion/drive kits. Read retained material purchases, not the separate forming-service kg:ordinary/stainless steel16215.4+1503.6+2250=19969kg, plus46kg control housing gives20015kg to existing scrap-steel route. Reinforcing steel6500+5000+8.5+452.1+399+7+267=12633.6kg to its existing sorting route. Previous20421kg scrap steel and12227kg reinforcement misplaced approximately406kg between routes and retained0.6kg source rounding. Correct these two amounts only. Cast iron3000kg has its separate route. All new transformer, converter and replacement-drive metals remain handled by their separate treatment kit: do not add them to these totals again. Manufacturing, metal feeds, operating energy, lifetimes, waste signs and supplier identities are unchanged. This reconciles the existing nominal material ledger, not actual plant grades or recycling recovery fractions; no avoided-production credit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -20255,7 +20259,7 @@
         <v>210</v>
       </c>
       <c r="B593" s="11">
-        <v>-34.8</v>
+        <v>-2.8</v>
       </c>
       <c r="C593" s="11" t="s">
         <v>212</v>
@@ -20271,7 +20275,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>APPROVED ELECTROLYZER AUXILIARY DRIVE REFERENCES, issue98, 2026-10-18. ABB ACS880-01 R6 environmentalclaim RevB20240619:75kW,46.82kgincludingwood10.7%+cardboard1.3%,10yearlife. R3 EPD RevA20241127:18.5kWrepresentative,range5.5-22kWincludes15kW,11.9kgincludingcardboard11.5%+paper1.7%. R1 claim RevB20240617:5.5kWrepresentative,range0.75-5.5kWincludes1.1kW,8.71kgincludingcardboard8.8%+EPP4.1%. Sources https://library.e.abb.com/public/38ade840ed494fa4864fdb705fed986a/Self-Declared_Environmental_Claim_ACS880-01_R6_3AXD10002202569_RevB_EN_20240619.pdf ; https://library.e.abb.com/public/657ba75f918a4bfe9c6d28b90bc926fa/PEP_EPD_ACS880-01_R3_3AXD10002381313_RevA_EN_20241127.pdf ; https://library.e.abb.com/public/8eb29c5519684381bfc61d575364e663/Self-Declared_Environmental_Claim_ACS880-01_R1_3AXD10002202558_RevB_EN_20240617.pdf . Originalcompressorfrequencyconverter300kg(60Al+45Cu+180reinforcingsteel+15elastomer)containednodedicatedswitches/capacitors/controlparts;SOECfivecopies1500kgplus4.9kgwaterpumpdrive. ReplaceonlytheseexplicitdrivevectorsandCuwiredrawing,notcompressors,motors,100kgplantcontrols,mainrectifier93orotherBoP. Motornameplates/pressurestageallocationwerenotrecovered. ChooseEXPLICITengineeringdutyenvelope75kWaggregatecompressormotorcapacity:one75kWdriveinPEM/AEC;five15kWdrivesinSOEC;one1.1kWwaterpumpdriveinSOEC. Thesearecapacity-matchedREFERENCEASSUMPTIONS,notproofoldplantmotorshadtheseratings. For25kgH2/h,1-&gt;30bar,298K,theisothermalminimum~29kW;75kWenvelopegivesheadroombutPEM/AECpressureconditions/actualstageworkdifferandmustbevalidated. Sensitivitytotal30/75/150kW,onevsfivestagesandoriginalmass-basedrecipe;nonewcompressionlossenergyaddedbecauseexistingH2energydemandretained. R3/R1profiletransferredwithinpublishedframepowerrange,notlinearlyscaledby15/18.5or1.1/5.5. R6knownfractionssteel45,Al14.4,Cu7.2,PC5.3,ABS3.7,electronics7.7wt%ofgross46.82;R3steel19.5,Al22.1,PC18.9,ABS5.1,SEBS0.9,electronics15.7;R1steel16.7,Al16.4,Cu3.4,PC22,ABS8.5,electronics15.4. Percentagesapplytogrosspackagedmass,packagingexcludedfrominstalledweightandmodeledonce. EPDother/missingfractionkeptUNRESOLVED,notallocatedtozero-metalplastic;R3smallCucontentlikelywithinother,notclaimedzeroCu. Electronicscategoryisexplicitpartitionassumption:75kW6halfbridgemodules(3IGBTswitching+3usingintegralantiparalleldiodesaspassivebridge),0.75kgmountedPCB,0.65kgfilmDC-linkcaps,0.05kgfan;15kW12TO2471200Vparts(6switches+6bodydiodesforpassiverectification),1kgmountedPCB,0.6kgcaps,0.05kgfan;1.1kW12TO247650Vparts,0.65kgPCB,0.35kgcaps,0.06kgfan. ThisisCONSERVATIVEsyntheticrectifierchoicewithunusedswitchdies,notABBfittedBOM. Mountedsupplierincludesgate/controlICs;doNOTaddTIgate-driverpackagesagain. Reference0.2mF/kWDC-linkat600V and8kHzswitchingisnotvalidatedripple/thermal/EMIdesign. BulkEPDmetalsareassumedoutsideelectronicscategory;partitionuncertaintymustbesensitivitytested,nodoublecompleteEVinverter. OtherresidualelectronicsunmodelledcompositionisnotzeroAu/Ag/Ta. EPD10yearlifevs20yearBoPmeans2expectedmanufacturing/EOLpurchasesperdrive;5-20yearlifesensitivity. Nooperatingelectricityorlifechangeselsewhere. RemoveoldknowncomponentamountsfromexistingaggregateAl/Cu/reinforcingsteel/plasticEOLandaddonekitWEEErouteformatchednewfinishedmass;legacyrounding/otherBoPwastesunvalidated. Packagingtreatedinmanufactureonce,notinstalledWEEE. Fullcomponentmassandassumptionsdocumented,notuniversalindustrialinventory.</t>
+          <t>DUPLICATE CONTROL-PLASTIC RETIREMENT CORRECTION, 2026-10-20. Existing purchased control-unit assembly:100kg, nominal46%steel/32%industrial plastic/14%mounted boards/8%cables; native ecoinvent control-unit documentation, checked in3.12cutoff RER andRoW. Cable inputs expressed partly in metres are NOT summed as kg. These are retained source assembly fractions, not a newly measured control-panel BOM. Existing inventory sources Gerloff2021 DOI10.1016/j.est.2021.102759 and the separately documented replacement power-conversion/drive kits. The100kg plant control-unit assembly already sends its32kg nominal housing plastic to the existing industrial-electronics plastic waste route. The additional32kg mixed-plastic entry in PEM, and32kg within the34.8kg SOEC mixed-plastic entry, duplicate that same finished housing. Remove only the duplicate32kg: PEM-32 becomes0kg; SOEC-34.8 becomes-2.8kg. Keep SOEC1.4kgABS control panel+1.4kg elastomer insulation once in the mixed route. Keep PEM764.6kg and SOEC534kg PE/PP retirement separately; these correspond to the direct finished polymer purchases. AEC mixed plastic remains unchanged: its93kg represents92.9kg separate elastomer insulation with original rounding, not another control housing. The source control-unit32.193kg gross polymer feed contains its own manufacturing loss and is not32.193kg finished housing. Dedicated converter/drive-kit and cable/PCB treatments remain unchanged. No extra manufacture, changed metal input, operating energy, lifetime or recycling credit. This reconciles the nominal retirement boundary, not polymer grade or actual fate.</t>
         </is>
       </c>
       <c r="J593"/>
